--- a/docs/PARALLAXE_Design_Complet.xlsx
+++ b/docs/PARALLAXE_Design_Complet.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="R83c7ea82cdde49e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boucle" sheetId="2" r:id="R87e2aaee61a549bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomalies" sheetId="3" r:id="Rf6fcc9d2bcc044db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coopération" sheetId="4" r:id="R6e3a01744b3247ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Radio" sheetId="5" r:id="R4b3a049d2c614c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="6" r:id="R8ea18143cbcc4689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveaux" sheetId="7" r:id="R2c80bd39626e4bd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lieux" sheetId="8" r:id="R97cf5e5b18ed4911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direction artistique" sheetId="9" r:id="R3da3ac57945940aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="10" r:id="Rcd983a22f1954b00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commandes" sheetId="11" r:id="R7077c20af6eb4cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narration" sheetId="12" r:id="R72369e6f05ea470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="13" r:id="Rf3047eb4c2b642b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="14" r:id="Rd5a82cbf77d1405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="15" r:id="Re9ac3f53d5044ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="Rd860a8f3c5fd43ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boucle" sheetId="2" r:id="R473a0ffd5eff42af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomalies" sheetId="3" r:id="R3095c15dee364e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coopération" sheetId="4" r:id="R2332f36235c94e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Radio" sheetId="5" r:id="Rc308d49f9a9a4280"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="6" r:id="Re871745b31d14919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveaux" sheetId="7" r:id="R9413597ed0de4b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lieux" sheetId="8" r:id="R29bca919142a44ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direction artistique" sheetId="9" r:id="R658864451f604223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="10" r:id="R18e419a2df38430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commandes" sheetId="11" r:id="Rdc22a7b299c64b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narration" sheetId="12" r:id="R4300c79667974324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="13" r:id="R64f150af41194520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="14" r:id="R4850e4e2055445f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="15" r:id="Red9d6b2d8fac4aa9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -713,8 +713,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="P9_Production" displayName="P9_Production" ref="A5:H59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H59"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="P9_Production" displayName="P9_Production" ref="A5:H61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H61"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Priorité"/>
@@ -730,8 +730,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="P9_QA" displayName="P9_QA" ref="A5:H81" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="P9_QA" displayName="P9_QA" ref="A5:H86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H86"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Priorité"/>
@@ -747,8 +747,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="P9_References" displayName="P9_References" ref="A5:G31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="P9_References" displayName="P9_References" ref="A5:G34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G34"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Type"/>
@@ -810,8 +810,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="P9_Radio" displayName="P9_Radio" ref="A5:H32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="P9_Radio" displayName="P9_Radio" ref="A5:H35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H35"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Système / preuve"/>
@@ -1153,7 +1153,7 @@
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>Conception et suivi · édition 0.2.0 · 26 octobre 2026</x:v>
+        <x:v>Conception et suivi · édition 0.2.1 · 26 octobre 2026</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -1204,8 +1204,8 @@
         <x:v>Lots de production</x:v>
       </x:c>
       <x:c r="E7" s="34" t="n">
-        <x:f>COUNTA('Production'!$A$6:$A$59)</x:f>
-        <x:v>54</x:v>
+        <x:f>COUNTA('Production'!$A$6:$A$61)</x:f>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F7" s="3"/>
       <x:c r="G7" s="3"/>
@@ -1224,8 +1224,8 @@
         <x:v>Lots en code ou présents</x:v>
       </x:c>
       <x:c r="E8" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$59,"Présent")+COUNTIFS('Production'!$E$6:$E$59,"Implémenté — QA partielle")</x:f>
-        <x:v>27</x:v>
+        <x:f>COUNTIFS('Production'!$E$6:$E$61,"Présent")+COUNTIFS('Production'!$E$6:$E$61,"Implémenté — QA partielle")</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="3"/>
       <x:c r="G8" s="3"/>
@@ -1244,7 +1244,7 @@
         <x:v>Lots à vérifier / éprouver</x:v>
       </x:c>
       <x:c r="E9" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$59,"À vérifier")+COUNTIFS('Production'!$E$6:$E$59,"À exécuter")+COUNTIFS('Production'!$E$6:$E$59,"À tester sur GPU")+COUNTIFS('Production'!$E$6:$E$59,"À tester sur appareils")</x:f>
+        <x:f>COUNTIFS('Production'!$E$6:$E$61,"À vérifier")+COUNTIFS('Production'!$E$6:$E$61,"À exécuter")+COUNTIFS('Production'!$E$6:$E$61,"À tester sur GPU")+COUNTIFS('Production'!$E$6:$E$61,"À tester sur appareils")</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="3"/>
@@ -1264,7 +1264,7 @@
         <x:v>Lots futurs</x:v>
       </x:c>
       <x:c r="E10" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$59,"Conçu — non implémenté")</x:f>
+        <x:f>COUNTIFS('Production'!$E$6:$E$61,"Conçu — non implémenté")</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="3"/>
@@ -1284,8 +1284,8 @@
         <x:v>Priorités P0</x:v>
       </x:c>
       <x:c r="E11" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$B$6:$B$59,"P0")</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTIFS('Production'!$B$6:$B$61,"P0")</x:f>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F11" s="3"/>
       <x:c r="G11" s="3"/>
@@ -1304,7 +1304,7 @@
         <x:v>Priorités P1</x:v>
       </x:c>
       <x:c r="E12" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$B$6:$B$59,"P1")</x:f>
+        <x:f>COUNTIFS('Production'!$B$6:$B$61,"P1")</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="3"/>
@@ -1324,8 +1324,8 @@
         <x:v>Parcours QA documentés</x:v>
       </x:c>
       <x:c r="E13" s="34" t="n">
-        <x:f>COUNTA('QA'!$A$6:$A$81)</x:f>
-        <x:v>76</x:v>
+        <x:f>COUNTA('QA'!$A$6:$A$86)</x:f>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F13" s="3"/>
       <x:c r="G13" s="3"/>
@@ -1543,7 +1543,7 @@
     </x:row>
     <x:row r="28" ht="31" customHeight="1">
       <x:c r="A28" s="37" t="str">
-        <x:v>Vraie voix avec permission explicite, PTT, six effets de réception et calibration sans micro. Corps articulés et reflets planaires.</x:v>
+        <x:v>Correctif 0.2.1 : flux micro tardifs arrêtés après extinction / sortie ; réactivation récente préservée ; commande de radio débloquée sans attendre une ancienne permission.</x:v>
       </x:c>
       <x:c r="B28" s="37"/>
       <x:c r="C28" s="37"/>
@@ -1555,7 +1555,7 @@
     </x:row>
     <x:row r="29" ht="39" customHeight="1">
       <x:c r="A29" s="37" t="str">
-        <x:v>Vérifié : 17 tests de règles, 12 tests radio, 11 suites CPU 3D et campagne D1 à quatre clients HTTP. Deux onglets échangent offre/réponse, mais zéro candidat ICE empêche la connexion audio. GPU et microphones physiques non éprouvés.</x:v>
+        <x:v>Correctif 0.2.1 : 19 tests radio, 4 du contrôleur UI, deux builds et test portable à deux clients HTTP réussis. Preuves v0.2 conservées : 17 règles, 11 suites CPU 3D et D1 quatre clients. GPU, microphones physiques, transport vocal et TURN réel restent non validés.</x:v>
       </x:c>
       <x:c r="B29" s="37"/>
       <x:c r="C29" s="37"/>
@@ -2160,7 +2160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eade47a9daa4217"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb869eebedf0b44f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2806,7 +2806,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f099ff108a84c6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R110b77c14b7242b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3314,7 +3314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd534c747764e44e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd05a49a6e2943b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3495,7 +3495,7 @@
         <x:v>Contenu</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Intégrer les 54 anomalies présentes au catalogue runtime v0.2.</x:v>
+        <x:v>Intégrer les 54 anomalies présentes au catalogue runtime 0.2.1.</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -3663,7 +3663,7 @@
         <x:v>QA15–QA25, QA41–QA46</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
+        <x:v>Rapport v0.2 conservé : D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="40" customHeight="1">
@@ -4290,7 +4290,7 @@
         <x:v>Un prototype jouable n’est pas une validation commerciale complète.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="40" customHeight="1">
+    <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="12" t="str">
         <x:v>P35</x:v>
       </x:c>
@@ -4301,7 +4301,7 @@
         <x:v>Export</x:v>
       </x:c>
       <x:c r="D40" s="12" t="str">
-        <x:v>Fournir source, édition autonome, instructions et Excel v0.2 synchronisé.</x:v>
+        <x:v>Fournir source, édition autonome, instructions et Excel 0.2.1 synchronisé.</x:v>
       </x:c>
       <x:c r="E40" s="13" t="str">
         <x:v>À vérifier</x:v>
@@ -4310,10 +4310,10 @@
         <x:v>Livraison</x:v>
       </x:c>
       <x:c r="G40" s="12" t="str">
-        <x:v>Version 0.2.0</x:v>
+        <x:v>Version 0.2.1</x:v>
       </x:c>
       <x:c r="H40" s="12" t="str">
-        <x:v>Dépôt GitHub et archive reproductibles ; aucun secret ou dépendance volumineuse inutile.</x:v>
+        <x:v>Builds local / hébergé et test portable à deux clients HTTP réussis. Classeur synchronisé. Intégrité des nouvelles archives et GitHub CI à vérifier après assemblage / publication ; rapport docs/qa-final-v0.2.1.json.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="40" customHeight="1">
@@ -4810,20 +4810,72 @@
         <x:v>GLTFExporter puis GLTFLoader réussis ; matériaux de base et articulation rigide explicités. Visuel GPU restant.</x:v>
       </x:c>
     </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="12" t="str">
+        <x:v>P55</x:v>
+      </x:c>
+      <x:c r="B60" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C60" s="12" t="str">
+        <x:v>Cycle du microphone</x:v>
+      </x:c>
+      <x:c r="D60" s="12" t="str">
+        <x:v>Fermer les flux retournés après extinction / sortie et protéger une réactivation plus récente.</x:v>
+      </x:c>
+      <x:c r="E60" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F60" s="12" t="str">
+        <x:v>Audio / cycle asynchrone</x:v>
+      </x:c>
+      <x:c r="G60" s="12" t="str">
+        <x:v>Radio R28–R29 ; QA77–QA79</x:v>
+      </x:c>
+      <x:c r="H60" s="12" t="str">
+        <x:v>19/19 tests radio réussis, dont 7 nouveaux : extinction, micro seul, anciennes réponses, nouvelle demande et sortie. Avant correction : 6 échecs / 1 succès ; après : 7/7. Pistes et API simulées ; aucun microphone physique ni transmission mesurée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="77" customHeight="1">
+      <x:c r="A61" s="11" t="str">
+        <x:v>P56</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="str">
+        <x:v>Commande de radio</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="str">
+        <x:v>Libérer l’état d’attente de l’interface à l’extinction et isoler chaque nouvelle opération.</x:v>
+      </x:c>
+      <x:c r="E61" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="str">
+        <x:v>UI / contrôleur</x:v>
+      </x:c>
+      <x:c r="G61" s="11" t="str">
+        <x:v>Radio R30 ; QA80</x:v>
+      </x:c>
+      <x:c r="H61" s="11" t="str">
+        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E59">
+  <x:conditionalFormatting sqref="E6:E61">
     <x:cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E59">
+    <x:dataValidation type="list" sqref="E6:E61">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f9ee089d5c426d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cd1f55f13514701"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5891,7 @@
         <x:v>Contrôler IDs, couverture runtime, compteurs, statuts, tableaux et rendu.</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>120 fiches ; 54 en code ; 66 futures ; 15 feuilles ; 76 parcours QA.</x:v>
+        <x:v>120 fiches ; 54 en code ; 66 futures ; 15 feuilles ; 80 parcours QA.</x:v>
       </x:c>
       <x:c r="F41" s="13" t="str">
         <x:v>Réussi</x:v>
@@ -5848,7 +5900,7 @@
         <x:v>Artifact Tool / XLSX</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>Générateur v0.2 : 120 IDs uniques, 54 runtime, 66 prévus ; compteurs et pools recalculés, statuts modifiés puis restaurés ; contrôle du XLSX et rendus représentatifs.</x:v>
+        <x:v>Générateur v0.2.1 : 120 IDs uniques, 54 runtime, 66 prévus ; versions cohérentes, compteurs et pools recalculés, modifications temporaires restaurées et feuilles touchées rendues.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="40" customHeight="1">
@@ -6111,7 +6163,7 @@
         <x:v>Campagne quatre clients HTTP traversée avec lieux/références synchronisés ; mode unique couvert dans les règles. Vérification graphique multi-appareils restante.</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="51" customHeight="1">
+    <x:row r="52" ht="64" customHeight="1">
       <x:c r="A52" s="12" t="str">
         <x:v>QA47</x:v>
       </x:c>
@@ -6134,7 +6186,7 @@
         <x:v>Chrome / Firefox / Safari</x:v>
       </x:c>
       <x:c r="H52" s="12" t="str">
-        <x:v>Tests avec doubles de périphériques : aucune demande avant action explicite, démarrage muet et libération des pistes. Permission et indicateur sur micro physique non observés.</x:v>
+        <x:v>19 tests radio réussis avec doubles de périphériques : permission explicite, démarrage muet et arrêt des flux reçus après invalidation. Aucun microphone physique ni indicateur matériel observé.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="51" customHeight="1">
@@ -6238,7 +6290,7 @@
         <x:v>Navigateurs / certificats</x:v>
       </x:c>
       <x:c r="H56" s="12" t="str">
-        <x:v>12 tests radio incluent une origine LAN non sécurisée : indisponibilité technique annoncée, aucun prompt micro ni altération de preuve. Certificat LAN réel non testé.</x:v>
+        <x:v>19 tests radio incluent une origine LAN non sécurisée : indisponibilité technique annoncée, aucun prompt micro ni altération de preuve. Certificat LAN réel non testé.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
@@ -6319,7 +6371,7 @@
         <x:v>Les tests établissent l’indépendance de la preuve au consentement et au transport. Scénario complet de coupure pendant une session vocale physique restant.</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="51" customHeight="1">
+    <x:row r="60" ht="64" customHeight="1">
       <x:c r="A60" s="12" t="str">
         <x:v>QA55</x:v>
       </x:c>
@@ -6342,7 +6394,7 @@
         <x:v>WebAudio et inspection code</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str">
-        <x:v>Tests radio : fermeture et instances retirées contrôlées ; états PTT expirent. Vérifier à l’oreille les queues d’effet et transitions répétées sur appareil.</x:v>
+        <x:v>Correctif v0.2.1 : les demandes micro invalidées ne peuvent plus installer un flux tardif ; les pistes reçues sont arrêtées. Nettoyage vérifié avec doubles de périphériques. Queues sonores et matériel restent à écouter.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="51" customHeight="1">
@@ -6891,20 +6943,150 @@
         <x:v>Deux onglets réels : salon, écoute sans permission micro, calibration écrite et échange offre/réponse réussis ; négociation stable. ICE terminé avec zéro candidat local/distant : liaison audio non établie. Aucun flux vocal ni micro physique validé.</x:v>
       </x:c>
     </x:row>
+    <x:row r="82" ht="64" customHeight="1">
+      <x:c r="A82" s="12" t="str">
+        <x:v>QA77</x:v>
+      </x:c>
+      <x:c r="B82" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C82" s="12" t="str">
+        <x:v>Permission après arrêt</x:v>
+      </x:c>
+      <x:c r="D82" s="12" t="str">
+        <x:v>Différer getUserMedia, éteindre la radio ou couper le micro seul puis résoudre l’autorisation avec un flux.</x:v>
+      </x:c>
+      <x:c r="E82" s="12" t="str">
+        <x:v>Chaque piste tardive est stoppée ; aucun flux local retenu. L’écoute seule reste active si elle a été conservée.</x:v>
+      </x:c>
+      <x:c r="F82" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G82" s="12" t="str">
+        <x:v>Tests radio à promesse différée</x:v>
+      </x:c>
+      <x:c r="H82" s="12" t="str">
+        <x:v>Deux tests réussis : désactiver toute la radio ou le micro seul avant résolution. La piste tardive est stoppée ; le micro reste éteint et l’écoute choisie est conservée. Promesses et flux simulés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
+      <x:c r="A83" s="11" t="str">
+        <x:v>QA78</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="str">
+        <x:v>Permission après sortie</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="str">
+        <x:v>Différer getUserMedia, détruire la radio / quitter puis résoudre la permission.</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="str">
+        <x:v>Le résultat obsolète est fermé et ne ressuscite pas la session retirée.</x:v>
+      </x:c>
+      <x:c r="F83" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G83" s="11" t="str">
+        <x:v>Test radio à promesse différée</x:v>
+      </x:c>
+      <x:c r="H83" s="11" t="str">
+        <x:v>Test réussi : un flux retourné après destruction de la radio est stoppé et la session reste inactive. Cette protection existante passait déjà avant le correctif et reste conservée. Aucun périphérique physique utilisé.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
+      <x:c r="A84" s="12" t="str">
+        <x:v>QA79</x:v>
+      </x:c>
+      <x:c r="B84" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C84" s="12" t="str">
+        <x:v>Réactivation concurrente</x:v>
+      </x:c>
+      <x:c r="D84" s="12" t="str">
+        <x:v>Désactiver, relancer puis résoudre/refuser l’ancienne demande ou son activation d’écoute dans différents ordres.</x:v>
+      </x:c>
+      <x:c r="E84" s="12" t="str">
+        <x:v>Flux récent, demande courante et écoute préservés ; ancien succès arrêté, ancien refus ou finaliseur sans effet sur l’état récent.</x:v>
+      </x:c>
+      <x:c r="F84" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G84" s="12" t="str">
+        <x:v>Quatre tests radio de réactivation</x:v>
+      </x:c>
+      <x:c r="H84" s="12" t="str">
+        <x:v>Quatre tests réussis : ancien accord, ancien refus, ancienne finalisation et ancien échec d’écoute ne remplacent ni ne coupent le flux / la demande / l’écoute récents. Nouvel état PTT préservé et demande courante non dupliquée. API simulées.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="77" customHeight="1">
+      <x:c r="A85" s="11" t="str">
+        <x:v>QA80</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="str">
+        <x:v>Attente de l’interface</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="str">
+        <x:v>Lancer une permission différée, éteindre, réactiver puis terminer l’ancienne opération.</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="str">
+        <x:v>Nouvelle activation disponible ; les résultats anciens ne modifient pas l’état d’attente de l’opération récente.</x:v>
+      </x:c>
+      <x:c r="F85" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G85" s="11" t="str">
+        <x:v>Tests du contrôleur UI</x:v>
+      </x:c>
+      <x:c r="H85" s="11" t="str">
+        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="77" customHeight="1">
+      <x:c r="A86" s="12" t="str">
+        <x:v>QA81</x:v>
+      </x:c>
+      <x:c r="B86" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C86" s="12" t="str">
+        <x:v>Builds et édition portable</x:v>
+      </x:c>
+      <x:c r="D86" s="12" t="str">
+        <x:v>Compiler les éditions locale et hébergée ; lancer le serveur portable compilé avec deux clients HTTP, sans node_modules.</x:v>
+      </x:c>
+      <x:c r="E86" s="12" t="str">
+        <x:v>HTML servi ; modules serveur privés ; références et consensus justes ; départ des deux membres.</x:v>
+      </x:c>
+      <x:c r="F86" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G86" s="12" t="str">
+        <x:v>Build / HTTP portable</x:v>
+      </x:c>
+      <x:c r="H86" s="12" t="str">
+        <x:v>v0.2.1 : typecheck, build local, build hébergé et test portable réussis. Deux clients HTTP authentifiés : référence, inspection, perceptions privées, unanimité et sortie ; serveur compilé lancé sans node_modules. Les archives finales et GitHub CI restent à contrôler après assemblage / publication.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F6:F81">
+  <x:conditionalFormatting sqref="F6:F86">
     <x:cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="38" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F6:F81">
+    <x:dataValidation type="list" sqref="F6:F86">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re43065e9d1fd43cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5e62a490fb44b8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7065,7 +7247,7 @@
         <x:v>Source de vérité code</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Catalogue runtime v0.2</x:v>
+        <x:v>Catalogue runtime 0.2.1</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>54 identifiants intégrés ; titres, baseline, intensité, difficulté et lieux proviennent du code.</x:v>
@@ -7088,7 +7270,7 @@
         <x:v>Règles actuelles</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Machine de jeu v0.2</x:v>
+        <x:v>Machine de jeu 0.2.1</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
         <x:v>Campagne 3 × 3 avec paliers ; lieu unique 9 consécutifs ; 68 % d’anomalies ; 3 erreurs standard.</x:v>
@@ -7471,7 +7653,7 @@
         <x:v>Le panneau métro et le moniteur clinique sont des références fixes de jeu.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="64" customHeight="1">
+    <x:row r="27" ht="77" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>R22</x:v>
       </x:c>
@@ -7482,7 +7664,7 @@
         <x:v>Bilan de vérification</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>17 tests de règles, 12 tests radio, 11 suites géométriques CPU ; D1 local quatre clients et neuf tours réussi. Deux onglets : offre/réponse échangées, mais zéro candidat ICE et aucun audio connecté. GLB relu avec trois clips.</x:v>
+        <x:v>v0.2.1 : 19 tests radio et 4 du contrôleur UI réussis ; typecheck, builds local / hébergé et test portable à deux clients HTTP réussis. Preuves v0.2 conservées : 17 règles, 11 suites CPU 3D, D1 quatre clients et GLB relu. Aucun nouvel essai ICE ou de microphone physique.</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
         <x:v>docs/QA.md</x:v>
@@ -7586,10 +7768,79 @@
         <x:v>Modèle procédural original ; pas de skinning, pas de lettrage badge embarqué et pas de validation GPU.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>R27</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Correctif vérifié</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Autorisation micro tardive · 0.2.1</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>Invalider les demandes obsolètes, arrêter leurs flux retournés et préserver la réactivation la plus récente.</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>docs/qa-radio-cancellation-v0.2.1.json ; tests/radio.test.mjs</x:v>
+      </x:c>
+      <x:c r="F32" s="20" t="d">
+        <x:v>2026-10-26T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>19/19 tests radio réussis, dont 7 nouveaux : extinction, micro seul, anciennes réponses, nouvelle demande et sortie. Avant correction : 6 échecs / 1 succès ; après : 7/7. Pistes et API simulées ; aucun microphone physique ni transmission mesurée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="77" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>R28</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Contrôleur vérifié</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>État d’attente de la radio · 0.2.1</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>Annuler l’opération UI retirée afin qu’une permission encore ouverte ne bloque pas la commande suivante.</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>docs/qa-radio-ui-v0.2.1.json ; tests/radio-actions.test.mjs</x:v>
+      </x:c>
+      <x:c r="F33" s="22" t="d">
+        <x:v>2026-10-26T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str">
+        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="77" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>R29</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Livraison vérifiée</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Compilation et serveur portable · 0.2.1</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>Typecheck, builds local / hébergé et parcours HTTP portable à deux clients exécutés.</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>docs/qa-final-v0.2.1.json ; .github/workflows/ci.yml</x:v>
+      </x:c>
+      <x:c r="F34" s="20" t="d">
+        <x:v>2026-10-26T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>v0.2.1 : typecheck, build local, build hébergé et test portable réussis. Deux clients HTTP authentifiés : référence, inspection, perceptions privées, unanimité et sortie ; serveur compilé lancé sans node_modules. Les archives finales et GitHub CI restent à contrôler après assemblage / publication.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43fd63bcae4a42e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f1c5233b67e42d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8304,7 +8555,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7778cb633344f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c3b554c7314ae1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8508,7 +8759,7 @@
         <x:v>Canal de preuve</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="64" customHeight="1">
+    <x:row r="6" ht="77" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>PX-001</x:v>
       </x:c>
@@ -8561,7 +8812,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R6" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S6" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8576,7 +8827,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="64" customHeight="1">
+    <x:row r="7" ht="77" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>PX-002</x:v>
       </x:c>
@@ -8629,7 +8880,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R7" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S7" s="19" t="str">
         <x:v>Oui</x:v>
@@ -8644,7 +8895,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="64" customHeight="1">
+    <x:row r="8" ht="77" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>PX-003</x:v>
       </x:c>
@@ -8697,7 +8948,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R8" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S8" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8712,7 +8963,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="64" customHeight="1">
+    <x:row r="9" ht="77" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>PX-004</x:v>
       </x:c>
@@ -8765,7 +9016,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R9" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S9" s="19" t="str">
         <x:v>Oui</x:v>
@@ -8780,7 +9031,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="64" customHeight="1">
+    <x:row r="10" ht="77" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>PX-005</x:v>
       </x:c>
@@ -8833,7 +9084,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R10" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S10" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8848,7 +9099,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="64" customHeight="1">
+    <x:row r="11" ht="77" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>PX-006</x:v>
       </x:c>
@@ -8901,7 +9152,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R11" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S11" s="19" t="str">
         <x:v>Oui</x:v>
@@ -8916,7 +9167,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="64" customHeight="1">
+    <x:row r="12" ht="77" customHeight="1">
       <x:c r="A12" s="12" t="str">
         <x:v>PX-007</x:v>
       </x:c>
@@ -8969,7 +9220,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R12" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S12" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8984,7 +9235,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="64" customHeight="1">
+    <x:row r="13" ht="77" customHeight="1">
       <x:c r="A13" s="11" t="str">
         <x:v>PX-008</x:v>
       </x:c>
@@ -9037,7 +9288,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R13" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S13" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9052,7 +9303,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="64" customHeight="1">
+    <x:row r="14" ht="77" customHeight="1">
       <x:c r="A14" s="12" t="str">
         <x:v>PX-009</x:v>
       </x:c>
@@ -9105,7 +9356,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R14" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S14" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9120,7 +9371,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="64" customHeight="1">
+    <x:row r="15" ht="77" customHeight="1">
       <x:c r="A15" s="11" t="str">
         <x:v>PX-010</x:v>
       </x:c>
@@ -9173,7 +9424,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R15" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S15" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9188,7 +9439,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="64" customHeight="1">
+    <x:row r="16" ht="77" customHeight="1">
       <x:c r="A16" s="12" t="str">
         <x:v>PX-011</x:v>
       </x:c>
@@ -9241,7 +9492,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R16" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S16" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9256,7 +9507,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="64" customHeight="1">
+    <x:row r="17" ht="77" customHeight="1">
       <x:c r="A17" s="11" t="str">
         <x:v>PX-012</x:v>
       </x:c>
@@ -9309,7 +9560,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R17" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S17" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9324,7 +9575,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="64" customHeight="1">
+    <x:row r="18" ht="77" customHeight="1">
       <x:c r="A18" s="12" t="str">
         <x:v>PX-013</x:v>
       </x:c>
@@ -9377,7 +9628,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R18" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S18" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9392,7 +9643,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="64" customHeight="1">
+    <x:row r="19" ht="77" customHeight="1">
       <x:c r="A19" s="11" t="str">
         <x:v>PX-014</x:v>
       </x:c>
@@ -9445,7 +9696,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R19" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S19" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9460,7 +9711,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="64" customHeight="1">
+    <x:row r="20" ht="77" customHeight="1">
       <x:c r="A20" s="12" t="str">
         <x:v>PX-015</x:v>
       </x:c>
@@ -9513,7 +9764,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R20" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S20" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9528,7 +9779,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="64" customHeight="1">
+    <x:row r="21" ht="77" customHeight="1">
       <x:c r="A21" s="11" t="str">
         <x:v>PX-016</x:v>
       </x:c>
@@ -9581,7 +9832,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R21" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S21" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9596,7 +9847,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="64" customHeight="1">
+    <x:row r="22" ht="77" customHeight="1">
       <x:c r="A22" s="12" t="str">
         <x:v>PX-017</x:v>
       </x:c>
@@ -9649,7 +9900,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R22" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S22" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9664,7 +9915,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="64" customHeight="1">
+    <x:row r="23" ht="77" customHeight="1">
       <x:c r="A23" s="11" t="str">
         <x:v>PX-018</x:v>
       </x:c>
@@ -9717,7 +9968,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R23" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S23" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9732,7 +9983,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="64" customHeight="1">
+    <x:row r="24" ht="77" customHeight="1">
       <x:c r="A24" s="12" t="str">
         <x:v>PX-019</x:v>
       </x:c>
@@ -9785,7 +10036,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R24" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S24" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9800,7 +10051,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="64" customHeight="1">
+    <x:row r="25" ht="77" customHeight="1">
       <x:c r="A25" s="11" t="str">
         <x:v>PX-020</x:v>
       </x:c>
@@ -9853,7 +10104,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R25" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S25" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9868,7 +10119,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="64" customHeight="1">
+    <x:row r="26" ht="77" customHeight="1">
       <x:c r="A26" s="12" t="str">
         <x:v>PX-021</x:v>
       </x:c>
@@ -9921,7 +10172,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R26" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S26" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9936,7 +10187,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="64" customHeight="1">
+    <x:row r="27" ht="77" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>PX-022</x:v>
       </x:c>
@@ -9989,7 +10240,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R27" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S27" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10004,7 +10255,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="64" customHeight="1">
+    <x:row r="28" ht="77" customHeight="1">
       <x:c r="A28" s="12" t="str">
         <x:v>PX-023</x:v>
       </x:c>
@@ -10057,7 +10308,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R28" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S28" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10072,7 +10323,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="64" customHeight="1">
+    <x:row r="29" ht="77" customHeight="1">
       <x:c r="A29" s="11" t="str">
         <x:v>PX-024</x:v>
       </x:c>
@@ -10125,7 +10376,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R29" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S29" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10140,7 +10391,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="64" customHeight="1">
+    <x:row r="30" ht="77" customHeight="1">
       <x:c r="A30" s="12" t="str">
         <x:v>PX-025</x:v>
       </x:c>
@@ -10193,7 +10444,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R30" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S30" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10261,7 +10512,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R31" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S31" s="19" t="str">
         <x:v>—</x:v>
@@ -10276,7 +10527,7 @@
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="64" customHeight="1">
+    <x:row r="32" ht="77" customHeight="1">
       <x:c r="A32" s="12" t="str">
         <x:v>PX-027</x:v>
       </x:c>
@@ -10329,7 +10580,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R32" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S32" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10397,7 +10648,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R33" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S33" s="19" t="str">
         <x:v>—</x:v>
@@ -10465,7 +10716,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R34" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S34" s="18" t="str">
         <x:v>—</x:v>
@@ -10533,7 +10784,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R35" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S35" s="19" t="str">
         <x:v>—</x:v>
@@ -10601,7 +10852,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R36" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S36" s="18" t="str">
         <x:v>—</x:v>
@@ -10616,7 +10867,7 @@
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="64" customHeight="1">
+    <x:row r="37" ht="77" customHeight="1">
       <x:c r="A37" s="11" t="str">
         <x:v>PX-032</x:v>
       </x:c>
@@ -10669,7 +10920,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R37" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S37" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10737,7 +10988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R38" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S38" s="18" t="str">
         <x:v>—</x:v>
@@ -10805,7 +11056,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R39" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S39" s="19" t="str">
         <x:v>—</x:v>
@@ -10873,7 +11124,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R40" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S40" s="18" t="str">
         <x:v>—</x:v>
@@ -10941,7 +11192,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R41" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S41" s="19" t="str">
         <x:v>—</x:v>
@@ -11009,7 +11260,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R42" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S42" s="18" t="str">
         <x:v>—</x:v>
@@ -11077,7 +11328,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R43" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S43" s="19" t="str">
         <x:v>—</x:v>
@@ -11145,7 +11396,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R44" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S44" s="18" t="str">
         <x:v>—</x:v>
@@ -11213,7 +11464,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R45" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S45" s="19" t="str">
         <x:v>—</x:v>
@@ -11281,7 +11532,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R46" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S46" s="18" t="str">
         <x:v>—</x:v>
@@ -11349,7 +11600,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R47" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S47" s="19" t="str">
         <x:v>—</x:v>
@@ -11417,7 +11668,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R48" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S48" s="18" t="str">
         <x:v>—</x:v>
@@ -11485,7 +11736,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R49" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S49" s="19" t="str">
         <x:v>—</x:v>
@@ -11553,7 +11804,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R50" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S50" s="18" t="str">
         <x:v>—</x:v>
@@ -11621,7 +11872,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R51" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S51" s="19" t="str">
         <x:v>—</x:v>
@@ -11689,7 +11940,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R52" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S52" s="18" t="str">
         <x:v>—</x:v>
@@ -11757,7 +12008,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R53" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S53" s="19" t="str">
         <x:v>—</x:v>
@@ -11825,7 +12076,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R54" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S54" s="18" t="str">
         <x:v>—</x:v>
@@ -11893,7 +12144,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R55" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S55" s="19" t="str">
         <x:v>—</x:v>
@@ -11908,7 +12159,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="64" customHeight="1">
+    <x:row r="56" ht="77" customHeight="1">
       <x:c r="A56" s="12" t="str">
         <x:v>PX-051</x:v>
       </x:c>
@@ -11961,7 +12212,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R56" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S56" s="18" t="str">
         <x:v>—</x:v>
@@ -11976,7 +12227,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="64" customHeight="1">
+    <x:row r="57" ht="77" customHeight="1">
       <x:c r="A57" s="11" t="str">
         <x:v>PX-052</x:v>
       </x:c>
@@ -12029,7 +12280,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R57" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S57" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12097,7 +12348,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R58" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S58" s="18" t="str">
         <x:v>—</x:v>
@@ -12165,7 +12416,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R59" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S59" s="19" t="str">
         <x:v>—</x:v>
@@ -12233,7 +12484,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R60" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S60" s="18" t="str">
         <x:v>—</x:v>
@@ -12248,7 +12499,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="64" customHeight="1">
+    <x:row r="61" ht="77" customHeight="1">
       <x:c r="A61" s="11" t="str">
         <x:v>PX-056</x:v>
       </x:c>
@@ -12301,7 +12552,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R61" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S61" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12369,7 +12620,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R62" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S62" s="18" t="str">
         <x:v>—</x:v>
@@ -12437,7 +12688,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R63" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S63" s="19" t="str">
         <x:v>—</x:v>
@@ -12505,7 +12756,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R64" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S64" s="18" t="str">
         <x:v>—</x:v>
@@ -12520,7 +12771,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="64" customHeight="1">
+    <x:row r="65" ht="77" customHeight="1">
       <x:c r="A65" s="11" t="str">
         <x:v>PX-060</x:v>
       </x:c>
@@ -12573,7 +12824,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R65" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S65" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12641,7 +12892,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R66" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S66" s="18" t="str">
         <x:v>—</x:v>
@@ -12709,7 +12960,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R67" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S67" s="19" t="str">
         <x:v>—</x:v>
@@ -12777,7 +13028,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R68" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S68" s="18" t="str">
         <x:v>—</x:v>
@@ -12845,7 +13096,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R69" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S69" s="19" t="str">
         <x:v>—</x:v>
@@ -12913,7 +13164,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R70" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S70" s="18" t="str">
         <x:v>—</x:v>
@@ -12928,7 +13179,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="64" customHeight="1">
+    <x:row r="71" ht="77" customHeight="1">
       <x:c r="A71" s="11" t="str">
         <x:v>PX-066</x:v>
       </x:c>
@@ -12981,7 +13232,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R71" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S71" s="19" t="str">
         <x:v>Oui</x:v>
@@ -13049,7 +13300,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R72" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S72" s="18" t="str">
         <x:v>—</x:v>
@@ -13117,7 +13368,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R73" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S73" s="19" t="str">
         <x:v>—</x:v>
@@ -13185,7 +13436,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R74" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S74" s="18" t="str">
         <x:v>—</x:v>
@@ -13253,7 +13504,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R75" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S75" s="19" t="str">
         <x:v>—</x:v>
@@ -13321,7 +13572,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R76" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S76" s="18" t="str">
         <x:v>—</x:v>
@@ -13389,7 +13640,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R77" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S77" s="19" t="str">
         <x:v>—</x:v>
@@ -13457,7 +13708,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R78" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S78" s="18" t="str">
         <x:v>—</x:v>
@@ -13525,7 +13776,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R79" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S79" s="19" t="str">
         <x:v>—</x:v>
@@ -13593,7 +13844,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R80" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S80" s="18" t="str">
         <x:v>—</x:v>
@@ -13661,7 +13912,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R81" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S81" s="19" t="str">
         <x:v>—</x:v>
@@ -13729,7 +13980,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R82" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S82" s="18" t="str">
         <x:v>—</x:v>
@@ -13744,7 +13995,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="64" customHeight="1">
+    <x:row r="83" ht="77" customHeight="1">
       <x:c r="A83" s="11" t="str">
         <x:v>PX-078</x:v>
       </x:c>
@@ -13797,7 +14048,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R83" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S83" s="19" t="str">
         <x:v>—</x:v>
@@ -13812,7 +14063,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="64" customHeight="1">
+    <x:row r="84" ht="77" customHeight="1">
       <x:c r="A84" s="12" t="str">
         <x:v>PX-079</x:v>
       </x:c>
@@ -13865,7 +14116,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R84" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S84" s="18" t="str">
         <x:v>—</x:v>
@@ -13933,7 +14184,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R85" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S85" s="19" t="str">
         <x:v>—</x:v>
@@ -13948,7 +14199,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="64" customHeight="1">
+    <x:row r="86" ht="77" customHeight="1">
       <x:c r="A86" s="12" t="str">
         <x:v>PX-081</x:v>
       </x:c>
@@ -14001,7 +14252,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R86" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S86" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14016,7 +14267,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="64" customHeight="1">
+    <x:row r="87" ht="77" customHeight="1">
       <x:c r="A87" s="11" t="str">
         <x:v>PX-082</x:v>
       </x:c>
@@ -14069,7 +14320,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R87" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S87" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14084,7 +14335,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="64" customHeight="1">
+    <x:row r="88" ht="77" customHeight="1">
       <x:c r="A88" s="12" t="str">
         <x:v>PX-083</x:v>
       </x:c>
@@ -14137,7 +14388,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R88" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S88" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14152,7 +14403,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="64" customHeight="1">
+    <x:row r="89" ht="77" customHeight="1">
       <x:c r="A89" s="11" t="str">
         <x:v>PX-084</x:v>
       </x:c>
@@ -14205,7 +14456,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R89" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S89" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14220,7 +14471,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="64" customHeight="1">
+    <x:row r="90" ht="77" customHeight="1">
       <x:c r="A90" s="12" t="str">
         <x:v>PX-085</x:v>
       </x:c>
@@ -14273,7 +14524,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R90" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S90" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14288,7 +14539,7 @@
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="64" customHeight="1">
+    <x:row r="91" ht="77" customHeight="1">
       <x:c r="A91" s="11" t="str">
         <x:v>PX-086</x:v>
       </x:c>
@@ -14341,7 +14592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R91" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S91" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14356,7 +14607,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="64" customHeight="1">
+    <x:row r="92" ht="77" customHeight="1">
       <x:c r="A92" s="12" t="str">
         <x:v>PX-087</x:v>
       </x:c>
@@ -14409,7 +14660,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R92" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S92" s="18" t="str">
         <x:v>—</x:v>
@@ -14424,7 +14675,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="64" customHeight="1">
+    <x:row r="93" ht="77" customHeight="1">
       <x:c r="A93" s="11" t="str">
         <x:v>PX-088</x:v>
       </x:c>
@@ -14477,7 +14728,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R93" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S93" s="19" t="str">
         <x:v>—</x:v>
@@ -14492,7 +14743,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="64" customHeight="1">
+    <x:row r="94" ht="77" customHeight="1">
       <x:c r="A94" s="12" t="str">
         <x:v>PX-089</x:v>
       </x:c>
@@ -14545,7 +14796,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R94" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S94" s="18" t="str">
         <x:v>—</x:v>
@@ -14560,7 +14811,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="64" customHeight="1">
+    <x:row r="95" ht="77" customHeight="1">
       <x:c r="A95" s="11" t="str">
         <x:v>PX-090</x:v>
       </x:c>
@@ -14613,7 +14864,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R95" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S95" s="19" t="str">
         <x:v>—</x:v>
@@ -14628,7 +14879,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="64" customHeight="1">
+    <x:row r="96" ht="77" customHeight="1">
       <x:c r="A96" s="12" t="str">
         <x:v>PX-091</x:v>
       </x:c>
@@ -14681,7 +14932,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R96" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S96" s="18" t="str">
         <x:v>—</x:v>
@@ -14696,7 +14947,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="64" customHeight="1">
+    <x:row r="97" ht="77" customHeight="1">
       <x:c r="A97" s="11" t="str">
         <x:v>PX-092</x:v>
       </x:c>
@@ -14749,7 +15000,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R97" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S97" s="19" t="str">
         <x:v>—</x:v>
@@ -14764,7 +15015,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="64" customHeight="1">
+    <x:row r="98" ht="77" customHeight="1">
       <x:c r="A98" s="12" t="str">
         <x:v>PX-093</x:v>
       </x:c>
@@ -14817,7 +15068,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R98" s="12" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S98" s="18" t="str">
         <x:v>—</x:v>
@@ -14832,7 +15083,7 @@
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="64" customHeight="1">
+    <x:row r="99" ht="77" customHeight="1">
       <x:c r="A99" s="11" t="str">
         <x:v>PX-094</x:v>
       </x:c>
@@ -14885,7 +15136,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R99" s="11" t="str">
-        <x:v>ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
       </x:c>
       <x:c r="S99" s="19" t="str">
         <x:v>—</x:v>
@@ -14953,7 +15204,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R100" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S100" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15021,7 +15272,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R101" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S101" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15089,7 +15340,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R102" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S102" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15157,7 +15408,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R103" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S103" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15225,7 +15476,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R104" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S104" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15293,7 +15544,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R105" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 12 tests radio réussis, dont relevés sans micro/réseau, PTT et consentement. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S105" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15361,7 +15612,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R106" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S106" s="18" t="str">
         <x:v>—</x:v>
@@ -15429,7 +15680,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R107" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S107" s="19" t="str">
         <x:v>—</x:v>
@@ -15497,7 +15748,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R108" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S108" s="18" t="str">
         <x:v>—</x:v>
@@ -15565,7 +15816,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R109" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S109" s="19" t="str">
         <x:v>—</x:v>
@@ -15633,7 +15884,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R110" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S110" s="18" t="str">
         <x:v>—</x:v>
@@ -15701,7 +15952,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R111" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S111" s="19" t="str">
         <x:v>—</x:v>
@@ -15769,7 +16020,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R112" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S112" s="18" t="str">
         <x:v>—</x:v>
@@ -15837,7 +16088,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R113" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S113" s="19" t="str">
         <x:v>—</x:v>
@@ -15905,7 +16156,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R114" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S114" s="18" t="str">
         <x:v>—</x:v>
@@ -15973,7 +16224,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R115" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S115" s="19" t="str">
         <x:v>—</x:v>
@@ -16041,7 +16292,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R116" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S116" s="18" t="str">
         <x:v>—</x:v>
@@ -16109,7 +16360,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R117" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S117" s="19" t="str">
         <x:v>—</x:v>
@@ -16177,7 +16428,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R118" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S118" s="18" t="str">
         <x:v>—</x:v>
@@ -16245,7 +16496,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R119" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S119" s="19" t="str">
         <x:v>—</x:v>
@@ -16313,7 +16564,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R120" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S120" s="18" t="str">
         <x:v>—</x:v>
@@ -16381,7 +16632,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R121" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S121" s="19" t="str">
         <x:v>—</x:v>
@@ -16449,7 +16700,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R122" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S122" s="18" t="str">
         <x:v>—</x:v>
@@ -16517,7 +16768,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R123" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S123" s="19" t="str">
         <x:v>—</x:v>
@@ -16585,7 +16836,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R124" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S124" s="18" t="str">
         <x:v>—</x:v>
@@ -16653,7 +16904,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R125" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
       </x:c>
       <x:c r="S125" s="19" t="str">
         <x:v>—</x:v>
@@ -16689,7 +16940,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad04e8c4c964606"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c06891e25be4b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17000,7 +17251,7 @@
         <x:v>Rejouer une mutation après conflit seulement si elle reste valide.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="64" customHeight="1">
+    <x:row r="16" ht="77" customHeight="1">
       <x:c r="A16" s="12" t="str">
         <x:v>C11</x:v>
       </x:c>
@@ -17017,7 +17268,7 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
-        <x:v>D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
+        <x:v>Rapport v0.2 conservé : D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
       </x:c>
       <x:c r="G16" s="12" t="str">
         <x:v>Un départ explicite retire le membre ; le transfert de responsable ne révèle pas les autres perceptions.</x:v>
@@ -17358,7 +17609,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra060023856a64296"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35883761b6a46d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17528,7 +17779,7 @@
         <x:v>Relâcher, perdre le focus, masquer la page, fermer la radio ou ouvrir une modale coupe la transmission.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" ht="51" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>R04</x:v>
       </x:c>
@@ -17536,7 +17787,7 @@
         <x:v>Sortie propre</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Arrêter pistes, connexions et nœuds audio en quittant la salle.</x:v>
+        <x:v>Arrêter les pistes et connexions en quittant ; invalider aussi toute demande de microphone encore en attente.</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>Aucun micro utilisé après sortie.</x:v>
@@ -17548,10 +17799,10 @@
         <x:v>Quitter / déconnecter</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>Indicateur micro navigateur s’éteint et le pair voit la déconnexion.</x:v>
+        <x:v>Un flux qui arrive après fermeture est arrêté immédiatement, sans être affecté à la radio.</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>Le test de code n’atteste pas encore le matériel physique.</x:v>
+        <x:v>La boîte de permission du navigateur peut répondre plus tard ; la protection porte sur le traitement du résultat. Matériel physique non éprouvé.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="51" customHeight="1">
@@ -18071,7 +18322,7 @@
         <x:v>Deux puis quatre microphones physiques, plusieurs navigateurs.</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>12 tests radio et négociation partielle dans deux onglets ne constituent pas un essai de microphones physiques ou d’écoute de flux vocal.</x:v>
+        <x:v>19 tests radio et la négociation partielle de la v0.2 ne constituent pas un essai de microphones physiques ou d’écoute de flux vocal.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="40" customHeight="1">
@@ -18152,20 +18403,98 @@
         <x:v>Le test 1 / 2 / 3 est un autre appareil de preuve ; nommer le repère évite de comparer deux écrans différents.</x:v>
       </x:c>
     </x:row>
+    <x:row r="33" ht="40" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>R28</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Autorisation devenue obsolète</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>Éteindre le micro ou fermer la radio invalide la demande applicative encore en attente.</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>Si le navigateur fournit ensuite un flux, arrêter toutes ses pistes avant toute installation.</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>Désactiver / quitter pendant la permission</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str">
+        <x:v>Aucun flux tardif n’est conservé ni ajouté aux pairs ; les pistes sont effectivement stoppées.</x:v>
+      </x:c>
+      <x:c r="H33" s="11" t="str">
+        <x:v>La boîte système n’est pas prétendue annulée. Tests de promesses différées et de pistes simulées, matériel encore à vérifier.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="40" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>R29</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Réactivation récente</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Chaque activation possède un identifiant de demande ; seul le résultat de la demande courante peut être retenu.</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>Ancien succès ou ancien refus après une nouvelle activation : état récent préservé.</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Désactiver puis réactiver</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>L’ancienne réponse ne remplace pas le nouveau flux et ne réaffiche pas une erreur périmée.</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>Distinguer arrêt et simple mute : une piste muette doit aussi être arrêtée si sa demande est obsolète.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="40" customHeight="1">
+      <x:c r="A35" s="11" t="str">
+        <x:v>R30</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>Commande libérée</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>L’extinction invalide aussi l’opération en cours dans le contrôleur de l’interface.</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>La commande redevient disponible sans attendre la fin de l’ancienne permission.</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>Éteindre puis réactiver la radio</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str">
+        <x:v>Un ancien résultat ou finaliseur ne bloque ni ne déverrouille à tort la nouvelle opération.</x:v>
+      </x:c>
+      <x:c r="H35" s="11" t="str">
+        <x:v>Contrôleur testé séparément du client vocal ; ces tests ne sont pas un essai de permission sur microphone physique.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E32">
+  <x:conditionalFormatting sqref="E6:E35">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E32">
+    <x:dataValidation type="list" sqref="E6:E35">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fe229cd51ae43f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d358a9cbaef4e53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18816,7 +19145,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1c63dfd74794f13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red0cdd15c5124224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19036,7 +19365,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R914392a9ea5d43d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a7ae2a3476c4be6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19684,7 +20013,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe884bdf9c74482"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2424c44b8c9c40f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20328,7 +20657,7 @@
         <x:v>Hôtel : 196 580 triangles ; métro : 84 278 ; clinique : 107 032, effets cachés compris. Inspecteur articulé : 52 444 triangles. Six surfaces planaires, deux actives par lieu.</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>11 suites CPU réussies : données finies, normales, luminaires, 48 effets et raycasts, corps/reflets sans récursion, retard réel proche d’une seconde, traversée des trois lieux, relais, collision, qualité et nettoyage.</x:v>
+        <x:v>Preuves v0.2 conservées : 11 suites CPU réussies : données finies, normales, luminaires, 48 effets et raycasts, corps/reflets sans récursion, retard réel proche d’une seconde, traversée des trois lieux, relais, collision, qualité et nettoyage.</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
         <x:v>Contrôle structurel partiel</x:v>
@@ -20560,7 +20889,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebe31c88376f4dfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb908f5982fa1425a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/PARALLAXE_Design_Complet.xlsx
+++ b/docs/PARALLAXE_Design_Complet.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="Rd860a8f3c5fd43ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boucle" sheetId="2" r:id="R473a0ffd5eff42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomalies" sheetId="3" r:id="R3095c15dee364e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coopération" sheetId="4" r:id="R2332f36235c94e02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Radio" sheetId="5" r:id="Rc308d49f9a9a4280"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="6" r:id="Re871745b31d14919"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveaux" sheetId="7" r:id="R9413597ed0de4b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lieux" sheetId="8" r:id="R29bca919142a44ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direction artistique" sheetId="9" r:id="R658864451f604223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="10" r:id="R18e419a2df38430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commandes" sheetId="11" r:id="Rdc22a7b299c64b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narration" sheetId="12" r:id="R4300c79667974324"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="13" r:id="R64f150af41194520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="14" r:id="R4850e4e2055445f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="15" r:id="Red9d6b2d8fac4aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="R1c6fb86e3c09477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boucle" sheetId="2" r:id="Ref48f75986c94d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomalies" sheetId="3" r:id="Rfbcec1d28d9a454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coopération" sheetId="4" r:id="Rbd9f84bac3b34d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Radio" sheetId="5" r:id="R5401ecee9c09480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="6" r:id="Ra81be71aaa30411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Niveaux" sheetId="7" r:id="R1b2dad9349c24ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lieux" sheetId="8" r:id="R5f3eb6aa925044dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direction artistique" sheetId="9" r:id="Ra20e40da884340da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="10" r:id="R15011e39a4dd4ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commandes" sheetId="11" r:id="Rf0e1f8dce4b1401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narration" sheetId="12" r:id="R32cdfebe58334493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="13" r:id="R29c2d9b3631c4ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="14" r:id="R0182229f0fa548ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="15" r:id="R2328aed333f24698"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -713,8 +713,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="P9_Production" displayName="P9_Production" ref="A5:H61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H61"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="P9_Production" displayName="P9_Production" ref="A5:H72" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H72"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Priorité"/>
@@ -730,8 +730,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="P9_QA" displayName="P9_QA" ref="A5:H86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H86"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="P9_QA" displayName="P9_QA" ref="A5:H140" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H140"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Priorité"/>
@@ -747,8 +747,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="P9_References" displayName="P9_References" ref="A5:G34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="P9_References" displayName="P9_References" ref="A5:G49" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G49"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Type"/>
@@ -763,9 +763,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="P9_Anomalies" displayName="P9_Anomalies" ref="A5:V125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:V125"/>
-  <x:tableColumns count="22">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="P9_Anomalies" displayName="P9_Anomalies" ref="A5:W125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:W125"/>
+  <x:tableColumns count="23">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Anomalie"/>
     <x:tableColumn id="3" name="Famille"/>
@@ -788,14 +788,15 @@
     <x:tableColumn id="20" name="Terminus 09 (code)"/>
     <x:tableColumn id="21" name="Aile blanche (code)"/>
     <x:tableColumn id="22" name="Canal de preuve"/>
+    <x:tableColumn id="23" name="Chalet (code)"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="P9_Cooperation" displayName="P9_Cooperation" ref="A5:G30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="P9_Cooperation" displayName="P9_Cooperation" ref="A5:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G35"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Système"/>
@@ -810,8 +811,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="P9_Radio" displayName="P9_Radio" ref="A5:H35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="P9_Radio" displayName="P9_Radio" ref="A5:H45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H45"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Système / preuve"/>
@@ -827,8 +828,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="P9_Personnages" displayName="P9_Personnages" ref="A5:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="P9_Personnages" displayName="P9_Personnages" ref="A5:H34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H34"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Système / asset"/>
@@ -844,8 +845,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="P9_Niveaux" displayName="P9_Niveaux" ref="A5:J8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:J8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="P9_Niveaux" displayName="P9_Niveaux" ref="A5:J9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:J9"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Ordre"/>
     <x:tableColumn id="2" name="Lieu officiel"/>
@@ -863,8 +864,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="P9_Lieux" displayName="P9_Lieux" ref="A5:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="P9_Lieux" displayName="P9_Lieux" ref="A5:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:H33"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Lieu"/>
@@ -880,8 +881,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="P9_Directionartistique" displayName="P9_Directionartistique" ref="A5:G39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="P9_Directionartistique" displayName="P9_Directionartistique" ref="A5:G40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G40"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Élément"/>
@@ -896,8 +897,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="P9_Audio" displayName="P9_Audio" ref="A5:G22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:G22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="P9_Audio" displayName="P9_Audio" ref="A5:G25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:G25"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Usage"/>
@@ -1153,7 +1154,7 @@
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>Conception et suivi · édition 0.2.1 · 26 octobre 2026</x:v>
+        <x:v>Conception et suivi · édition 0.4.0 · 28 octobre 2026</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -1204,8 +1205,8 @@
         <x:v>Lots de production</x:v>
       </x:c>
       <x:c r="E7" s="34" t="n">
-        <x:f>COUNTA('Production'!$A$6:$A$61)</x:f>
-        <x:v>56</x:v>
+        <x:f>COUNTA('Production'!$A$6:$A$72)</x:f>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F7" s="3"/>
       <x:c r="G7" s="3"/>
@@ -1217,15 +1218,15 @@
       </x:c>
       <x:c r="B8" s="32" t="n">
         <x:f>COUNTIFS('Anomalies'!$D$6:$D$125,"Présent")</x:f>
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="3" t="str">
         <x:v>Lots en code ou présents</x:v>
       </x:c>
       <x:c r="E8" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$61,"Présent")+COUNTIFS('Production'!$E$6:$E$61,"Implémenté — QA partielle")</x:f>
-        <x:v>29</x:v>
+        <x:f>COUNTIFS('Production'!$E$6:$E$72,"Présent")+COUNTIFS('Production'!$E$6:$E$72,"Implémenté — QA partielle")</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F8" s="3"/>
       <x:c r="G8" s="3"/>
@@ -1237,15 +1238,15 @@
       </x:c>
       <x:c r="B9" s="32" t="n">
         <x:f>COUNTIFS('Anomalies'!$E$6:$E$125,"Conçu — non implémenté")</x:f>
-        <x:v>66</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="3"/>
       <x:c r="D9" s="3" t="str">
-        <x:v>Lots à vérifier / éprouver</x:v>
+        <x:v>Lots à compléter / éprouver</x:v>
       </x:c>
       <x:c r="E9" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$61,"À vérifier")+COUNTIFS('Production'!$E$6:$E$61,"À exécuter")+COUNTIFS('Production'!$E$6:$E$61,"À tester sur GPU")+COUNTIFS('Production'!$E$6:$E$61,"À tester sur appareils")</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIFS('Production'!$E$6:$E$72,"À vérifier")+COUNTIFS('Production'!$E$6:$E$72,"À exécuter")+COUNTIFS('Production'!$E$6:$E$72,"À tester sur GPU")+COUNTIFS('Production'!$E$6:$E$72,"À tester sur appareils")+COUNTIFS('Production'!$E$6:$E$72,"Partiel")</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="3"/>
       <x:c r="G9" s="3"/>
@@ -1264,8 +1265,8 @@
         <x:v>Lots futurs</x:v>
       </x:c>
       <x:c r="E10" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$E$6:$E$61,"Conçu — non implémenté")</x:f>
-        <x:v>17</x:v>
+        <x:f>COUNTIFS('Production'!$E$6:$E$72,"Conçu — non implémenté")</x:f>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F10" s="3"/>
       <x:c r="G10" s="3"/>
@@ -1277,15 +1278,15 @@
       </x:c>
       <x:c r="B11" s="32" t="n">
         <x:f>COUNTIFS('Anomalies'!$E$6:$E$125,"Implémenté — QA partielle")</x:f>
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C11" s="3"/>
       <x:c r="D11" s="3" t="str">
         <x:v>Priorités P0</x:v>
       </x:c>
       <x:c r="E11" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$B$6:$B$61,"P0")</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTIFS('Production'!$B$6:$B$72,"P0")</x:f>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F11" s="3"/>
       <x:c r="G11" s="3"/>
@@ -1304,8 +1305,8 @@
         <x:v>Priorités P1</x:v>
       </x:c>
       <x:c r="E12" s="34" t="n">
-        <x:f>COUNTIFS('Production'!$B$6:$B$61,"P1")</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTIFS('Production'!$B$6:$B$72,"P1")</x:f>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F12" s="3"/>
       <x:c r="G12" s="3"/>
@@ -1317,15 +1318,15 @@
       </x:c>
       <x:c r="B13" s="33" t="n">
         <x:f>B8/B7</x:f>
-        <x:v>0.45</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C13" s="3"/>
       <x:c r="D13" s="3" t="str">
         <x:v>Parcours QA documentés</x:v>
       </x:c>
       <x:c r="E13" s="34" t="n">
-        <x:f>COUNTA('QA'!$A$6:$A$86)</x:f>
-        <x:v>81</x:v>
+        <x:f>COUNTA('QA'!$A$6:$A$140)</x:f>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F13" s="3"/>
       <x:c r="G13" s="3"/>
@@ -1353,7 +1354,7 @@
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>Campagne</x:v>
+        <x:v>Lieux et campagne</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
         <x:v>Règle actuelle</x:v>
@@ -1392,7 +1393,7 @@
         <x:v>Lieux construits</x:v>
       </x:c>
       <x:c r="B18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="3"/>
       <x:c r="D18" s="3" t="str">
@@ -1407,7 +1408,7 @@
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
       <x:c r="A19" s="3" t="str">
-        <x:v>Validations par lieu</x:v>
+        <x:v>Par lieu de campagne</x:v>
       </x:c>
       <x:c r="B19" s="3" t="n">
         <x:v>3</x:v>
@@ -1425,7 +1426,7 @@
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
       <x:c r="A20" s="3" t="str">
-        <x:v>Validations pour sortir</x:v>
+        <x:v>Objectif de campagne</x:v>
       </x:c>
       <x:c r="B20" s="3" t="n">
         <x:v>9</x:v>
@@ -1519,7 +1520,7 @@
     </x:row>
     <x:row r="26" ht="31" customHeight="1">
       <x:c r="A26" s="37" t="str">
-        <x:v>Trois lieux : Saint-Clair, Terminus 09, Aile blanche. 54 anomalies en code ; 66 fiches supplémentaires conçues.</x:v>
+        <x:v>Quatre lieux : Saint-Clair, Terminus 09, Aile blanche et Chalet de service. 96 anomalies en code ; 24 fiches supplémentaires conçues.</x:v>
       </x:c>
       <x:c r="B26" s="37"/>
       <x:c r="C26" s="37"/>
@@ -1531,7 +1532,7 @@
     </x:row>
     <x:row r="27" ht="31" customHeight="1">
       <x:c r="A27" s="37" t="str">
-        <x:v>Campagne : trois validations par lieu avec paliers conservés, et une nouvelle référence à chaque lieu. Lieu unique : neuf validations consécutives.</x:v>
+        <x:v>Campagne : Saint-Clair → Terminus 09 → Aile blanche, trois validations par lieu et paliers conservés. Chalet en lieu unique uniquement : neuf validations consécutives.</x:v>
       </x:c>
       <x:c r="B27" s="37"/>
       <x:c r="C27" s="37"/>
@@ -1543,7 +1544,7 @@
     </x:row>
     <x:row r="28" ht="31" customHeight="1">
       <x:c r="A28" s="37" t="str">
-        <x:v>Correctif 0.2.1 : flux micro tardifs arrêtés après extinction / sortie ; réactivation récente préservée ; commande de radio débloquée sans attendre une ancienne permission.</x:v>
+        <x:v>0.4.0 : 15 fiches promues, soit 96 en code (84 visuelles, 12 radio). Chalet autonome, archives R9, galerie G9 et reflets enrichis ; correctifs de reprise et de configuration radio conservés.</x:v>
       </x:c>
       <x:c r="B28" s="37"/>
       <x:c r="C28" s="37"/>
@@ -1555,7 +1556,7 @@
     </x:row>
     <x:row r="29" ht="39" customHeight="1">
       <x:c r="A29" s="37" t="str">
-        <x:v>Correctif 0.2.1 : 19 tests radio, 4 du contrôleur UI, deux builds et test portable à deux clients HTTP réussis. Preuves v0.2 conservées : 17 règles, 11 suites CPU 3D et D1 quatre clients. GPU, microphones physiques, transport vocal et TURN réel restent non validés.</x:v>
+        <x:v>189 contrôles automatisés réussis ; builds local/hébergé et serveur portable sans node_modules vérifiés (chalet, quatre clients, neuf diagnostics). Route preview refusée ; GPU, microphones physiques et TURN réel restent non validés.</x:v>
       </x:c>
       <x:c r="B29" s="37"/>
       <x:c r="C29" s="37"/>
@@ -1756,7 +1757,7 @@
         <x:v>Règle de mixage ou de jeu</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="51" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>S01</x:v>
       </x:c>
@@ -1764,7 +1765,7 @@
         <x:v>Ambiance des lieux</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Souffle d’hôtel, résonance de station, ventilation clinique ; textures synthétiques originales.</x:v>
+        <x:v>Souffle d’hôtel, résonance de station, ventilation clinique et bois du chalet ; textures synthétiques originales.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
         <x:v>Ambiances procédurales par lieu</x:v>
@@ -1787,7 +1788,7 @@
         <x:v>Pas</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Cadence de marche et timbre adaptés aux matières des trois lieux.</x:v>
+        <x:v>Cadence de marche et timbre adaptés aux matières des quatre lieux.</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>Retour de locomotion procédural</x:v>
@@ -1917,7 +1918,7 @@
         <x:v>Les réglages exacts restent des choix de mix à auditer sur appareils. Voir feuille Radio.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" ht="51" customHeight="1">
       <x:c r="A13" s="11" t="str">
         <x:v>S08</x:v>
       </x:c>
@@ -1925,7 +1926,7 @@
         <x:v>Anomalies sonores</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>Six anomalies de réception radio et leur séquence d’étalonnage équivalente.</x:v>
+        <x:v>Douze profils de contrôle radio, dont dix modifient aussi la réception vocale locale ; relevés factuels accessibles.</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>Effets privés sur réception</x:v>
@@ -2032,7 +2033,7 @@
         <x:v>L’option ne doit pas supprimer les informations de diagnostic.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="40" customHeight="1">
+    <x:row r="18" ht="51" customHeight="1">
       <x:c r="A18" s="12" t="str">
         <x:v>S13</x:v>
       </x:c>
@@ -2040,7 +2041,7 @@
         <x:v>Étalonnage</x:v>
       </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>Trois sons courts connus, puis silence ; variante personnelle si anomalie radio.</x:v>
+        <x:v>Clic initial, identifiant RELAIS synthétique, trois étapes principales puis clic final ; variantes privées si anomalie radio.</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
         <x:v>Oscillateurs et bruit synthétique</x:v>
@@ -2147,20 +2148,89 @@
         <x:v>Le message système et le vrai roster demeurent fiables ; pas d’imitation d’un partenaire réel.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="40" customHeight="1">
+      <x:c r="A23" s="11" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>Identifiant du contrôle</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>Quatre chiffres encodés en doubles tonalités téléphoniques, puis séquence principale distincte.</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>Oscillateurs synthétiques originaux</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>Code écrit complet et sections nommées</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="str">
+        <x:v>Pas de parole synthétisée ni de donnée vocale personnelle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="40" customHeight="1">
+      <x:c r="A24" s="12" t="str">
+        <x:v>S19</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>Routage et queue</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="str">
+        <x:v>Centre normal ; variante gauche seule et réverbération longue.</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="str">
+        <x:v>WebAudio et relevé déterministe</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>Le relevé conserve la preuve en mono ou sans audition</x:v>
+      </x:c>
+      <x:c r="G24" s="12" t="str">
+        <x:v>L’écoute réelle et le confort de chaque profil demandent une recette matérielle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="40" customHeight="1">
+      <x:c r="A25" s="11" t="str">
+        <x:v>S20</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>Séquences élargies</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>Début / fin, ordre 1-3-2 et quatrième impulsion soufflée.</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>Ordonnanceur et souffle synthétique</x:v>
+      </x:c>
+      <x:c r="E25" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>Étalonnage répétable sans microphone</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str">
+        <x:v>Séparer la section d’identifiant des étapes principales pour éviter les erreurs de comptage.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E22">
+  <x:conditionalFormatting sqref="E6:E25">
     <x:cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E22">
+    <x:dataValidation type="list" sqref="E6:E25">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb869eebedf0b44f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc575646a231454a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2327,10 +2397,10 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>Désigner un repère au centre de la vue.</x:v>
+        <x:v>Désigner un repère, envoyer son ping, l’ajouter au carnet puis ouvrir sa lecture agrandie si elle existe.</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>Le nom de l’objet reste stable même si l’objet est invisible dans une perception.</x:v>
+        <x:v>Le ping ne transmet aucune valeur privée. Une lecture agrandie présente seulement l’état local du repère, sans verdict.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="40" customHeight="1">
@@ -2806,7 +2876,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R110b77c14b7242b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9fbf84857204f10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3314,7 +3384,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd05a49a6e2943b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67837c336fde4b57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3495,7 +3565,7 @@
         <x:v>Contenu</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Intégrer les 54 anomalies présentes au catalogue runtime 0.2.1.</x:v>
+        <x:v>Intégrer les 96 anomalies présentes au catalogue runtime 0.4.0.</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -3625,7 +3695,7 @@
         <x:v>QA visuelle</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>Inspecter toutes les anomalies et reflets dans les deux perceptions et les trois lieux.</x:v>
+        <x:v>Inspecter les 84 preuves visuelles et les reflets dans les perceptions pertinentes des quatre lieux.</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
         <x:v>À tester sur GPU</x:v>
@@ -3640,7 +3710,7 @@
         <x:v>Captures GPU réelles et résultat concordants avec le catalogue.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="64" customHeight="1">
+    <x:row r="15" ht="77" customHeight="1">
       <x:c r="A15" s="11" t="str">
         <x:v>P10</x:v>
       </x:c>
@@ -3663,10 +3733,10 @@
         <x:v>QA15–QA25, QA41–QA46</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>Rapport v0.2 conservé : D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="40" customHeight="1">
+        <x:v>19 tests de règles, 28 de résilience et vrai serveur HTTP portable réussis. Deux clients puis chalet à quatre clients, neuf diagnostics jusqu’à victoire, pings sans lecture privée. Linux / Node 24.22.1 ; aucune nouvelle campagne D1 hébergée ni partie humaine.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="51" customHeight="1">
       <x:c r="A16" s="12" t="str">
         <x:v>P11</x:v>
       </x:c>
@@ -3689,7 +3759,7 @@
         <x:v>C11</x:v>
       </x:c>
       <x:c r="H16" s="12" t="str">
-        <x:v>État et perception conservés ; vérification Internet et voix sur appareils encore nécessaire.</x:v>
+        <x:v>28/28 tests de résilience réussis : votes périmés, quorum, migrations, projections privées, epochs radio et nettoyage. Essais Internet et voix sur appareils restent ouverts.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="40" customHeight="1">
@@ -3833,19 +3903,19 @@
         <x:v>Relations</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>Produire douze anomalies nécessitant des témoignages complémentaires.</x:v>
+        <x:v>Registre, gant et météo privés ; photo d’équipe, plan, règlement et occupants. La constellation reste à produire.</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Partiel</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str">
         <x:v>Gameplay</x:v>
       </x:c>
       <x:c r="G22" s="12" t="str">
-        <x:v>Catalogue relationnel</x:v>
+        <x:v>PX-028,030,031,035,069,070,071,072</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str">
-        <x:v>Les joueurs ne peuvent pas répondre avec une seule capture isolée.</x:v>
+        <x:v>Sept cas intégrés et testés en CPU ; recettes GPU et constellation PX-035 restent ouvertes.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="40" customHeight="1">
@@ -3859,7 +3929,7 @@
         <x:v>Audio privé</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>Six transformations de réception et étalonnage accessible sans micro.</x:v>
+        <x:v>Douze profils de contrôle, avec transformations de réception selon le profil et étalonnage accessible sans micro.</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -3868,7 +3938,7 @@
         <x:v>Audio / gameplay</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>radio_echo à radio_aftertone</x:v>
+        <x:v>Douze profils radio ; R12–R17 et R31–R38</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str">
         <x:v>Relevé cohérent avec l’effet, sans dépendre d’une panne technique ni du silence d’un partenaire.</x:v>
@@ -4030,7 +4100,7 @@
         <x:v>Récompenses sans avantage révélant la vérité.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="40" customHeight="1">
+    <x:row r="30" ht="51" customHeight="1">
       <x:c r="A30" s="12" t="str">
         <x:v>P25</x:v>
       </x:c>
@@ -4041,10 +4111,10 @@
         <x:v>Chalet</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>Créer module industriel de chalet inspectable.</x:v>
+        <x:v>Chalet original : table, cheminée, hangar, collisions, ambiance et deux anomalies propres.</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F30" s="12" t="str">
         <x:v>Level design</x:v>
@@ -4053,7 +4123,7 @@
         <x:v>Z09</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Nouvelle baseline, parcours complet et catalogue propre.</x:v>
+        <x:v>Autonome à neuf validations ; 9 tests CPU réussis ; campagne des trois lieux conservée. Images et parcours sur appareils à vérifier.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -4290,7 +4360,7 @@
         <x:v>Un prototype jouable n’est pas une validation commerciale complète.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="64" customHeight="1">
+    <x:row r="40" ht="77" customHeight="1">
       <x:c r="A40" s="12" t="str">
         <x:v>P35</x:v>
       </x:c>
@@ -4301,7 +4371,7 @@
         <x:v>Export</x:v>
       </x:c>
       <x:c r="D40" s="12" t="str">
-        <x:v>Fournir source, édition autonome, instructions et Excel 0.2.1 synchronisé.</x:v>
+        <x:v>Fournir source, édition autonome, instructions et Excel 0.4.0 synchronisé.</x:v>
       </x:c>
       <x:c r="E40" s="13" t="str">
         <x:v>À vérifier</x:v>
@@ -4310,10 +4380,10 @@
         <x:v>Livraison</x:v>
       </x:c>
       <x:c r="G40" s="12" t="str">
-        <x:v>Version 0.2.1</x:v>
+        <x:v>Version 0.4.0</x:v>
       </x:c>
       <x:c r="H40" s="12" t="str">
-        <x:v>Builds local / hébergé et test portable à deux clients HTTP réussis. Classeur synchronisé. Intégrité des nouvelles archives et GitHub CI à vérifier après assemblage / publication ; rapport docs/qa-final-v0.2.1.json.</x:v>
+        <x:v>0.4.0 : TypeScript strict, builds local et hébergé réussis. Portable sans node_modules sous Linux / Node 24.22.1 : deux clients puis chalet à quatre, neuf diagnostics et victoire ; 12 contrôles de chemins. Pas d’essai natif Windows/macOS. Publication et CI 0.4.0 suivies séparément.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="40" customHeight="1">
@@ -4483,7 +4553,7 @@
         <x:v>Calibrations</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
-        <x:v>Vérifier les six formes sonores et leur relevé écrit.</x:v>
+        <x:v>Vérifier les douze profils radio intégrés, leurs séquences et leur relevé écrit.</x:v>
       </x:c>
       <x:c r="E47" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -4561,7 +4631,7 @@
         <x:v>Ambiances des lieux</x:v>
       </x:c>
       <x:c r="D50" s="12" t="str">
-        <x:v>Timbres de ventilation et pas propres aux trois lieux.</x:v>
+        <x:v>Timbres de ventilation et pas propres aux quatre lieux.</x:v>
       </x:c>
       <x:c r="E50" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -4717,7 +4787,7 @@
         <x:v>Concepts restants</x:v>
       </x:c>
       <x:c r="D56" s="12" t="str">
-        <x:v>Prioriser les 66 fiches encore conçues selon valeur de coopération et coût.</x:v>
+        <x:v>Prioriser les 24 fiches encore conçues selon valeur de coopération et coût.</x:v>
       </x:c>
       <x:c r="E56" s="13" t="str">
         <x:v>Conçu — non implémenté</x:v>
@@ -4810,7 +4880,7 @@
         <x:v>GLTFExporter puis GLTFLoader réussis ; matériaux de base et articulation rigide explicités. Visuel GPU restant.</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="64" customHeight="1">
+    <x:row r="60" ht="51" customHeight="1">
       <x:c r="A60" s="12" t="str">
         <x:v>P55</x:v>
       </x:c>
@@ -4833,10 +4903,10 @@
         <x:v>Radio R28–R29 ; QA77–QA79</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str">
-        <x:v>19/19 tests radio réussis, dont 7 nouveaux : extinction, micro seul, anciennes réponses, nouvelle demande et sortie. Avant correction : 6 échecs / 1 succès ; après : 7/7. Pistes et API simulées ; aucun microphone physique ni transmission mesurée.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="77" customHeight="1">
+        <x:v>Les sept scénarios de permission tardive 0.2.1 sont conservés dans les 32 tests radio réussis en 0.4.0. Pistes et API simulées ; aucun microphone physique ni transmission réelle mesurés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="51" customHeight="1">
       <x:c r="A61" s="11" t="str">
         <x:v>P56</x:v>
       </x:c>
@@ -4859,23 +4929,309 @@
         <x:v>Radio R30 ; QA80</x:v>
       </x:c>
       <x:c r="H61" s="11" t="str">
-        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
+        <x:v>4/4 tests du contrôleur radio réussis en 0.4.0 : attente libérée, réponses obsolètes ignorées, changement de client et geste utilisateur. API simulées ; aucun test DOM ou microphone physique.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="40" customHeight="1">
+      <x:c r="A62" s="12" t="str">
+        <x:v>P57</x:v>
+      </x:c>
+      <x:c r="B62" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C62" s="12" t="str">
+        <x:v>Calibrations élargies</x:v>
+      </x:c>
+      <x:c r="D62" s="12" t="str">
+        <x:v>Six nouvelles preuves : clic, contre-code, canal gauche, réverbération, ordre et quatrième impulsion.</x:v>
+      </x:c>
+      <x:c r="E62" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F62" s="12" t="str">
+        <x:v>Radio / WebAudio</x:v>
+      </x:c>
+      <x:c r="G62" s="12" t="str">
+        <x:v>PX-101–106</x:v>
+      </x:c>
+      <x:c r="H62" s="12" t="str">
+        <x:v>Signal généré et relevé décrivent la même anomalie ; preuve indépendante du transport et de la permission micro.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="40" customHeight="1">
+      <x:c r="A63" s="11" t="str">
+        <x:v>P58</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="str">
+        <x:v>Corps divergents</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="str">
+        <x:v>Badge absent, taille, main du talkie, regard et contact au sol.</x:v>
+      </x:c>
+      <x:c r="E63" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="str">
+        <x:v>Character / 3D</x:v>
+      </x:c>
+      <x:c r="G63" s="11" t="str">
+        <x:v>PX-107–111</x:v>
+      </x:c>
+      <x:c r="H63" s="11" t="str">
+        <x:v>Altération limitée au modèle désigné ; pose réseau, interface et collision partagées inchangées.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="40" customHeight="1">
+      <x:c r="A64" s="12" t="str">
+        <x:v>P59</x:v>
+      </x:c>
+      <x:c r="B64" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C64" s="12" t="str">
+        <x:v>Reflets divergents</x:v>
+      </x:c>
+      <x:c r="D64" s="12" t="str">
+        <x:v>Pose assise et code de badge contradictoire dans le reflet.</x:v>
+      </x:c>
+      <x:c r="E64" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F64" s="12" t="str">
+        <x:v>Rendu / animation</x:v>
+      </x:c>
+      <x:c r="G64" s="12" t="str">
+        <x:v>PX-112–113</x:v>
+      </x:c>
+      <x:c r="H64" s="12" t="str">
+        <x:v>Corps réel préservé ; indices visibles en miroir ; référence et nettoyage contrôlés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="40" customHeight="1">
+      <x:c r="A65" s="11" t="str">
+        <x:v>P60</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="str">
+        <x:v>Quai étendu</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="str">
+        <x:v>Archives ferroviaires, plan, compteur et horizon anormaux.</x:v>
+      </x:c>
+      <x:c r="E65" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="str">
+        <x:v>Level design / 3D</x:v>
+      </x:c>
+      <x:c r="G65" s="11" t="str">
+        <x:v>PX-114–117</x:v>
+      </x:c>
+      <x:c r="H65" s="11" t="str">
+        <x:v>Quai de référence vide ; nouvelles preuves lisibles depuis une zone sûre.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="40" customHeight="1">
+      <x:c r="A66" s="12" t="str">
+        <x:v>P61</x:v>
+      </x:c>
+      <x:c r="B66" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C66" s="12" t="str">
+        <x:v>Clinique étendue</x:v>
+      </x:c>
+      <x:c r="D66" s="12" t="str">
+        <x:v>Plaque de lit dupliquée, ombre occupée et gouttes ascendantes.</x:v>
+      </x:c>
+      <x:c r="E66" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F66" s="12" t="str">
+        <x:v>Level design / 3D</x:v>
+      </x:c>
+      <x:c r="G66" s="12" t="str">
+        <x:v>PX-118–120</x:v>
+      </x:c>
+      <x:c r="H66" s="12" t="str">
+        <x:v>Distinguer lits du couloir et de la salle vitrée ; aucun patient ni geste clinique réel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="40" customHeight="1">
+      <x:c r="A67" s="11" t="str">
+        <x:v>P62</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="str">
+        <x:v>Objets de contrôle</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="str">
+        <x:v>Bureau D2, consigne C9, sablier, vapeur et clé dupliquée.</x:v>
+      </x:c>
+      <x:c r="E67" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="str">
+        <x:v>Props / systèmes</x:v>
+      </x:c>
+      <x:c r="G67" s="11" t="str">
+        <x:v>PX-026,029,034,036,049,050,073</x:v>
+      </x:c>
+      <x:c r="H67" s="11" t="str">
+        <x:v>Quatre contradictions réellement privées ; mouvements inversés réels ; supports de référence inspectables.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="40" customHeight="1">
+      <x:c r="A68" s="12" t="str">
+        <x:v>P63</x:v>
+      </x:c>
+      <x:c r="B68" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C68" s="12" t="str">
+        <x:v>Recette extension</x:v>
+      </x:c>
+      <x:c r="D68" s="12" t="str">
+        <x:v>Recette visuelle des 27 ajouts historiques de 0.3.0, maintenus dans 0.4.0 : passage normal, reset, accès et vue témoin.</x:v>
+      </x:c>
+      <x:c r="E68" s="13" t="str">
+        <x:v>À tester sur GPU</x:v>
+      </x:c>
+      <x:c r="F68" s="12" t="str">
+        <x:v>QA / coopération</x:v>
+      </x:c>
+      <x:c r="G68" s="12" t="str">
+        <x:v>QA82–QA108</x:v>
+      </x:c>
+      <x:c r="H68" s="12" t="str">
+        <x:v>25 suites CPU de scène, 32 radio, 19 règles et 13 inspection réussies en 0.4.0. Rendus, mix et appareils restent ouverts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="40" customHeight="1">
+      <x:c r="A69" s="11" t="str">
+        <x:v>P64</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="str">
+        <x:v>Quinze ajouts 0.4.0</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="str">
+        <x:v>Intégrer les 15 fiches existantes : chalet, reflets, objets d’archives et phénomènes du couloir.</x:v>
+      </x:c>
+      <x:c r="E69" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="str">
+        <x:v>3D / inspection</x:v>
+      </x:c>
+      <x:c r="G69" s="11" t="str">
+        <x:v>QA115–QA129</x:v>
+      </x:c>
+      <x:c r="H69" s="11" t="str">
+        <x:v>96 entrées uniques au total ; normalité, vue privée et reset contrôlés ; capture GPU restante.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="40" customHeight="1">
+      <x:c r="A70" s="12" t="str">
+        <x:v>P65</x:v>
+      </x:c>
+      <x:c r="B70" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C70" s="12" t="str">
+        <x:v>Roster de référence</x:v>
+      </x:c>
+      <x:c r="D70" s="12" t="str">
+        <x:v>Stabiliser les archives pendant un changement de perspective solo ; actualiser les membres présents en coop.</x:v>
+      </x:c>
+      <x:c r="E70" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F70" s="12" t="str">
+        <x:v>Systèmes / inspection</x:v>
+      </x:c>
+      <x:c r="G70" s="12" t="str">
+        <x:v>QA130 ; C29</x:v>
+      </x:c>
+      <x:c r="H70" s="12" t="str">
+        <x:v>Un changement Alpha/Bêta ne crée aucune contradiction normale ; déconnexion et retour actualisent le nombre exact.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="40" customHeight="1">
+      <x:c r="A71" s="11" t="str">
+        <x:v>P66</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="str">
+        <x:v>Résilience et radio</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="str">
+        <x:v>Conserver les votes frais, projections privées, epochs radio et configuration STUN/TURN validée.</x:v>
+      </x:c>
+      <x:c r="E71" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="str">
+        <x:v>Réseau</x:v>
+      </x:c>
+      <x:c r="G71" s="11" t="str">
+        <x:v>QA133–QA134</x:v>
+      </x:c>
+      <x:c r="H71" s="11" t="str">
+        <x:v>28 tests de résilience et 59 de configuration réussis ; preuve réelle ICE/TURN sur appareils toujours distincte.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="77" customHeight="1">
+      <x:c r="A72" s="12" t="str">
+        <x:v>P67</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C72" s="12" t="str">
+        <x:v>Chalet à quatre clients</x:v>
+      </x:c>
+      <x:c r="D72" s="12" t="str">
+        <x:v>Parcourir les neuf diagnostics autonomes sur le serveur portable sans node_modules.</x:v>
+      </x:c>
+      <x:c r="E72" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F72" s="12" t="str">
+        <x:v>Livraison / QA</x:v>
+      </x:c>
+      <x:c r="G72" s="12" t="str">
+        <x:v>QA132 ; tests/portable.test.mjs</x:v>
+      </x:c>
+      <x:c r="H72" s="12" t="str">
+        <x:v>Réussi : serveur portable compilé sans node_modules, Linux / Node 24.22.1 ; quatre clients dans le chalet, neuf diagnostics et victoire, pings table/foyer sans fuite. Douze contrôles de chemins privés. docs/qa-portable-v0.4.0.json ; aucune fenêtre 3D ni partie humaine validée.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E61">
+  <x:conditionalFormatting sqref="E6:E72">
     <x:cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E61">
+    <x:dataValidation type="list" sqref="E6:E72">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cd1f55f13514701"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a5bfcb25cc2424b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4967,7 +5323,7 @@
         <x:v>Preuve / précision</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="51" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>QA01</x:v>
       </x:c>
@@ -4978,7 +5334,7 @@
         <x:v>Référence</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>Démarrer chacun des trois lieux, puis franchir un palier de campagne.</x:v>
+        <x:v>Démarrer chacun des quatre lieux en mode autonome, puis franchir un palier de la campagne des trois lieux.</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
         <x:v>Aucune anomalie ni point pendant chaque nouvelle référence.</x:v>
@@ -4990,7 +5346,7 @@
         <x:v>Solo et coop</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>Règles et rapport HTTP v0.2 : références propres et non notées dans les trois lieux. Inspection visuelle GPU encore ouverte.</x:v>
+        <x:v>19 tests de règles et scène CPU : références sans anomalie et sans point, quatre lieux autonomes ; campagne de trois lieux conservée. Images et parcours GPU ouverts.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="40" customHeight="1">
@@ -5068,7 +5424,7 @@
         <x:v>Toutes anomalies</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>11 suites CPU : 48 cas appliqués puis état de visibilité et matériaux restauré. Pas de validation des pixels ni d’artefacts de shader.</x:v>
+        <x:v>25 contrôles CPU de scène : 84 effets visuels appliqués puis restaurés. Géométrie et raycasting réels ; renderer et canvas simulés. Aucun pixel ni shader validé.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="51" customHeight="1">
@@ -5354,7 +5710,7 @@
         <x:v>Deux navigateurs</x:v>
       </x:c>
       <x:c r="H20" s="12" t="str">
-        <x:v>Rapport qa-network-v0.2.json : quatre vrais clients HTTP indépendants, trois arrivées concurrentes. Ne vaut pas quatre fenêtres 3D rendues.</x:v>
+        <x:v>0.4.0 : quatre clients HTTP indépendants rejoignent le chalet ; neuf diagnostics jusqu’à victoire. Le scénario n’utilise pas quatre fenêtres 3D rendues. docs/qa-portable-v0.4.0.json.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="51" customHeight="1">
@@ -5380,10 +5736,10 @@
         <x:v>Clients multiples</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str">
-        <x:v>Test D1 v0.2 : quatre membres uniques conservés et cinquième connexion refusée ; contrôles de capacité et autorisation réussis.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+        <x:v>Preuves précédentes conservées. Test D1 v0.2 : quatre membres uniques conservés et cinquième connexion refusée ; contrôles de capacité et autorisation réussis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="77" customHeight="1">
       <x:c r="A22" s="12" t="str">
         <x:v>QA17</x:v>
       </x:c>
@@ -5406,10 +5762,10 @@
         <x:v>DevTools / requêtes</x:v>
       </x:c>
       <x:c r="H22" s="12" t="str">
-        <x:v>Règles et HTTP v0.2 : projections privées avant chaque verdict, absence de seed/réponse et de perceptions d’autrui.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="40" customHeight="1">
+        <x:v>19 tests de règles, 28 de résilience et portable HTTP : projections privées, absence de résultat pendant inspection et aucune lecture privée incluse dans les pings table/foyer. Sources : tests/rules.test.mjs, tests/session-resilience.test.mjs, tests/portable.test.mjs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="51" customHeight="1">
       <x:c r="A23" s="11" t="str">
         <x:v>QA18</x:v>
       </x:c>
@@ -5432,10 +5788,10 @@
         <x:v>Requêtes contrôlées</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str">
-        <x:v>Tests de règles et D1 : jeton, plafond de salle et actions réservées au responsable contrôlés côté serveur.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="40" customHeight="1">
+        <x:v>Preuves précédentes conservées. Tests de règles et D1 : jeton, plafond de salle et actions réservées au responsable contrôlés côté serveur.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="51" customHeight="1">
       <x:c r="A24" s="12" t="str">
         <x:v>QA19</x:v>
       </x:c>
@@ -5458,10 +5814,10 @@
         <x:v>Deux clients</x:v>
       </x:c>
       <x:c r="H24" s="12" t="str">
-        <x:v>Test de domaine : désaccord maintient le tour ouvert ; modification du vote possible jusqu’à unanimité.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="40" customHeight="1">
+        <x:v>Preuves précédentes conservées. Test de domaine : désaccord maintient le tour ouvert ; modification du vote possible jusqu’à unanimité.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="51" customHeight="1">
       <x:c r="A25" s="11" t="str">
         <x:v>QA20</x:v>
       </x:c>
@@ -5484,7 +5840,7 @@
         <x:v>Deux clients</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>Tests de domaine et neuf consensus HTTP concurrents : un seul résultat partagé et un seul point par résolution.</x:v>
+        <x:v>Règles : désaccord, vote révisable et résolution unique. Portable 0.4.0 : neuf consensus à quatre clients produisent exactement les neuf points du chalet. Contrôles HTTP, sans rendu GPU.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="40" customHeight="1">
@@ -5510,10 +5866,10 @@
         <x:v>Test automatisé</x:v>
       </x:c>
       <x:c r="H26" s="12" t="str">
-        <x:v>Rapport D1 v0.2 : neuf tours de consensus concurrents terminent la campagne sans double comptage.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="51" customHeight="1">
+        <x:v>Preuves précédentes conservées. Rapport D1 v0.2 : neuf tours de consensus concurrents terminent la campagne sans double comptage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>QA22</x:v>
       </x:c>
@@ -5536,7 +5892,7 @@
         <x:v>Règles et interfaces</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str">
-        <x:v>Tests des règles : victoire en lieu unique et campagne. HTTP : campagne de neuf réussites. Écrans 3D et parcours matériel restent à éprouver.</x:v>
+        <x:v>Règles 0.4.0 : campagne et lieu autonome. Portable courant : chalet à quatre clients jusqu’à neuf diagnostics et victoire. Campagne D1 v0.2 historique ; écrans et jeu humain restent à éprouver.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="51" customHeight="1">
@@ -5562,7 +5918,7 @@
         <x:v>Standard et détendu</x:v>
       </x:c>
       <x:c r="H28" s="12" t="str">
-        <x:v>Test de règles : erreur après le palier hôtel conserve 3 et le métro courant ; remise à zéro en lieu unique. Tous les parcours UI de frontière restent ouverts.</x:v>
+        <x:v>Preuves précédentes conservées. Test de règles : erreur après le palier hôtel conserve 3 et le métro courant ; remise à zéro en lieu unique. Tous les parcours UI de frontière restent ouverts.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="51" customHeight="1">
@@ -5588,10 +5944,10 @@
         <x:v>Règles et UI</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>Tests de règles : troisième erreur standard termine ; détendu reste jouable au-delà. Présentation matérielle du bilan non validée ici.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="51" customHeight="1">
+        <x:v>Preuves précédentes conservées. Tests de règles : troisième erreur standard termine ; détendu reste jouable au-delà. Présentation matérielle du bilan non validée ici.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="12" t="str">
         <x:v>QA25</x:v>
       </x:c>
@@ -5614,7 +5970,7 @@
         <x:v>Deux et quatre clients</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Tests v0.2 : témoin absent suspend le verdict et départ nettoie les votes ; HTTP leave révoque le jeton. Essais Internet prolongés encore ouverts.</x:v>
+        <x:v>28/28 tests de résilience réussis : votes périmés, quorum, migrations, projections privées, epochs radio et nettoyage. Essais Internet et voix sur appareils restent ouverts. Source : tests/session-resilience.test.mjs.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -5695,7 +6051,7 @@
         <x:v>L’action finale doit être confirmée par le serveur.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="40" customHeight="1">
+    <x:row r="34" ht="51" customHeight="1">
       <x:c r="A34" s="12" t="str">
         <x:v>QA29</x:v>
       </x:c>
@@ -5718,7 +6074,7 @@
         <x:v>Test automatisé</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str">
-        <x:v>Test de règles : mêmes seeds/configurations produisent les mêmes tours, avec passages conformes et anormaux.</x:v>
+        <x:v>Preuves précédentes conservées. Test de règles : mêmes seeds/configurations produisent les mêmes tours, avec passages conformes et anormaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="40" customHeight="1">
@@ -5761,7 +6117,7 @@
         <x:v>Couper le son et le micro ; résoudre chaque type radio à l’aide du relevé.</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
-        <x:v>Les six tests restent interprétables et les autres preuves accessibles.</x:v>
+        <x:v>Les douze contrôles restent interprétables et les autres preuves accessibles.</x:v>
       </x:c>
       <x:c r="F36" s="13" t="str">
         <x:v>Partiel</x:v>
@@ -5877,7 +6233,7 @@
         <x:v>Aucun statut 60 FPS validé sans mesure.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="51" customHeight="1">
+    <x:row r="41" ht="77" customHeight="1">
       <x:c r="A41" s="11" t="str">
         <x:v>QA36</x:v>
       </x:c>
@@ -5891,7 +6247,7 @@
         <x:v>Contrôler IDs, couverture runtime, compteurs, statuts, tableaux et rendu.</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>120 fiches ; 54 en code ; 66 futures ; 15 feuilles ; 80 parcours QA.</x:v>
+        <x:v>120 fiches ; 96 en code ; 24 futures ; 15 feuilles ; 135 parcours QA.</x:v>
       </x:c>
       <x:c r="F41" s="13" t="str">
         <x:v>Réussi</x:v>
@@ -5900,7 +6256,7 @@
         <x:v>Artifact Tool / XLSX</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>Générateur v0.2.1 : 120 IDs uniques, 54 runtime, 66 prévus ; versions cohérentes, compteurs et pools recalculés, modifications temporaires restaurées et feuilles touchées rendues.</x:v>
+        <x:v>Générateur 0.4.0 : 120 IDs conservés dans leur ordre, 96 présents et 24 prévus ; 15 feuilles et 135 parcours QA. Compteurs, quatre pools et modifications temporaires (statut, présence, chalet) recalculés et restaurés ; rendu examiné. docs/workbook-validation.json.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="40" customHeight="1">
@@ -6007,7 +6363,7 @@
         <x:v>La première livraison ne porte pas le statut jeu commercial terminé.</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="40" customHeight="1">
+    <x:row r="46" ht="51" customHeight="1">
       <x:c r="A46" s="12" t="str">
         <x:v>QA41</x:v>
       </x:c>
@@ -6030,10 +6386,10 @@
         <x:v>Règles / HTTP coop</x:v>
       </x:c>
       <x:c r="H46" s="12" t="str">
-        <x:v>Tests de domaine et D1 v0.2 : hôtel → métro après trois bonnes décisions, référence propre et synchronisée avant l’inspection.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="40" customHeight="1">
+        <x:v>Preuves précédentes conservées. Tests de domaine et D1 v0.2 : hôtel → métro après trois bonnes décisions, référence propre et synchronisée avant l’inspection.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="51" customHeight="1">
       <x:c r="A47" s="11" t="str">
         <x:v>QA42</x:v>
       </x:c>
@@ -6056,7 +6412,7 @@
         <x:v>Règles / HTTP coop</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str">
-        <x:v>Tests de domaine et D1 v0.2 : métro → clinique au palier 6, référence propre et remise à zéro du secteur courant.</x:v>
+        <x:v>Preuves précédentes conservées. Tests de domaine et D1 v0.2 : métro → clinique au palier 6, référence propre et remise à zéro du secteur courant.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="51" customHeight="1">
@@ -6082,10 +6438,10 @@
         <x:v>Catalog / règles</x:v>
       </x:c>
       <x:c r="H48" s="12" t="str">
-        <x:v>Test de couverture : 54 entrées uniques et toutes observées sur 900 seeds, deux à quatre joueurs et trois niveaux ; chaque tirage appartient au pool du lieu.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="40" customHeight="1">
+        <x:v>19 tests de règles réussis en 0.4.0 : 96 IDs uniques et tirages compatibles avec les quatre lieux ; perceptions privées et campagne de trois lieux conservées. tests/rules.test.mjs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="51" customHeight="1">
       <x:c r="A49" s="11" t="str">
         <x:v>QA44</x:v>
       </x:c>
@@ -6108,7 +6464,7 @@
         <x:v>Tests de domaine</x:v>
       </x:c>
       <x:c r="H49" s="11" t="str">
-        <x:v>Test de règles : sauvegarde v0.1 migrée vers single hotel sans perdre la série ; données malformées rejetées.</x:v>
+        <x:v>Preuves précédentes conservées. Test de règles : sauvegarde v0.1 migrée vers single hotel sans perdre la série ; données malformées rejetées.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="51" customHeight="1">
@@ -6134,10 +6490,10 @@
         <x:v>Tests de session / HTTP</x:v>
       </x:c>
       <x:c r="H50" s="12" t="str">
-        <x:v>Tests radio et D1 : expéditeur autorisé, destinataire privé, epochs périmées rejetées, accusés protégés et configuration ICE authentifiée.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="51" customHeight="1">
+        <x:v>28 tests de résilience et 59 de configuration : destinataire privé, epochs périmées rejetées, accusés protégés, identifiants temporaires et secrets validés. Pas de transport réel démontré.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
       <x:c r="A51" s="11" t="str">
         <x:v>QA46</x:v>
       </x:c>
@@ -6160,10 +6516,10 @@
         <x:v>HTTP réel</x:v>
       </x:c>
       <x:c r="H51" s="11" t="str">
-        <x:v>Campagne quatre clients HTTP traversée avec lieux/références synchronisés ; mode unique couvert dans les règles. Vérification graphique multi-appareils restante.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="64" customHeight="1">
+        <x:v>0.4.0 : règles de campagne des trois lieux conservées ; chalet autonome validé par neuf diagnostics à quatre clients HTTP. La campagne D1 v0.2 demeure historique ; nouveau parcours graphique multi-appareils restant.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="51" customHeight="1">
       <x:c r="A52" s="12" t="str">
         <x:v>QA47</x:v>
       </x:c>
@@ -6186,7 +6542,7 @@
         <x:v>Chrome / Firefox / Safari</x:v>
       </x:c>
       <x:c r="H52" s="12" t="str">
-        <x:v>19 tests radio réussis avec doubles de périphériques : permission explicite, démarrage muet et arrêt des flux reçus après invalidation. Aucun microphone physique ni indicateur matériel observé.</x:v>
+        <x:v>32 tests radio : consentement explicite, démarrage muet et rejet des flux tardifs vérifiés avec doubles de périphériques. Aucun microphone physique ni indicateur matériel observé.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="51" customHeight="1">
@@ -6238,7 +6594,7 @@
         <x:v>Deux navigateurs physiques</x:v>
       </x:c>
       <x:c r="H54" s="12" t="str">
-        <x:v>Deux onglets réels : activation de l’écoute sans prompt microphone et calibration écrite réussies. Offre/réponse présentes et négociation stable, mais zéro candidat ICE ; aucun flux audio connecté.</x:v>
+        <x:v>Historique v0.2 : deux onglets ont activé l’écoute et la calibration sans prompt micro ; SDP présent mais zéro candidat ICE. Ce résultat ne constitue pas une liaison audio et n’a pas été remesuré en 0.4.0.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="40" customHeight="1">
@@ -6290,7 +6646,7 @@
         <x:v>Navigateurs / certificats</x:v>
       </x:c>
       <x:c r="H56" s="12" t="str">
-        <x:v>19 tests radio incluent une origine LAN non sécurisée : indisponibilité technique annoncée, aucun prompt micro ni altération de preuve. Certificat LAN réel non testé.</x:v>
+        <x:v>Suite radio 32/32 : origine LAN non sécurisée annoncée sans prompt micro ni modification de la preuve. Aucun certificat LAN réel ni transport vocal validé.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="40" customHeight="1">
@@ -6330,7 +6686,7 @@
         <x:v>Radio 1–2–3</x:v>
       </x:c>
       <x:c r="D58" s="12" t="str">
-        <x:v>Étalonner avec effet absent puis chacun des six IDs radio.</x:v>
+        <x:v>Étalonner avec effet absent puis chacun des douze IDs radio.</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
         <x:v>Trace écrite et signal synthétique correspondent au contrat de chaque variante.</x:v>
@@ -6342,7 +6698,7 @@
         <x:v>Code / WebAudio / écoute humaine</x:v>
       </x:c>
       <x:c r="H58" s="12" t="str">
-        <x:v>Tests radio : les six profils ont des preuves locales déterministes et relevés distincts. L’écoute réelle de chaque signal synthétique reste nécessaire.</x:v>
+        <x:v>Les douze profils produisent des formes d’onde PCM distinctes et bornées et des relevés accessibles. Fréquences, code, clic final, canaux et queues analysés numériquement. Écoute humaine restante.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="51" customHeight="1">
@@ -6382,7 +6738,7 @@
         <x:v>Reset audio</x:v>
       </x:c>
       <x:c r="D60" s="12" t="str">
-        <x:v>Alterner les six effets puis un tour normal et quitter.</x:v>
+        <x:v>Alterner les douze profils puis un tour normal et quitter.</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
         <x:v>Pas de delay, bruit, modulation ou porteuse résiduelle ; nœuds libérés.</x:v>
@@ -6394,7 +6750,7 @@
         <x:v>WebAudio et inspection code</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str">
-        <x:v>Correctif v0.2.1 : les demandes micro invalidées ne peuvent plus installer un flux tardif ; les pistes reçues sont arrêtées. Nettoyage vérifié avec doubles de périphériques. Queues sonores et matériel restent à écouter.</x:v>
+        <x:v>Suite radio 32/32 : arrêt/remplacement/profil/référence/dispose annulent les sources de calibration ; ancienne reprise AudioContext ne relance pas un test retiré. Pistes micro tardives toujours arrêtées. Matériel restant.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="51" customHeight="1">
@@ -6446,10 +6802,10 @@
         <x:v>Capture vidéo réelle</x:v>
       </x:c>
       <x:c r="H62" s="12" t="str">
-        <x:v>11e suite CPU : retard du corps réfléchi proche d’une seconde et parcours des trois lieux réussis. Retard perçu et lisibilité du mouvement restent à capturer sur GPU réel.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="51" customHeight="1">
+        <x:v>25 contrôles CPU conservent le retard corporel proche d’une seconde et la traversée des quatre lieux. Retard perçu, pixels et lisibilité restent à capturer sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="40" customHeight="1">
       <x:c r="A63" s="11" t="str">
         <x:v>QA58</x:v>
       </x:c>
@@ -6472,7 +6828,7 @@
         <x:v>Capture vidéo réelle</x:v>
       </x:c>
       <x:c r="H63" s="11" t="str">
-        <x:v>Geste autonome intégré et effet inclus dans les 48 cas appliqués/reset. Comparaison visuelle de la main et du corps encore à enregistrer.</x:v>
+        <x:v>Geste autonome intégré parmi 84 effets visuels appliqués/reset. Comparaison visuelle de la main et du corps encore à enregistrer.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="40" customHeight="1">
@@ -6524,7 +6880,7 @@
         <x:v>GPU desktop et mobile</x:v>
       </x:c>
       <x:c r="H65" s="11" t="str">
-        <x:v>Six surfaces planaires, deux actives par lieu ; pass sans récursion contrôlé en CPU. Exactitude visuelle, transparence et coût GPU non mesurés.</x:v>
+        <x:v>Huit surfaces planaires, deux par lieu ; passe sans récursion contrôlée en CPU. Exactitude visuelle, transparence et coût GPU non mesurés.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="40" customHeight="1">
@@ -6862,7 +7218,7 @@
         <x:v>Règles / HTTP / GPU</x:v>
       </x:c>
       <x:c r="H78" s="12" t="str">
-        <x:v>Test de couverture des 54 IDs : paired_arrow et paired_clock distribuent deux valeurs privées distinctes sans effets révélateurs. Lecture des panneaux sur GPU restante.</x:v>
+        <x:v>19 tests de règles couvrent 96 IDs : paired_arrow et paired_clock distribuent deux valeurs privées distinctes sans effet révélateur. Lecture sur GPU restante.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="51" customHeight="1">
@@ -6888,7 +7244,7 @@
         <x:v>Trois lieux et profils</x:v>
       </x:c>
       <x:c r="H79" s="11" t="str">
-        <x:v>Les huit cas font partie des 48 effets visuels appliqués/reset et repères raycast en CPU. Leur apparence finale sur écran n’est pas certifiée.</x:v>
+        <x:v>Les huit ajouts historiques font partie des 84 effets visuels contrôlés/reset en CPU. Leur apparence finale sur écran reste à vérifier.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="64" customHeight="1">
@@ -6914,10 +7270,10 @@
         <x:v>GLB original / CPU</x:v>
       </x:c>
       <x:c r="H80" s="12" t="str">
-        <x:v>GLTFExporter → GLTFLoader réussi : 52 444 triangles, 51 meshes, 12 nœuds articulés, trois clips et sommets finis. Manifeste public/models/inspecteur-parallaxe.manifest.json ; aucun rendu GPU certifié.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="64" customHeight="1">
+        <x:v>GLB 0.3.0 conservé : source et empreinte inchangées, en-tête vérifié en 0.4.0. 53 990 triangles, 58 maillages, 12 articulations et 3 clips selon manifeste ; relecture GLTFLoader historique. Aucun GPU. docs/qa-final-v0.4.0.json.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="51" customHeight="1">
       <x:c r="A81" s="11" t="str">
         <x:v>QA76</x:v>
       </x:c>
@@ -6940,7 +7296,7 @@
         <x:v>Deux onglets réels</x:v>
       </x:c>
       <x:c r="H81" s="11" t="str">
-        <x:v>Deux onglets réels : salon, écoute sans permission micro, calibration écrite et échange offre/réponse réussis ; négociation stable. ICE terminé avec zéro candidat local/distant : liaison audio non établie. Aucun flux vocal ni micro physique validé.</x:v>
+        <x:v>Aucun nouvel essai vocal connecté en 0.4.0 : terminal.local:4173 a refusé la connexion. Les anciennes négociations SDP sans candidat ICE restent historiques, sans nouvelle mesure.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="64" customHeight="1">
@@ -7021,7 +7377,7 @@
         <x:v>Quatre tests réussis : ancien accord, ancien refus, ancienne finalisation et ancien échec d’écoute ne remplacent ni ne coupent le flux / la demande / l’écoute récents. Nouvel état PTT préservé et demande courante non dupliquée. API simulées.</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="77" customHeight="1">
+    <x:row r="85" ht="64" customHeight="1">
       <x:c r="A85" s="11" t="str">
         <x:v>QA80</x:v>
       </x:c>
@@ -7044,7 +7400,7 @@
         <x:v>Tests du contrôleur UI</x:v>
       </x:c>
       <x:c r="H85" s="11" t="str">
-        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
+        <x:v>4/4 tests du contrôleur radio réussis en 0.4.0 : attente libérée, réponses obsolètes ignorées, changement de client et geste utilisateur. API simulées ; aucun test DOM ou microphone physique.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="77" customHeight="1">
@@ -7058,10 +7414,10 @@
         <x:v>Builds et édition portable</x:v>
       </x:c>
       <x:c r="D86" s="12" t="str">
-        <x:v>Compiler les éditions locale et hébergée ; lancer le serveur portable compilé avec deux clients HTTP, sans node_modules.</x:v>
+        <x:v>Compiler les éditions locale et hébergée ; lancer le serveur portable sans node_modules, scénario à deux clients puis chalet à quatre clients HTTP.</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
-        <x:v>HTML servi ; modules serveur privés ; références et consensus justes ; départ des deux membres.</x:v>
+        <x:v>HTML et assets servis ; modules privés bloqués ; neuf diagnostics corrects du chalet mènent à la victoire ; tous les membres quittent.</x:v>
       </x:c>
       <x:c r="F86" s="13" t="str">
         <x:v>Réussi</x:v>
@@ -7070,23 +7426,1427 @@
         <x:v>Build / HTTP portable</x:v>
       </x:c>
       <x:c r="H86" s="12" t="str">
-        <x:v>v0.2.1 : typecheck, build local, build hébergé et test portable réussis. Deux clients HTTP authentifiés : référence, inspection, perceptions privées, unanimité et sortie ; serveur compilé lancé sans node_modules. Les archives finales et GitHub CI restent à contrôler après assemblage / publication.</x:v>
+        <x:v>0.4.0 : TypeScript strict, builds local et hébergé réussis. Portable sans node_modules sous Linux / Node 24.22.1 : deux clients puis chalet à quatre, neuf diagnostics et victoire ; 12 contrôles de chemins. Pas d’essai natif Windows/macOS. Publication et CI 0.4.0 suivies séparément.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64" customHeight="1">
+      <x:c r="A87" s="11" t="str">
+        <x:v>QA82</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="str">
+        <x:v>Le clic qui manque</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="str">
+        <x:v>Lancer deux calibrations normales puis affectées ; comparer clic initial, section RELAIS et clic final.</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="str">
+        <x:v>L’absence reproductible d’un clic de référence constitue une anomalie légère.</x:v>
+      </x:c>
+      <x:c r="F87" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G87" s="11" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H87" s="11" t="str">
+        <x:v>radio_no_squelch. 32 tests radio réussis : PCM de production, relevé déterministe, routage et cycle de vie. Les API navigateur sont simulées. Aucune écoute humaine, aucun microphone physique, aucune nouvelle liaison ICE/TURN validés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
+      <x:c r="A88" s="12" t="str">
+        <x:v>QA83</x:v>
+      </x:c>
+      <x:c r="B88" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C88" s="12" t="str">
+        <x:v>Les chiffres au mauvais endroit</x:v>
+      </x:c>
+      <x:c r="D88" s="12" t="str">
+        <x:v>Fixer un RELAIS connu ; comparer chaque chiffre du panneau et du relevé, puis changer de passage et répéter.</x:v>
+      </x:c>
+      <x:c r="E88" s="12" t="str">
+        <x:v>La contradiction appareil / panneau confirme même si personne ne parle.</x:v>
+      </x:c>
+      <x:c r="F88" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G88" s="12" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H88" s="12" t="str">
+        <x:v>radio_countercode. 32 tests radio : le vrai signal DTMF change de chiffre, le panneau de référence demeure intact ; le relevé reste disponible sans micro ni réseau. Calibration seule : aucune réécriture de paroles humaines. Écoute matérielle restante.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
+      <x:c r="A89" s="11" t="str">
+        <x:v>QA84</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="str">
+        <x:v>Le canal de gauche</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="str">
+        <x:v>Comparer la répartition de sortie et le relevé en stéréo ; répéter sans écoute audio.</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
+        <x:v>Le routage fictionnel unilatéral décrit par le relevé est la preuve.</x:v>
+      </x:c>
+      <x:c r="F89" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G89" s="11" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H89" s="11" t="str">
+        <x:v>radio_left_only. 32 tests radio réussis : PCM de production, relevé déterministe, routage et cycle de vie. Les API navigateur sont simulées. Aucune écoute humaine, aucun microphone physique, aucune nouvelle liaison ICE/TURN validés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="64" customHeight="1">
+      <x:c r="A90" s="12" t="str">
+        <x:v>QA85</x:v>
+      </x:c>
+      <x:c r="B90" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C90" s="12" t="str">
+        <x:v>La réverbération impossible</x:v>
+      </x:c>
+      <x:c r="D90" s="12" t="str">
+        <x:v>Mesurer la queue du signal normal puis affecté, sans entrée microphone et sans pair parlant.</x:v>
+      </x:c>
+      <x:c r="E90" s="12" t="str">
+        <x:v>Une réverbération synthétique anormalement longue confirme.</x:v>
+      </x:c>
+      <x:c r="F90" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G90" s="12" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H90" s="12" t="str">
+        <x:v>radio_wrong_room. 32 tests radio réussis : PCM de production, relevé déterministe, routage et cycle de vie. Les API navigateur sont simulées. Aucune écoute humaine, aucun microphone physique, aucune nouvelle liaison ICE/TURN validés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="64" customHeight="1">
+      <x:c r="A91" s="11" t="str">
+        <x:v>QA86</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="str">
+        <x:v>Le deuxième vient après</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="str">
+        <x:v>Distinguer l’identifiant DTMF et les trois étapes principales ; vérifier ordre et nombre de celles-ci.</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="str">
+        <x:v>L’ordre contradictoire stable constitue la preuve.</x:v>
+      </x:c>
+      <x:c r="F91" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G91" s="11" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H91" s="11" t="str">
+        <x:v>radio_order_swap. 32 tests radio : fréquences réelles des étapes 2 et 3 inversées, trois étapes conservées, identifiant RELAIS séparé. Calibration seule, sans réécriture de paroles humaines. Écoute matérielle restante.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="64" customHeight="1">
+      <x:c r="A92" s="12" t="str">
+        <x:v>QA87</x:v>
+      </x:c>
+      <x:c r="B92" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C92" s="12" t="str">
+        <x:v>La quatrième respiration</x:v>
+      </x:c>
+      <x:c r="D92" s="12" t="str">
+        <x:v>Écouter / lire toute la fin du test après le clic de clôture ; compter la séquence principale.</x:v>
+      </x:c>
+      <x:c r="E92" s="12" t="str">
+        <x:v>Une quatrième impulsion tardive, également décrite dans le relevé, confirme.</x:v>
+      </x:c>
+      <x:c r="F92" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G92" s="12" t="str">
+        <x:v>WebAudio simulé + écoute matérielle</x:v>
+      </x:c>
+      <x:c r="H92" s="12" t="str">
+        <x:v>radio_pulse_inside. 32 tests radio réussis : PCM de production, relevé déterministe, routage et cycle de vie. Les API navigateur sont simulées. Aucune écoute humaine, aucun microphone physique, aucune nouvelle liaison ICE/TURN validés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="51" customHeight="1">
+      <x:c r="A93" s="11" t="str">
+        <x:v>QA88</x:v>
+      </x:c>
+      <x:c r="B93" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C93" s="11" t="str">
+        <x:v>Le badge absent</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="str">
+        <x:v>Identifier le pair ciblé puis inspecter sa plaque ; comparer une vue témoin et le roster.</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="str">
+        <x:v>Une plaque de modèle vide alors que le badge normal est connu confirme.</x:v>
+      </x:c>
+      <x:c r="F93" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G93" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H93" s="11" t="str">
+        <x:v>Fiche PX-107 · avatar_badge_missing 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="51" customHeight="1">
+      <x:c r="A94" s="12" t="str">
+        <x:v>QA89</x:v>
+      </x:c>
+      <x:c r="B94" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C94" s="12" t="str">
+        <x:v>Le collègue trop grand</x:v>
+      </x:c>
+      <x:c r="D94" s="12" t="str">
+        <x:v>Arrêter le pair près d’une porte ; comparer hauteur apparente, pose autoritaire et collision.</x:v>
+      </x:c>
+      <x:c r="E94" s="12" t="str">
+        <x:v>Un changement d’échelle local confirmé par repère fixe est anormal.</x:v>
+      </x:c>
+      <x:c r="F94" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G94" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H94" s="12" t="str">
+        <x:v>Fiche PX-108 · avatar_height_offset 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="51" customHeight="1">
+      <x:c r="A95" s="11" t="str">
+        <x:v>QA90</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C95" s="11" t="str">
+        <x:v>La mauvaise main</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="str">
+        <x:v>Sans micro ni PTT, regarder le talkie abaissé de face, de dos et dans le miroir.</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="str">
+        <x:v>Une inversion persistante entre le corps attendu et sa perception confirme.</x:v>
+      </x:c>
+      <x:c r="F95" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G95" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H95" s="11" t="str">
+        <x:v>Fiche PX-109 · avatar_hands_swap 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="51" customHeight="1">
+      <x:c r="A96" s="12" t="str">
+        <x:v>QA91</x:v>
+      </x:c>
+      <x:c r="B96" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C96" s="12" t="str">
+        <x:v>Le regard sous la visière</x:v>
+      </x:c>
+      <x:c r="D96" s="12" t="str">
+        <x:v>Tourner la tête du pair et déplacer l’observateur ; comparer direction des yeux et de la visière.</x:v>
+      </x:c>
+      <x:c r="E96" s="12" t="str">
+        <x:v>Un regard autonome dans une seule perception confirme.</x:v>
+      </x:c>
+      <x:c r="F96" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G96" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H96" s="12" t="str">
+        <x:v>Fiche PX-110 · avatar_visor_watch 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="51" customHeight="1">
+      <x:c r="A97" s="11" t="str">
+        <x:v>QA92</x:v>
+      </x:c>
+      <x:c r="B97" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C97" s="11" t="str">
+        <x:v>Les pas au-dessus du sol</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="str">
+        <x:v>Faire marcher puis arrêter le pair sur sol plan ; comparer semelles, joints et coordonnées réseau.</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="str">
+        <x:v>La hauteur locale anormale avec pose réseau stable confirme.</x:v>
+      </x:c>
+      <x:c r="F97" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G97" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H97" s="11" t="str">
+        <x:v>Fiche PX-111 · avatar_no_contact 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="51" customHeight="1">
+      <x:c r="A98" s="12" t="str">
+        <x:v>QA93</x:v>
+      </x:c>
+      <x:c r="B98" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C98" s="12" t="str">
+        <x:v>La posture restée assise</x:v>
+      </x:c>
+      <x:c r="D98" s="12" t="str">
+        <x:v>Se tenir debout au miroir, changer d’orientation puis restaurer la référence.</x:v>
+      </x:c>
+      <x:c r="E98" s="12" t="str">
+        <x:v>Une posture autonome clairement différente confirme.</x:v>
+      </x:c>
+      <x:c r="F98" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G98" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H98" s="12" t="str">
+        <x:v>Fiche PX-112 · reflection_seated 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="64" customHeight="1">
+      <x:c r="A99" s="11" t="str">
+        <x:v>QA94</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>L’identité derrière le verre</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="str">
+        <x:v>Lire le badge physique, le roster et le badge réfléchi du même inspecteur.</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="str">
+        <x:v>Une identité inversée seulement dans le reflet constitue la preuve.</x:v>
+      </x:c>
+      <x:c r="F99" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G99" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H99" s="11" t="str">
+        <x:v>Fiche PX-113 · reflection_badge_code 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="51" customHeight="1">
+      <x:c r="A100" s="12" t="str">
+        <x:v>QA95</x:v>
+      </x:c>
+      <x:c r="B100" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C100" s="12" t="str">
+        <x:v>La minute annoncée deux fois</x:v>
+      </x:c>
+      <x:c r="D100" s="12" t="str">
+        <x:v>Lire les deux lignes statiques d’archives ; noter rame, direction et minute sans attendre une rotation de page.</x:v>
+      </x:c>
+      <x:c r="E100" s="12" t="str">
+        <x:v>Deux lignes incompatibles pour un même identifiant de train confirment.</x:v>
+      </x:c>
+      <x:c r="F100" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G100" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H100" s="12" t="str">
+        <x:v>Fiche PX-114 · metro_timetable_loop 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="51" customHeight="1">
+      <x:c r="A101" s="11" t="str">
+        <x:v>QA96</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="str">
+        <x:v>La station ajoutée</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="str">
+        <x:v>Lire les stations du plan dans l’ordre depuis un même embranchement.</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="str">
+        <x:v>Une station ajoutée au même emplacement confirme.</x:v>
+      </x:c>
+      <x:c r="F101" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G101" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H101" s="11" t="str">
+        <x:v>Fiche PX-115 · metro_route_poster 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="51" customHeight="1">
+      <x:c r="A102" s="12" t="str">
+        <x:v>QA97</x:v>
+      </x:c>
+      <x:c r="B102" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C102" s="12" t="str">
+        <x:v>Le quai qui compte seul</x:v>
+      </x:c>
+      <x:c r="D102" s="12" t="str">
+        <x:v>Lire le portique SCELLÉ sur deux instants séparés de plus de 2,4 s ; aucun franchissement requis ; roster inchangé.</x:v>
+      </x:c>
+      <x:c r="E102" s="12" t="str">
+        <x:v>Une augmentation sans passage réel confirme.</x:v>
+      </x:c>
+      <x:c r="F102" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G102" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H102" s="12" t="str">
+        <x:v>Fiche PX-116 · metro_platform_count 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="64" customHeight="1">
+      <x:c r="A103" s="11" t="str">
+        <x:v>QA98</x:v>
+      </x:c>
+      <x:c r="B103" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C103" s="11" t="str">
+        <x:v>Le matin sous terre</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="str">
+        <x:v>Comparer le fond du tunnel depuis le quai ; vérifier que le passage physique reste inaccessible.</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="str">
+        <x:v>L’extérieur diurne incompatible avec la référence confirme.</x:v>
+      </x:c>
+      <x:c r="F103" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G103" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H103" s="11" t="str">
+        <x:v>Fiche PX-117 · metro_tunnel_daylight 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="51" customHeight="1">
+      <x:c r="A104" s="12" t="str">
+        <x:v>QA99</x:v>
+      </x:c>
+      <x:c r="B104" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C104" s="12" t="str">
+        <x:v>Le nom sur deux lits</x:v>
+      </x:c>
+      <x:c r="D104" s="12" t="str">
+        <x:v>Lire plaque09 au couloir et plaque10 dans la salle vitrée ; appliquer puis retirer la duplication.</x:v>
+      </x:c>
+      <x:c r="E104" s="12" t="str">
+        <x:v>La duplication du code 09 sur deux lits de référence distincts confirme.</x:v>
+      </x:c>
+      <x:c r="F104" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G104" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H104" s="12" t="str">
+        <x:v>Fiche PX-118 · clinic_tag_echo 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="51" customHeight="1">
+      <x:c r="A105" s="11" t="str">
+        <x:v>QA100</x:v>
+      </x:c>
+      <x:c r="B105" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C105" s="11" t="str">
+        <x:v>L’occupant de l’ombre</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="str">
+        <x:v>Observer lit vide et ombre, puis déplacer un vrai collègue pour écarter la confusion de silhouette.</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="str">
+        <x:v>Un occupant absent du lit mais visible dans son ombre confirme.</x:v>
+      </x:c>
+      <x:c r="F105" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G105" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H105" s="11" t="str">
+        <x:v>Fiche PX-119 · clinic_shadow_bed 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="51" customHeight="1">
+      <x:c r="A106" s="12" t="str">
+        <x:v>QA101</x:v>
+      </x:c>
+      <x:c r="B106" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C106" s="12" t="str">
+        <x:v>La goutte qui remonte</x:v>
+      </x:c>
+      <x:c r="D106" s="12" t="str">
+        <x:v>Suivre au moins trois gouttes de démonstration en référence puis en perception affectée.</x:v>
+      </x:c>
+      <x:c r="E106" s="12" t="str">
+        <x:v>Le mouvement inverse local est la preuve.</x:v>
+      </x:c>
+      <x:c r="F106" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G106" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H106" s="12" t="str">
+        <x:v>Fiche PX-120 · clinic_iv_reverse 25 contrôles CPU : géométrie, transformations, reset et repère inspectable. Renderer et canvas simulés ; pixels, lisibilité et confort à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="51" customHeight="1">
+      <x:c r="A107" s="11" t="str">
+        <x:v>QA102</x:v>
+      </x:c>
+      <x:c r="B107" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C107" s="11" t="str">
+        <x:v>Deux chambres raisonnables</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="str">
+        <x:v>Comparer BUREAU D2 à deux vues sur plusieurs passages ; contrôler que 204 et205 sont permis en normal.</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="str">
+        <x:v>Deux assignations plausibles mais différentes sur le même appareil confirment l’anomalie.</x:v>
+      </x:c>
+      <x:c r="F107" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G107" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H107" s="11" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="51" customHeight="1">
+      <x:c r="A108" s="12" t="str">
+        <x:v>QA103</x:v>
+      </x:c>
+      <x:c r="B108" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C108" s="12" t="str">
+        <x:v>La valise jumelle</x:v>
+      </x:c>
+      <x:c r="D108" s="12" t="str">
+        <x:v>Lire formes, côtés et étiquettes09/18 de C9 ; vérifier aussi le chariot distinct à une seule valise.</x:v>
+      </x:c>
+      <x:c r="E108" s="12" t="str">
+        <x:v>Le même identifiant unique est associé à deux positions différentes selon les témoins.</x:v>
+      </x:c>
+      <x:c r="F108" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G108" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H108" s="12" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="51" customHeight="1">
+      <x:c r="A109" s="11" t="str">
+        <x:v>QA104</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="str">
+        <x:v>L’autorisation refusée</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="str">
+        <x:v>Comparer DOSSIER09 à deux vues ; vérifier que VALIDÉ et REFUSÉ peuvent être des valeurs normales.</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="str">
+        <x:v>Deux décisions opposées et stables sur le même dossier constituent la preuve.</x:v>
+      </x:c>
+      <x:c r="F109" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G109" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H109" s="11" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="51" customHeight="1">
+      <x:c r="A110" s="12" t="str">
+        <x:v>QA105</x:v>
+      </x:c>
+      <x:c r="B110" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C110" s="12" t="str">
+        <x:v>Deux lendemains</x:v>
+      </x:c>
+      <x:c r="D110" s="12" t="str">
+        <x:v>Comparer date complète de l’édition au même passage ; ne pas utiliser la date de l’ordinateur.</x:v>
+      </x:c>
+      <x:c r="E110" s="12" t="str">
+        <x:v>Deux dates d’édition différentes au même emplacement confirment l’anomalie.</x:v>
+      </x:c>
+      <x:c r="F110" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G110" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H110" s="12" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="51" customHeight="1">
+      <x:c r="A111" s="11" t="str">
+        <x:v>QA106</x:v>
+      </x:c>
+      <x:c r="B111" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="str">
+        <x:v>Le sablier inversé</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="str">
+        <x:v>Observer la direction sur plusieurs instants puis restaurer la référence.</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="str">
+        <x:v>Mouvement contraire à la gravité.</x:v>
+      </x:c>
+      <x:c r="F111" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G111" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H111" s="11" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="51" customHeight="1">
+      <x:c r="A112" s="12" t="str">
+        <x:v>QA107</x:v>
+      </x:c>
+      <x:c r="B112" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C112" s="12" t="str">
+        <x:v>La vapeur lourde</x:v>
+      </x:c>
+      <x:c r="D112" s="12" t="str">
+        <x:v>Observer les volutes à deux niveaux de qualité et comparer leur direction dans les deux vues.</x:v>
+      </x:c>
+      <x:c r="E112" s="12" t="str">
+        <x:v>La vapeur descendante confirme.</x:v>
+      </x:c>
+      <x:c r="F112" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G112" s="12" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H112" s="12" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="51" customHeight="1">
+      <x:c r="A113" s="11" t="str">
+        <x:v>QA108</x:v>
+      </x:c>
+      <x:c r="B113" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C113" s="11" t="str">
+        <x:v>La clé en double</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="str">
+        <x:v>Compter les clés09, passer en anomalie puis revenir en référence sans ramassage.</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="str">
+        <x:v>La duplication d’un identifiant unique confirme.</x:v>
+      </x:c>
+      <x:c r="F113" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G113" s="11" t="str">
+        <x:v>CPU / rendu GPU / coopération</x:v>
+      </x:c>
+      <x:c r="H113" s="11" t="str">
+        <x:v>19 tests de règles, 13 d’inspection et 25 contrôles de scène CPU : valeurs privées, lectures actuelles et repères des quatorze postes hôtel contrôlés. Images et lisibilité GPU à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="51" customHeight="1">
+      <x:c r="A114" s="12" t="str">
+        <x:v>QA109</x:v>
+      </x:c>
+      <x:c r="B114" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C114" s="12" t="str">
+        <x:v>Témoins privés élargis</x:v>
+      </x:c>
+      <x:c r="D114" s="12" t="str">
+        <x:v>Échantillonner les nouvelles contradictions à deux, trois et quatre clients, dans chacun de leurs lieux autorisés.</x:v>
+      </x:c>
+      <x:c r="E114" s="12" t="str">
+        <x:v>Au moins un observateur de référence ; valeurs communes en passage conforme ; aucune vérité globale exposée.</x:v>
+      </x:c>
+      <x:c r="F114" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G114" s="12" t="str">
+        <x:v>Règles / HTTP</x:v>
+      </x:c>
+      <x:c r="H114" s="12" t="str">
+        <x:v>19 tests de règles couvrent 96 effets, valeurs privées et vue normale, de deux à quatre observateurs. Tests HTTP et vues graphiques suivis séparément.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="51" customHeight="1">
+      <x:c r="A115" s="11" t="str">
+        <x:v>QA110</x:v>
+      </x:c>
+      <x:c r="B115" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C115" s="11" t="str">
+        <x:v>Changement d’inspecteur</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="str">
+        <x:v>Faire quitter et revenir le collègue désigné pendant une distorsion de corps ; changer ensuite de lieu.</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="str">
+        <x:v>Cible déterministe, roster exact, absence de corps fantôme et nettoyage complet.</x:v>
+      </x:c>
+      <x:c r="F115" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G115" s="11" t="str">
+        <x:v>CPU / réseau / GPU</x:v>
+      </x:c>
+      <x:c r="H115" s="11" t="str">
+        <x:v>25 contrôles CPU vérifient nettoyage des pairs, cible corporelle et identité stable ; 28 tests de résilience vérifient absence et reprise. Rendu prolongé multi-appareils restant.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="64" customHeight="1">
+      <x:c r="A116" s="12" t="str">
+        <x:v>QA111</x:v>
+      </x:c>
+      <x:c r="B116" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C116" s="12" t="str">
+        <x:v>Lecture sans diagnostic</x:v>
+      </x:c>
+      <x:c r="D116" s="12" t="str">
+        <x:v>Lire un repère 3D puis son agrandissement depuis deux perceptions privées.</x:v>
+      </x:c>
+      <x:c r="E116" s="12" t="str">
+        <x:v>Valeurs identiques dans décor et panneau local ; aucune réponse de vote révélée.</x:v>
+      </x:c>
+      <x:c r="F116" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G116" s="12" t="str">
+        <x:v>Interface / GPU</x:v>
+      </x:c>
+      <x:c r="H116" s="12" t="str">
+        <x:v>13 tests d’inspection et contrôles de scène : lecture conditionnée à l’objet et à sa perception, sans verdict. E conserve ping et carnet ; aucune lecture privée dans le ping. DOM/GPU restant.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="51" customHeight="1">
+      <x:c r="A117" s="11" t="str">
+        <x:v>QA112</x:v>
+      </x:c>
+      <x:c r="B117" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C117" s="11" t="str">
+        <x:v>Accès à la recette navigateur</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="str">
+        <x:v>Ouvrir l’URL exacte de prévisualisation retournée par le service.</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="str">
+        <x:v>Une session rendue permet les captures et vérifications de la version.</x:v>
+      </x:c>
+      <x:c r="F117" s="13" t="str">
+        <x:v>Bloqué</x:v>
+      </x:c>
+      <x:c r="G117" s="11" t="str">
+        <x:v>Navigateur géré</x:v>
+      </x:c>
+      <x:c r="H117" s="11" t="str">
+        <x:v>0.4.0 : la route terminal.local:4173 a refusé la connexion. Aucun contrôle GPU, audio natif ou microphone exécuté ; aucun résultat matériel présumé.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="40" customHeight="1">
+      <x:c r="A118" s="12" t="str">
+        <x:v>QA113</x:v>
+      </x:c>
+      <x:c r="B118" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C118" s="12" t="str">
+        <x:v>Inspecteurs homonymes</x:v>
+      </x:c>
+      <x:c r="D118" s="12" t="str">
+        <x:v>Connecter deux inspecteurs portant le même pseudonyme, avec des identifiants et slots distincts.</x:v>
+      </x:c>
+      <x:c r="E118" s="12" t="str">
+        <x:v>La lecture de badge suit l’identité stable de la cible et ne récupère pas le badge du premier homonyme.</x:v>
+      </x:c>
+      <x:c r="F118" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G118" s="12" t="str">
+        <x:v>Régression CPU / inspection</x:v>
+      </x:c>
+      <x:c r="H118" s="12" t="str">
+        <x:v>tests/scene.geometry.test.mjs : identité stable, données et lectures contrôlées. Glyphes et lisibilité GPU encore ouverts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="64" customHeight="1">
+      <x:c r="A119" s="11" t="str">
+        <x:v>QA114</x:v>
+      </x:c>
+      <x:c r="B119" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C119" s="11" t="str">
+        <x:v>Chemins privés du serveur</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="str">
+        <x:v>Demander les variantes encodées des chemins de modules, puis les assets publics et un fichier factice hors racine.</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="str">
+        <x:v>Variantes encodées de chemins privés refusées ; assets publics conservés ; hors-racine interdit.</x:v>
+      </x:c>
+      <x:c r="F119" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G119" s="11" t="str">
+        <x:v>HTTP réel / Linux ; version Node indiquée dans le rapport</x:v>
+      </x:c>
+      <x:c r="H119" s="11" t="str">
+        <x:v>0.4.0 : 12 requêtes HTTP de protection passent (GET, HEAD, encodages, séparateurs, casse, hors-racine) ; HTML et assets JS/CSS publics conservés. Linux / Node 24.22.1, sans node_modules. docs/qa-portable-v0.4.0.json.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="51" customHeight="1">
+      <x:c r="A120" s="12" t="str">
+        <x:v>QA115</x:v>
+      </x:c>
+      <x:c r="B120" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C120" s="12" t="str">
+        <x:v>Table du chalet</x:v>
+      </x:c>
+      <x:c r="D120" s="12" t="str">
+        <x:v>Comparer le plateau normal et affecté depuis le garde-corps, puis rétablir la référence.</x:v>
+      </x:c>
+      <x:c r="E120" s="12" t="str">
+        <x:v>Le plateau normal mesure 2,10 × 1,40 m ; le bord gauche atteint le mur dans la vue affectée, sans changer le trajet, la tasse ou le carnet.</x:v>
+      </x:c>
+      <x:c r="F120" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G120" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H120" s="12" t="str">
+        <x:v>cabine_table_size ; tests/cabin.geometry.test.mjs ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="51" customHeight="1">
+      <x:c r="A121" s="11" t="str">
+        <x:v>QA116</x:v>
+      </x:c>
+      <x:c r="B121" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C121" s="11" t="str">
+        <x:v>Cheminée du chalet</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="str">
+        <x:v>Observer depuis le tapis le conduit normal, affecté et restauré.</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="str">
+        <x:v>Foyer vide et froid en référence ; visage et yeux immobiles dans la vue affectée seulement.</x:v>
+      </x:c>
+      <x:c r="F121" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G121" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H121" s="11" t="str">
+        <x:v>cabine_chimney_face ; tests/cabin.geometry.test.mjs ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="51" customHeight="1">
+      <x:c r="A122" s="12" t="str">
+        <x:v>QA117</x:v>
+      </x:c>
+      <x:c r="B122" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C122" s="12" t="str">
+        <x:v>Porte du reflet</x:v>
+      </x:c>
+      <x:c r="D122" s="12" t="str">
+        <x:v>Comparer le miroir de Saint-Clair au panneau réel, puis restaurer la référence.</x:v>
+      </x:c>
+      <x:c r="E122" s="12" t="str">
+        <x:v>La porte supplémentaire existe uniquement dans la passe du miroir concerné ; aucune porte réelle ni collision commune ajoutée.</x:v>
+      </x:c>
+      <x:c r="F122" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G122" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H122" s="12" t="str">
+        <x:v>mirror_extra_door ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="51" customHeight="1">
+      <x:c r="A123" s="11" t="str">
+        <x:v>QA118</x:v>
+      </x:c>
+      <x:c r="B123" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C123" s="11" t="str">
+        <x:v>Groupe absent</x:v>
+      </x:c>
+      <x:c r="D123" s="11" t="str">
+        <x:v>Comparer corps et reflet avec pairs, puis les deux témoins en solo ; essayer les quatre lieux.</x:v>
+      </x:c>
+      <x:c r="E123" s="11" t="str">
+        <x:v>Le corps local reste réfléchi ; seuls les collègues/témoins disparaissent du miroir affecté ; leur corps réel reste présent.</x:v>
+      </x:c>
+      <x:c r="F123" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G123" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H123" s="11" t="str">
+        <x:v>reflection_no_team ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="51" customHeight="1">
+      <x:c r="A124" s="12" t="str">
+        <x:v>QA119</x:v>
+      </x:c>
+      <x:c r="B124" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C124" s="12" t="str">
+        <x:v>Racines sous 901</x:v>
+      </x:c>
+      <x:c r="D124" s="12" t="str">
+        <x:v>Observer un cycle de croissance sous 901, passer à la vue normale puis à la référence.</x:v>
+      </x:c>
+      <x:c r="E124" s="12" t="str">
+        <x:v>Racines locales au seuil 901, animation mesurable et reset ; axe de marche toujours accessible.</x:v>
+      </x:c>
+      <x:c r="F124" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G124" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H124" s="12" t="str">
+        <x:v>root_under_door ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="51" customHeight="1">
+      <x:c r="A125" s="11" t="str">
+        <x:v>QA120</x:v>
+      </x:c>
+      <x:c r="B125" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C125" s="11" t="str">
+        <x:v>Eau ascendante</x:v>
+      </x:c>
+      <x:c r="D125" s="11" t="str">
+        <x:v>Suivre une goutte du panneau droit, comparer les perceptions puis restaurer.</x:v>
+      </x:c>
+      <x:c r="E125" s="11" t="str">
+        <x:v>La goutte monte ; le panneau témoin et la référence restent secs.</x:v>
+      </x:c>
+      <x:c r="F125" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G125" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H125" s="11" t="str">
+        <x:v>water_up_wall ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="51" customHeight="1">
+      <x:c r="A126" s="12" t="str">
+        <x:v>QA121</x:v>
+      </x:c>
+      <x:c r="B126" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C126" s="12" t="str">
+        <x:v>Cinquième chambre</x:v>
+      </x:c>
+      <x:c r="D126" s="12" t="str">
+        <x:v>Compter 901–904 depuis l’entrée puis observer le panneau droit près de la sortie.</x:v>
+      </x:c>
+      <x:c r="E126" s="12" t="str">
+        <x:v>905 apparaît seulement dans la vue affectée ; les quatre portes et collisions communes restent stables.</x:v>
+      </x:c>
+      <x:c r="F126" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G126" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H126" s="12" t="str">
+        <x:v>extra_door ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="51" customHeight="1">
+      <x:c r="A127" s="11" t="str">
+        <x:v>QA122</x:v>
+      </x:c>
+      <x:c r="B127" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C127" s="11" t="str">
+        <x:v>Issue animée</x:v>
+      </x:c>
+      <x:c r="D127" s="11" t="str">
+        <x:v>Observer un cycle du joint, vérifier la stabilité témoin et l’accès au vote.</x:v>
+      </x:c>
+      <x:c r="E127" s="11" t="str">
+        <x:v>Animation du battant et du joint locale ; terminal accessible ; référence immobile.</x:v>
+      </x:c>
+      <x:c r="F127" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G127" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H127" s="11" t="str">
+        <x:v>exit_breath ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="64" customHeight="1">
+      <x:c r="A128" s="12" t="str">
+        <x:v>QA123</x:v>
+      </x:c>
+      <x:c r="B128" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C128" s="12" t="str">
+        <x:v>Registre R9</x:v>
+      </x:c>
+      <x:c r="D128" s="12" t="str">
+        <x:v>Comparer ARRIVÉE 03:09 / LIGNE 09 entre vues, avec pseudonymes identiques puis différents.</x:v>
+      </x:c>
+      <x:c r="E128" s="12" t="str">
+        <x:v>Indicatifs stables distinguent les homonymes ; noms des membres présents ou témoin fictif explicitement étiqueté en solo, hors décompte réel ; une identité isolée ne suffit pas.</x:v>
+      </x:c>
+      <x:c r="F128" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G128" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H128" s="12" t="str">
+        <x:v>paired_guestbook ; tests/inspection.test.mjs ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="51" customHeight="1">
+      <x:c r="A129" s="11" t="str">
+        <x:v>QA124</x:v>
+      </x:c>
+      <x:c r="B129" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C129" s="11" t="str">
+        <x:v>Gant C9</x:v>
+      </x:c>
+      <x:c r="D129" s="11" t="str">
+        <x:v>Depuis ICI, poignet vers soi, comparer les pouces des deux perceptions puis les variantes normales.</x:v>
+      </x:c>
+      <x:c r="E129" s="11" t="str">
+        <x:v>Chaque latéralité est normale seule ; seule la contradiction est anormale ; le pouce géométrique et la lecture E concordent.</x:v>
+      </x:c>
+      <x:c r="F129" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G129" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H129" s="11" t="str">
+        <x:v>paired_hand ; tests/inspection.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="51" customHeight="1">
+      <x:c r="A130" s="12" t="str">
+        <x:v>QA125</x:v>
+      </x:c>
+      <x:c r="B130" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C130" s="12" t="str">
+        <x:v>Météo G9</x:v>
+      </x:c>
+      <x:c r="D130" s="12" t="str">
+        <x:v>Comparer les trois météos normales puis une paire contradictoire, avec lecture E.</x:v>
+      </x:c>
+      <x:c r="E130" s="12" t="str">
+        <x:v>Pluie/parapluie, neige/flocons ou soleil/rayons sont visibles ; égalité dans les vues normales et différence privée.</x:v>
+      </x:c>
+      <x:c r="F130" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G130" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H130" s="12" t="str">
+        <x:v>paired_photo_weather ; tests/inspection.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="51" customHeight="1">
+      <x:c r="A131" s="11" t="str">
+        <x:v>QA126</x:v>
+      </x:c>
+      <x:c r="B131" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C131" s="11" t="str">
+        <x:v>Équipe de nuit G9</x:v>
+      </x:c>
+      <x:c r="D131" s="11" t="str">
+        <x:v>Lire la référence puis la variante affectée ; faire partir et revenir un membre.</x:v>
+      </x:c>
+      <x:c r="E131" s="11" t="str">
+        <x:v>Trois signatures fictives en référence ; pseudonymes et silhouettes suivent les présents dans la vue affectée.</x:v>
+      </x:c>
+      <x:c r="F131" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G131" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H131" s="11" t="str">
+        <x:v>wrong_team_photo ; tests/inspection.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="51" customHeight="1">
+      <x:c r="A132" s="12" t="str">
+        <x:v>QA127</x:v>
+      </x:c>
+      <x:c r="B132" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C132" s="12" t="str">
+        <x:v>Plan G9</x:v>
+      </x:c>
+      <x:c r="D132" s="12" t="str">
+        <x:v>Lire les quatre chambres puis comparer le plan affecté à la porte physique 903.</x:v>
+      </x:c>
+      <x:c r="E132" s="12" t="str">
+        <x:v>Case 903 et branche absentes uniquement du plan affecté ; position et numéro de la porte réelle inchangés.</x:v>
+      </x:c>
+      <x:c r="F132" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G132" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H132" s="12" t="str">
+        <x:v>map_missing_room ; tests/inspection.test.mjs ; tests/scene.geometry.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="51" customHeight="1">
+      <x:c r="A133" s="11" t="str">
+        <x:v>QA128</x:v>
+      </x:c>
+      <x:c r="B133" s="11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C133" s="11" t="str">
+        <x:v>Règlement R9</x:v>
+      </x:c>
+      <x:c r="D133" s="11" t="str">
+        <x:v>Comparer la phrase du panneau et les règles permanentes de l’interface.</x:v>
+      </x:c>
+      <x:c r="E133" s="11" t="str">
+        <x:v>NE SIGNALEZ AUCUNE ANOMALIE reste une preuve du décor ; le vrai vote n’est pas modifié.</x:v>
+      </x:c>
+      <x:c r="F133" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G133" s="11" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H133" s="11" t="str">
+        <x:v>rules_swap ; tests/inspection.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="51" customHeight="1">
+      <x:c r="A134" s="12" t="str">
+        <x:v>QA129</x:v>
+      </x:c>
+      <x:c r="B134" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C134" s="12" t="str">
+        <x:v>Présence R9</x:v>
+      </x:c>
+      <x:c r="D134" s="12" t="str">
+        <x:v>Comparer afficheur et membres présents, y compris départ/retour et entraînement solo.</x:v>
+      </x:c>
+      <x:c r="E134" s="12" t="str">
+        <x:v>Nombre exact en référence ; +1 dans la seule vue affectée ; faux témoin du registre exclu du décompte.</x:v>
+      </x:c>
+      <x:c r="F134" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G134" s="12" t="str">
+        <x:v>CPU / inspection / GPU restant</x:v>
+      </x:c>
+      <x:c r="H134" s="12" t="str">
+        <x:v>guest_tally ; tests/inspection.test.mjs. Géométrie, données et reset contrôlés ; rendu et compréhension sur écran restent à éprouver.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="51" customHeight="1">
+      <x:c r="A135" s="11" t="str">
+        <x:v>QA130</x:v>
+      </x:c>
+      <x:c r="B135" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C135" s="11" t="str">
+        <x:v>Roster stable en solo</x:v>
+      </x:c>
+      <x:c r="D135" s="11" t="str">
+        <x:v>Basculer Alpha/Bêta plusieurs fois au même passage normal, puis activer un effet et rétablir la référence.</x:v>
+      </x:c>
+      <x:c r="E135" s="11" t="str">
+        <x:v>Registre, photo et nombre restent communs entre les deux vues normales ; seule la valeur de l’effet assigné diverge.</x:v>
+      </x:c>
+      <x:c r="F135" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G135" s="11" t="str">
+        <x:v>Scène CPU / interface à éprouver</x:v>
+      </x:c>
+      <x:c r="H135" s="11" t="str">
+        <x:v>tests/scene.geometry.test.mjs : roster explicite Inspecteur, priorité conservée sur setIdentity/setPeers ; annulation de l’override restaure le roster coop.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="51" customHeight="1">
+      <x:c r="A136" s="12" t="str">
+        <x:v>QA131</x:v>
+      </x:c>
+      <x:c r="B136" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C136" s="12" t="str">
+        <x:v>Chalet et campagne</x:v>
+      </x:c>
+      <x:c r="D136" s="12" t="str">
+        <x:v>Choisir le chalet autonome ; essayer une configuration de campagne contenant cabin ; charger les anciennes sauvegardes.</x:v>
+      </x:c>
+      <x:c r="E136" s="12" t="str">
+        <x:v>Le chalet accepte neuf validations autonomes. La campagne reste exactement hôtel → métro → clinique, avec paliers 3 et 6.</x:v>
+      </x:c>
+      <x:c r="F136" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G136" s="12" t="str">
+        <x:v>Règles automatisées</x:v>
+      </x:c>
+      <x:c r="H136" s="12" t="str">
+        <x:v>tests/rules.test.mjs : catalogue, niveaux, campagne et sauvegardes ; 19 tests réussis. Aucun parcours GPU revendiqué.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="77" customHeight="1">
+      <x:c r="A137" s="11" t="str">
+        <x:v>QA132</x:v>
+      </x:c>
+      <x:c r="B137" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C137" s="11" t="str">
+        <x:v>Chalet à quatre clients HTTP</x:v>
+      </x:c>
+      <x:c r="D137" s="11" t="str">
+        <x:v>Créer quatre identités indépendantes, parcourir neuf diagnostics, envoyer des pings table/foyer et quitter.</x:v>
+      </x:c>
+      <x:c r="E137" s="11" t="str">
+        <x:v>Victoire à neuf ; projections privées ; la lecture privée injectée n’est pas propagée dans le ping.</x:v>
+      </x:c>
+      <x:c r="F137" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G137" s="11" t="str">
+        <x:v>Serveur portable HTTP réel</x:v>
+      </x:c>
+      <x:c r="H137" s="11" t="str">
+        <x:v>Réussi : serveur portable compilé sans node_modules, Linux / Node 24.22.1 ; quatre clients dans le chalet, neuf diagnostics et victoire, pings table/foyer sans fuite. Douze contrôles de chemins privés. docs/qa-portable-v0.4.0.json ; aucune fenêtre 3D ni partie humaine validée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="51" customHeight="1">
+      <x:c r="A138" s="12" t="str">
+        <x:v>QA133</x:v>
+      </x:c>
+      <x:c r="B138" s="12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C138" s="12" t="str">
+        <x:v>Votes et radio après reprise</x:v>
+      </x:c>
+      <x:c r="D138" s="12" t="str">
+        <x:v>Perdre un témoin avant consensus, revenir, renouveler la radio et interroger les projections privées.</x:v>
+      </x:c>
+      <x:c r="E138" s="12" t="str">
+        <x:v>Votes antérieurs annulés ; aucun résultat anticipé ni ancien message radio livré à la mauvaise identité.</x:v>
+      </x:c>
+      <x:c r="F138" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G138" s="12" t="str">
+        <x:v>28 tests de résilience</x:v>
+      </x:c>
+      <x:c r="H138" s="12" t="str">
+        <x:v>tests/session-resilience.test.mjs : 28/28 réussites ; interruptions et files simulées ; Internet et voix matérielle non éprouvés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="40" customHeight="1">
+      <x:c r="A139" s="11" t="str">
+        <x:v>QA134</x:v>
+      </x:c>
+      <x:c r="B139" s="11" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="C139" s="11" t="str">
+        <x:v>Configuration STUN/TURN</x:v>
+      </x:c>
+      <x:c r="D139" s="11" t="str">
+        <x:v>Tester URI, limites, secrets, identifiants temporaires, précontrôle --json et --require-turn.</x:v>
+      </x:c>
+      <x:c r="E139" s="11" t="str">
+        <x:v>59 tests passent ; diagnostics expurgés ; la configuration seule ne prétend pas valider un relais connecté.</x:v>
+      </x:c>
+      <x:c r="F139" s="13" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="G139" s="11" t="str">
+        <x:v>Validation statique / commande</x:v>
+      </x:c>
+      <x:c r="H139" s="11" t="str">
+        <x:v>tests/radio-config.test.mjs : 59/59 réussites ; HMAC comparé à node:crypto, aucun DNS ni réseau TURN sondé.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="40" customHeight="1">
+      <x:c r="A140" s="12" t="str">
+        <x:v>QA135</x:v>
+      </x:c>
+      <x:c r="B140" s="12" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C140" s="12" t="str">
+        <x:v>Arches du métro</x:v>
+      </x:c>
+      <x:c r="D140" s="12" t="str">
+        <x:v>Traverser le centre sous chaque arche et tester les dégagements sur le trajet autorisé.</x:v>
+      </x:c>
+      <x:c r="E140" s="12" t="str">
+        <x:v>Aucun pilier ne coupe la route centrale ; forme des arches et accès restent cohérents après changement de lieu.</x:v>
+      </x:c>
+      <x:c r="F140" s="13" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="G140" s="12" t="str">
+        <x:v>Géométrie CPU / GPU restant</x:v>
+      </x:c>
+      <x:c r="H140" s="12" t="str">
+        <x:v>tests/scene.geometry.test.mjs ; correction de géométrie intégrée. Parcours et silhouette perçue à éprouver sur appareil.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F6:F86">
+  <x:conditionalFormatting sqref="F6:F140">
     <x:cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="37" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="38" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F6:F86">
+    <x:dataValidation type="list" sqref="F6:F140">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5e62a490fb44b8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76097457d4b94b8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7247,16 +9007,16 @@
         <x:v>Source de vérité code</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Catalogue runtime 0.2.1</x:v>
+        <x:v>Catalogue runtime 0.4.0</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>54 identifiants intégrés ; titres, baseline, intensité, difficulté et lieux proviennent du code.</x:v>
+        <x:v>96 identifiants intégrés ; titres, baseline, intensité, difficulté et lieux proviennent du code.</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
         <x:v>src/game/catalog.ts</x:v>
       </x:c>
       <x:c r="F9" s="22" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
         <x:v>Le classeur affiche explicitement la QA partielle ; présence dans le code ne vaut pas validation matérielle.</x:v>
@@ -7270,7 +9030,7 @@
         <x:v>Règles actuelles</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Machine de jeu 0.2.1</x:v>
+        <x:v>Machine de jeu 0.4.0</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
         <x:v>Campagne 3 × 3 avec paliers ; lieu unique 9 consécutifs ; 68 % d’anomalies ; 3 erreurs standard.</x:v>
@@ -7279,7 +9039,7 @@
         <x:v>src/game/rules.ts</x:v>
       </x:c>
       <x:c r="F10" s="20" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="12" t="str">
         <x:v>La référence de chaque lieu ne rapporte aucun point ; le mode détendu retire seulement la limite d’erreurs.</x:v>
@@ -7296,13 +9056,13 @@
         <x:v>Catalogue de 120 fiches</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>66 fiches restent conçues sans implémentation. IDs PX d’origine conservés ; nouvelles fiches ajoutées.</x:v>
+        <x:v>24 fiches restent conçues sans implémentation. IDs PX d’origine conservés ; nouvelles fiches ajoutées.</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
         <x:v>docs/anomalies-design.json</x:v>
       </x:c>
       <x:c r="F11" s="22" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
         <x:v>Une promotion de statut n’ajoute pas une fiche doublon pour la même anomalie.</x:v>
@@ -7641,19 +9401,19 @@
         <x:v>Baselines et noms officiels</x:v>
       </x:c>
       <x:c r="D26" s="12" t="str">
-        <x:v>Saint-Clair / Terminus 09 / Aile blanche ; règles de référence spécifiques.</x:v>
+        <x:v>Saint-Clair / Terminus 09 / Aile blanche en campagne ; Chalet de service en autonome ; règles de référence propres à chaque lieu.</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
         <x:v>src/game/levels.ts</x:v>
       </x:c>
       <x:c r="F26" s="20" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="12" t="str">
         <x:v>Le panneau métro et le moniteur clinique sont des références fixes de jeu.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="77" customHeight="1">
+    <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>R22</x:v>
       </x:c>
@@ -7664,13 +9424,13 @@
         <x:v>Bilan de vérification</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>v0.2.1 : 19 tests radio et 4 du contrôleur UI réussis ; typecheck, builds local / hébergé et test portable à deux clients HTTP réussis. Preuves v0.2 conservées : 17 règles, 11 suites CPU 3D, D1 quatre clients et GLB relu. Aucun nouvel essai ICE ou de microphone physique.</x:v>
+        <x:v>189 contrôles réussis : règles 19, résilience 28, scène 25, chalet 9, inspection 13, radio 32, UI radio 4, configuration 59. TypeScript, builds local/hébergé et portable HTTP 2 puis 4 clients réussis. GPU et voix matérielle non validés.</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
         <x:v>docs/QA.md</x:v>
       </x:c>
       <x:c r="F27" s="22" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
         <x:v>Les essais déclarés se limitent à leur périmètre ; aucune validation GPU ou microphone physique sans preuve.</x:v>
@@ -7693,7 +9453,7 @@
         <x:v>docs/workbook-v02.json ; docs/runtime-catalog.json ; docs/build-status.json</x:v>
       </x:c>
       <x:c r="F28" s="20" t="d">
-        <x:v>2026-10-26T12:00:00.000Z</x:v>
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G28" s="12" t="str">
         <x:v>Le générateur scripts/build-design-workbook.mjs reconstruit le classeur et ses contrôles.</x:v>
@@ -7745,7 +9505,7 @@
         <x:v>Pas de panne réseau indiscernable, aucun clonage vocal et aucune capture personnelle utilisés comme surprise.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="40" customHeight="1">
+    <x:row r="31" ht="51" customHeight="1">
       <x:c r="A31" s="11" t="str">
         <x:v>R26</x:v>
       </x:c>
@@ -7756,7 +9516,7 @@
         <x:v>Inspecteur GLB et manifeste</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>52 444 triangles, 12 articulations rigides, trois animations ; relecture GLTFLoader réussie.</x:v>
+        <x:v>Asset conservé de 0.3.0 : 53 990 triangles, 58 maillages, 12 articulations et trois animations ; validation de relecture documentée dans le manifeste.</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
         <x:v>public/models/inspecteur-parallaxe.glb ; public/models/inspecteur-parallaxe.manifest.json</x:v>
@@ -7765,10 +9525,10 @@
         <x:v>2026-10-26T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>Modèle procédural original ; pas de skinning, pas de lettrage badge embarqué et pas de validation GPU.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="64" customHeight="1">
+        <x:v>Modèle procédural original ; pas de skinning, pas de lettrage badge embarqué. Le rapport est historique, sans nouvelle validation GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="51" customHeight="1">
       <x:c r="A32" s="12" t="str">
         <x:v>R27</x:v>
       </x:c>
@@ -7788,10 +9548,10 @@
         <x:v>2026-10-26T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G32" s="12" t="str">
-        <x:v>19/19 tests radio réussis, dont 7 nouveaux : extinction, micro seul, anciennes réponses, nouvelle demande et sortie. Avant correction : 6 échecs / 1 succès ; après : 7/7. Pistes et API simulées ; aucun microphone physique ni transmission mesurée.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="77" customHeight="1">
+        <x:v>Les sept scénarios de permission tardive 0.2.1 sont conservés dans les 32 tests radio réussis en 0.4.0. Pistes et API simulées ; aucun microphone physique ni transmission réelle mesurés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="51" customHeight="1">
       <x:c r="A33" s="11" t="str">
         <x:v>R28</x:v>
       </x:c>
@@ -7811,10 +9571,10 @@
         <x:v>2026-10-26T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>4/4 tests de radio-actions : arrêt libère l’attente ; ancienne réponse ignorée, refus courant signalé ; changement de salon / démontage invalide les callbacks ; appel dans le geste utilisateur et échec synchrone nettoyé. Typecheck réussi. Aucun test DOM, micro physique ou GPU.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="77" customHeight="1">
+        <x:v>4/4 tests du contrôleur radio réussis en 0.4.0 : attente libérée, réponses obsolètes ignorées, changement de client et geste utilisateur. API simulées ; aucun test DOM ou microphone physique.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="40" customHeight="1">
       <x:c r="A34" s="12" t="str">
         <x:v>R29</x:v>
       </x:c>
@@ -7834,13 +9594,358 @@
         <x:v>2026-10-26T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="G34" s="12" t="str">
-        <x:v>v0.2.1 : typecheck, build local, build hébergé et test portable réussis. Deux clients HTTP authentifiés : référence, inspection, perceptions privées, unanimité et sortie ; serveur compilé lancé sans node_modules. Les archives finales et GitHub CI restent à contrôler après assemblage / publication.</x:v>
+        <x:v>Rapport historique 0.2.1. Le bilan courant est référencé séparément ; cette preuve ne valide pas les ajouts 0.4.0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="51" customHeight="1">
+      <x:c r="A35" s="11" t="str">
+        <x:v>R30</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>Contrats de conception</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>Extension 0.3.0 du 27 octobre 2026</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>Les 27 ajouts reprennent des fiches existantes, avec adaptations documentées pour les supports construits.</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>Brief de la conversation ; docs/anomalies-design.json</x:v>
+      </x:c>
+      <x:c r="F35" s="22" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str">
+        <x:v>Les 27 fiches sont promues avec leurs IDs historiques conservés. Baselines et descriptions sont alignées avec les objets réellement construits ; QA matérielle toujours distincte.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="40" customHeight="1">
+      <x:c r="A36" s="12" t="str">
+        <x:v>R31</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>Sources de vérité</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>Catalogue et preuves historiques · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
+        <x:v>Code runtime, projections privées, signal de calibration et modèles déterminent la description réalisée.</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>src/game/catalog.ts ; src/game/rules.ts ; src/game/radio.ts ; src/game/scene.ts ; src/game/avatar.ts</x:v>
+      </x:c>
+      <x:c r="F36" s="20" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>Catalogue figé : 81 entrées, 69 visuelles et 12 radio. La présence en code ne vaut pas validation GPU, mix ou transport vocal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="40" customHeight="1">
+      <x:c r="A37" s="11" t="str">
+        <x:v>R32</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>Tests radio exécutés</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>Radio et PCM · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>32/32 tests, dont 13 nouveaux : vrais buffers de production, fréquences, code, canaux, queue, annulation et API simulées.</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>docs/qa-radio-v0.3.json ; src/game/radio-evidence.ts</x:v>
+      </x:c>
+      <x:c r="F37" s="22" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="str">
+        <x:v>Aucune écoute humaine, aucun microphone physique ni transport ICE/TURN connecté validés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="40" customHeight="1">
+      <x:c r="A38" s="12" t="str">
+        <x:v>R33</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>Contrôles CPU exécutés</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="str">
+        <x:v>Scène et corps · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
+        <x:v>18 suites : 69 effets, reset, repères, modèles, lectures, changements de lieu et identité des inspecteurs homonymes.</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>docs/qa-scene-v0.3.0.json ; tests/scene.geometry.test.mjs</x:v>
+      </x:c>
+      <x:c r="F38" s="20" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>Géométrie, transformations et raycasting réels ; renderer et canvas simulés. Aucun pixel, shader ou FPS certifié.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="40" customHeight="1">
+      <x:c r="A39" s="11" t="str">
+        <x:v>R34</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>Limite de recette</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>Prévisualisation navigateur · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>La route de prévisualisation exacte a refusé la connexion avant les contrôles visuels.</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>docs/qa-browser-v0.3.0.json</x:v>
+      </x:c>
+      <x:c r="F39" s="22" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str">
+        <x:v>net::ERR_CONNECTION_REFUSED ; aucun contournement. Les anciens résultats GPU désactivé / zéro ICE restent historiques.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="40" customHeight="1">
+      <x:c r="A40" s="12" t="str">
+        <x:v>R35</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>Tests de logique exécutés</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>Règles, inspection et contrôle radio</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>18 tests de règles, 8 d’inspection et 4 du contrôleur radio réussis.</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>docs/qa-inspection-v0.3.0.json ; tests/rules.test.mjs ; tests/radio-actions.test.mjs</x:v>
+      </x:c>
+      <x:c r="F40" s="20" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>Contrôles de logique et données. Les textes dessinés, les interactions DOM et les microphones physiques demandent une recette séparée.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="77" customHeight="1">
+      <x:c r="A41" s="11" t="str">
+        <x:v>R36</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>Livraison versionnée</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>Compilations et essais de distribution · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>v0.3.0 : TypeScript strict, builds local / hébergé et serveur portable à deux clients HTTP réussis. Serveur sans node_modules ; chemins privés protégés après normalisation. Test HTTP sous Linux / Node 24.22.1, sans essai natif Windows/macOS. GitHub en attente d’autorisation ; CI 0.3.0 non exécutée.</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>docs/qa-final-v0.3.0.json</x:v>
+      </x:c>
+      <x:c r="F41" s="22" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="str">
+        <x:v>Rapport historique de la livraison 0.3.0, récupérée avant intégration. Le suivi de publication actuel figure dans le bilan 0.4.0.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="40" customHeight="1">
+      <x:c r="A42" s="12" t="str">
+        <x:v>R37</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>Serveur portable vérifié</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="str">
+        <x:v>Chemins normalisés · 0.3.0</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
+        <x:v>Le serveur refuse les chemins privés après résolution ; HTML, JavaScript et CSS publics demeurent servis.</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>docs/qa-portable-path-v0.3.0.json</x:v>
+      </x:c>
+      <x:c r="F42" s="20" t="d">
+        <x:v>2026-10-27T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>HTTP Linux / Node 24.22.1 ; dix GET privés et un HEAD refusés, fixture hors-racine inaccessible. Aucun stockage de sessions réel lu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="51" customHeight="1">
+      <x:c r="A43" s="11" t="str">
+        <x:v>R38</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>Source de vérité courante</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>Catalogue et extensions · 0.4.0</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>96 entrées : 84 effets visuels et 12 profils radio ; 15 fiches promues avec leurs IDs d’origine.</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>src/game/catalog.ts ; docs/runtime-catalog.json</x:v>
+      </x:c>
+      <x:c r="F43" s="22" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str">
+        <x:v>Pools chevauchants : Saint-Clair 76, Terminus 09 48, Aile blanche 48, Chalet 35. radio_signal est visuel et ne crée pas de profil radio supplémentaire.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="40" customHeight="1">
+      <x:c r="A44" s="12" t="str">
+        <x:v>R39</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>Objets originaux</x:v>
+      </x:c>
+      <x:c r="C44" s="12" t="str">
+        <x:v>Registre, gant et galerie</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="str">
+        <x:v>13 tests couvrent valeurs privées, vrais meshes, lectures E, météo, latéralité, reset et roster présent.</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>src/game/inspection-data.ts ; src/game/inspection-props.ts ; tests/inspection.test.mjs</x:v>
+      </x:c>
+      <x:c r="F44" s="20" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str">
+        <x:v>Les textes et mouvements sont contrôlés en CPU ; lisibilité finale et ergonomie restent à vérifier sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="11" t="str">
+        <x:v>R40</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>Contrôles de scène</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>Scène et reflets · 0.4.0</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>25 contrôles CPU de scène réussis : 84 effets visuels, reset, raycasts, accès, reflets, roster stable et quatre lieux. Huit surfaces planaires, deux par lieu. Neuf tests chalet séparés. Aucun pixel, shader ou FPS validé.</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>docs/qa-scene-v0.4.0.json ; tests/scene.geometry.test.mjs</x:v>
+      </x:c>
+      <x:c r="F45" s="22" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str">
+        <x:v>Géométrie stockée : 582 153 triangles et 1 244 maillages. Hôtel 252 932, métro 102 766, clinique 126 607, chalet 75 956. Inspecteur 53 990. Inclut objets/effets inactifs ; ce ne sont pas des triangles dessinés par image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="40" customHeight="1">
+      <x:c r="A46" s="12" t="str">
+        <x:v>R41</x:v>
+      </x:c>
+      <x:c r="B46" s="12" t="str">
+        <x:v>Quatrième lieu autonome</x:v>
+      </x:c>
+      <x:c r="C46" s="12" t="str">
+        <x:v>Chalet de service</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="str">
+        <x:v>9 tests CPU dédiés ; architecture, collisions, preuves table/foyer, lectures et référence.</x:v>
+      </x:c>
+      <x:c r="E46" s="12" t="str">
+        <x:v>src/game/cabin.ts ; docs/qa-cabin-v0.4.0.json ; tests/cabin.geometry.test.mjs</x:v>
+      </x:c>
+      <x:c r="F46" s="20" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G46" s="12" t="str">
+        <x:v>La campagne garde trois lieux ; le chalet se choisit en autonome, neuf diagnostics. Aucun FPS ni pixel validé.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="77" customHeight="1">
+      <x:c r="A47" s="11" t="str">
+        <x:v>R42</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="str">
+        <x:v>Vérification courante</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>Build et portable · 0.4.0</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="str">
+        <x:v>0.4.0 : TypeScript strict, builds local et hébergé réussis. Portable sans node_modules sous Linux / Node 24.22.1 : deux clients puis chalet à quatre, neuf diagnostics et victoire ; 12 contrôles de chemins. Pas d’essai natif Windows/macOS. Publication et CI 0.4.0 suivies séparément.</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>docs/qa-final-v0.4.0.json ; docs/qa-portable-v0.4.0.json</x:v>
+      </x:c>
+      <x:c r="F47" s="22" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="str">
+        <x:v>Les preuves sont limitées aux outils et environnements indiqués dans les rapports ; matériels physiques non testés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="51" customHeight="1">
+      <x:c r="A48" s="12" t="str">
+        <x:v>R43</x:v>
+      </x:c>
+      <x:c r="B48" s="12" t="str">
+        <x:v>Historique GitHub vérifié</x:v>
+      </x:c>
+      <x:c r="C48" s="12" t="str">
+        <x:v>CI main après correctifs coop / radio</x:v>
+      </x:c>
+      <x:c r="D48" s="12" t="str">
+        <x:v>CI réussie sur main ccf629a22b5409f9ea9ad4eb5a221253a7030893 : correctifs 0.2.1 intégrés avant la reprise 0.4.0.</x:v>
+      </x:c>
+      <x:c r="E48" s="21" t="str">
+        <x:v>https://github.com/darknigthmare/Parallaxe_Protocole9/actions/runs/40681454450</x:v>
+      </x:c>
+      <x:c r="F48" s="20" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G48" s="12" t="str">
+        <x:v>Cette réussite historique ne vaut pas CI de la branche 0.4.0. Le complément radio daté reste un document historique ; ce maître couvre le contenu courant complet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="40" customHeight="1">
+      <x:c r="A49" s="11" t="str">
+        <x:v>R44</x:v>
+      </x:c>
+      <x:c r="B49" s="11" t="str">
+        <x:v>Résilience et configuration</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="str">
+        <x:v>Correctifs préservés et rejoués</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>28 tests de résilience et 59 tests de configuration radio réussis sur le travail 0.4.0.</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>tests/session-resilience.test.mjs ; tests/radio-config.test.mjs</x:v>
+      </x:c>
+      <x:c r="F49" s="22" t="d">
+        <x:v>2026-10-28T12:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="str">
+        <x:v>Retours, votes, confidentialité, epochs, URI et HMAC contrôlés ; aucune prétention de voix relayée sur appareils.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f1c5233b67e42d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R288432846c314fcd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8266,7 +10371,7 @@
         <x:v>Le catalogue reste fini et peut être revu après plusieurs tours.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" ht="51" customHeight="1">
       <x:c r="A21" s="11" t="str">
         <x:v>L16</x:v>
       </x:c>
@@ -8286,7 +10391,7 @@
         <x:v>Présent</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>Les trois effets relationnels attribuent plutôt des codes, flèches ou heures SYNCHRO plausibles mais contradictoires.</x:v>
+        <x:v>Les comparaisons relationnelles distribuent des codes, flèches, heures ou valeurs d’objets plausibles ; seule leur contradiction entre témoins est anormale.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="40" customHeight="1">
@@ -8427,7 +10532,7 @@
         <x:v>Le compteur global demeure au palier acquis ; toutes les perceptions rejoignent le même lieu.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="40" customHeight="1">
+    <x:row r="28" ht="51" customHeight="1">
       <x:c r="A28" s="12" t="str">
         <x:v>L23</x:v>
       </x:c>
@@ -8435,7 +10540,7 @@
         <x:v>Lieu au choix</x:v>
       </x:c>
       <x:c r="C28" s="12" t="str">
-        <x:v>Choisir l’un des trois lieux et y jouer toute la session.</x:v>
+        <x:v>Choisir Saint-Clair, Terminus 09, Aile blanche ou le Chalet de service et y jouer toute la session.</x:v>
       </x:c>
       <x:c r="D28" s="12" t="str">
         <x:v>Mode single</x:v>
@@ -8447,10 +10552,10 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="G28" s="12" t="str">
-        <x:v>Utile pour apprendre une baseline ou rejouer un catalogue local.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="40" customHeight="1">
+        <x:v>Le chalet est un quatrième lieu autonome. La campagne demeure Saint-Clair → Terminus 09 → Aile blanche, soit neuf validations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="51" customHeight="1">
       <x:c r="A29" s="11" t="str">
         <x:v>L24</x:v>
       </x:c>
@@ -8458,13 +10563,13 @@
         <x:v>Étalonnage radio</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>Déclencher trois tonalités connues et lire le relevé privé.</x:v>
+        <x:v>Déclencher le contrôle : identifiant RELAIS, trois tonalités principales et clics, puis lire le relevé privé.</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>Bouton Étalonner</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>Détecter les six anomalies radio même sans voix entrante ni microphone.</x:v>
+        <x:v>Détecter les douze anomalies de contrôle radio même sans voix entrante ni microphone.</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -8555,7 +10660,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55c3b554c7314ae1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bd55e151a1540ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8589,6 +10694,7 @@
     <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="20" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="30" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -8614,6 +10720,7 @@
       <x:c r="T1" s="3"/>
       <x:c r="U1" s="3"/>
       <x:c r="V1" s="3"/>
+      <x:c r="W1" s="3"/>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -8640,6 +10747,7 @@
       <x:c r="T2" s="3"/>
       <x:c r="U2" s="3"/>
       <x:c r="V2" s="3"/>
+      <x:c r="W2" s="3"/>
     </x:row>
     <x:row r="3" ht="8" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -8664,10 +10772,11 @@
       <x:c r="T3" s="5"/>
       <x:c r="U3" s="5"/>
       <x:c r="V3" s="5"/>
+      <x:c r="W3" s="5"/>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>A = perception affectée ; B = autre témoin. Mise en scène / assets = conception. Les trois colonnes de lieu indiquent la disponibilité en code.</x:v>
+        <x:v>A = perception affectée ; B = autre témoin. Mise en scène / assets = conception. Les colonnes de lieu indiquent la disponibilité en code. Le chalet se joue en inspection autonome.</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -8690,6 +10799,7 @@
       <x:c r="T4" s="3"/>
       <x:c r="U4" s="3"/>
       <x:c r="V4" s="3"/>
+      <x:c r="W4" s="3"/>
     </x:row>
     <x:row r="5" ht="40" customHeight="1">
       <x:c r="A5" s="10" t="str">
@@ -8758,8 +10868,11 @@
       <x:c r="V5" s="10" t="str">
         <x:v>Canal de preuve</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="77" customHeight="1">
+      <x:c r="W5" s="10" t="str">
+        <x:v>Chalet (code)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>PX-001</x:v>
       </x:c>
@@ -8812,7 +10925,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R6" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S6" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8826,8 +10939,11 @@
       <x:c r="V6" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="77" customHeight="1">
+      <x:c r="W6" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>PX-002</x:v>
       </x:c>
@@ -8880,7 +10996,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R7" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S7" s="19" t="str">
         <x:v>Oui</x:v>
@@ -8894,8 +11010,11 @@
       <x:c r="V7" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="77" customHeight="1">
+      <x:c r="W7" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>PX-003</x:v>
       </x:c>
@@ -8948,7 +11067,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R8" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S8" s="18" t="str">
         <x:v>Oui</x:v>
@@ -8962,8 +11081,11 @@
       <x:c r="V8" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="77" customHeight="1">
+      <x:c r="W8" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>PX-004</x:v>
       </x:c>
@@ -9016,7 +11138,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R9" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S9" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9030,8 +11152,11 @@
       <x:c r="V9" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" ht="77" customHeight="1">
+      <x:c r="W9" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>PX-005</x:v>
       </x:c>
@@ -9084,7 +11209,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R10" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S10" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9098,8 +11223,11 @@
       <x:c r="V10" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="77" customHeight="1">
+      <x:c r="W10" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>PX-006</x:v>
       </x:c>
@@ -9152,7 +11280,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R11" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S11" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9166,8 +11294,11 @@
       <x:c r="V11" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="77" customHeight="1">
+      <x:c r="W11" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="12" t="str">
         <x:v>PX-007</x:v>
       </x:c>
@@ -9220,7 +11351,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R12" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S12" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9234,8 +11365,11 @@
       <x:c r="V12" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="77" customHeight="1">
+      <x:c r="W12" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="11" t="str">
         <x:v>PX-008</x:v>
       </x:c>
@@ -9288,7 +11422,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R13" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S13" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9302,8 +11436,11 @@
       <x:c r="V13" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="77" customHeight="1">
+      <x:c r="W13" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="12" t="str">
         <x:v>PX-009</x:v>
       </x:c>
@@ -9356,7 +11493,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R14" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S14" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9370,8 +11507,11 @@
       <x:c r="V14" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="77" customHeight="1">
+      <x:c r="W14" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="11" t="str">
         <x:v>PX-010</x:v>
       </x:c>
@@ -9424,7 +11564,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R15" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S15" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9438,8 +11578,11 @@
       <x:c r="V15" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="77" customHeight="1">
+      <x:c r="W15" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="12" t="str">
         <x:v>PX-011</x:v>
       </x:c>
@@ -9492,7 +11635,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R16" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S16" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9506,8 +11649,11 @@
       <x:c r="V16" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="77" customHeight="1">
+      <x:c r="W16" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="11" t="str">
         <x:v>PX-012</x:v>
       </x:c>
@@ -9560,7 +11706,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R17" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S17" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9574,8 +11720,11 @@
       <x:c r="V17" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="77" customHeight="1">
+      <x:c r="W17" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="12" t="str">
         <x:v>PX-013</x:v>
       </x:c>
@@ -9628,7 +11777,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R18" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S18" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9642,8 +11791,11 @@
       <x:c r="V18" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="77" customHeight="1">
+      <x:c r="W18" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="11" t="str">
         <x:v>PX-014</x:v>
       </x:c>
@@ -9696,7 +11848,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R19" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S19" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9710,8 +11862,11 @@
       <x:c r="V19" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="77" customHeight="1">
+      <x:c r="W19" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="12" t="str">
         <x:v>PX-015</x:v>
       </x:c>
@@ -9764,7 +11919,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R20" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S20" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9778,8 +11933,11 @@
       <x:c r="V20" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="77" customHeight="1">
+      <x:c r="W20" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="11" t="str">
         <x:v>PX-016</x:v>
       </x:c>
@@ -9832,7 +11990,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R21" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S21" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9846,8 +12004,11 @@
       <x:c r="V21" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22" ht="77" customHeight="1">
+      <x:c r="W21" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="12" t="str">
         <x:v>PX-017</x:v>
       </x:c>
@@ -9900,7 +12061,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R22" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S22" s="18" t="str">
         <x:v>Oui</x:v>
@@ -9912,10 +12073,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="V22" s="12" t="str">
-        <x:v>Visuel / objet / espace</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="77" customHeight="1">
+        <x:v>Corps / reflet / mouvement</x:v>
+      </x:c>
+      <x:c r="W22" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="11" t="str">
         <x:v>PX-018</x:v>
       </x:c>
@@ -9968,7 +12132,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R23" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S23" s="19" t="str">
         <x:v>Oui</x:v>
@@ -9982,8 +12146,11 @@
       <x:c r="V23" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" ht="77" customHeight="1">
+      <x:c r="W23" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="12" t="str">
         <x:v>PX-019</x:v>
       </x:c>
@@ -10036,7 +12203,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R24" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S24" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10050,8 +12217,11 @@
       <x:c r="V24" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" ht="77" customHeight="1">
+      <x:c r="W24" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="11" t="str">
         <x:v>PX-020</x:v>
       </x:c>
@@ -10104,7 +12274,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R25" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S25" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10118,8 +12288,11 @@
       <x:c r="V25" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" ht="77" customHeight="1">
+      <x:c r="W25" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="12" t="str">
         <x:v>PX-021</x:v>
       </x:c>
@@ -10172,7 +12345,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R26" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S26" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10186,8 +12359,11 @@
       <x:c r="V26" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" ht="77" customHeight="1">
+      <x:c r="W26" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>PX-022</x:v>
       </x:c>
@@ -10240,7 +12416,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R27" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S27" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10254,8 +12430,11 @@
       <x:c r="V27" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" ht="77" customHeight="1">
+      <x:c r="W27" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="12" t="str">
         <x:v>PX-023</x:v>
       </x:c>
@@ -10308,7 +12487,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R28" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S28" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10322,8 +12501,11 @@
       <x:c r="V28" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" ht="77" customHeight="1">
+      <x:c r="W28" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="11" t="str">
         <x:v>PX-024</x:v>
       </x:c>
@@ -10376,7 +12558,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R29" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S29" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10390,8 +12572,11 @@
       <x:c r="V29" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="77" customHeight="1">
+      <x:c r="W29" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="12" t="str">
         <x:v>PX-025</x:v>
       </x:c>
@@ -10444,7 +12629,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R30" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S30" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10458,8 +12643,11 @@
       <x:c r="V30" s="12" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="W30" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="11" t="str">
         <x:v>PX-026</x:v>
       </x:c>
@@ -10470,40 +12658,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E31" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F31" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>Porte</x:v>
+        <x:v>Hôtel · bureau D2</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
-        <x:v>Chaque observateur voit la même plaque de chambre.</x:v>
+        <x:v>Le bureau D2 assigne la chambre 204 ou 205. La valeur peut changer entre passages, mais doit être commune à tous les inspecteurs.</x:v>
       </x:c>
       <x:c r="I31" s="11" t="str">
-        <x:v>Il lit 204 sur la deuxième porte.</x:v>
+        <x:v>Le dossier D2 assigne deux chambres différentes selon les observateurs.</x:v>
       </x:c>
       <x:c r="J31" s="11" t="str">
-        <x:v>Il lit 205 sur la même porte.</x:v>
+        <x:v>Il lit la valeur commune normale du passage sur le même BUREAU D2.</x:v>
       </x:c>
       <x:c r="K31" s="11" t="str">
-        <x:v>Aucune vue n’est absurde seule. Lire ensemble la plaque et sa position.</x:v>
+        <x:v>Lisez le même dossier D2 et comparez le numéro de chambre, sans le confondre avec les portes 901–904.</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>Porte regardée par les deux joueurs à moins de 5 secondes d’écart.</x:v>
+        <x:v>Lecture de l’afficheur du bureau de contrôle près de l’entrée. Valeur stable pendant le passage.</x:v>
       </x:c>
       <x:c r="M31" s="11" t="str">
-        <x:v>Le désaccord stable entre deux valeurs plausibles est la preuve.</x:v>
+        <x:v>Deux assignations plausibles mais différentes sur le même appareil confirment l’anomalie.</x:v>
       </x:c>
       <x:c r="N31" s="11" t="str">
-        <x:v>Un code de localisation identique est imprimé sous la plaque.</x:v>
+        <x:v>Les vraies portes gardent leurs numéros. Une variation entre deux passages n’est pas une preuve ; comparer deux témoins du même passage.</x:v>
       </x:c>
       <x:c r="O31" s="11" t="str">
-        <x:v>Deux textures de numéro, attribution privée serveur.</x:v>
+        <x:v>Afficheur original BUREAU D2, valeurs privées serveur et lecture agrandie facultative.</x:v>
       </x:c>
       <x:c r="P31" s="11" t="str">
         <x:v>paired_room</x:v>
@@ -10512,10 +12700,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R31" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S31" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T31" s="19" t="str">
         <x:v>—</x:v>
@@ -10526,8 +12714,11 @@
       <x:c r="V31" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32" ht="77" customHeight="1">
+      <x:c r="W31" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="12" t="str">
         <x:v>PX-027</x:v>
       </x:c>
@@ -10580,7 +12771,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R32" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S32" s="18" t="str">
         <x:v>Oui</x:v>
@@ -10594,8 +12785,11 @@
       <x:c r="V32" s="12" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33" ht="40" customHeight="1">
+      <x:c r="W32" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="90" customHeight="1">
       <x:c r="A33" s="11" t="str">
         <x:v>PX-028</x:v>
       </x:c>
@@ -10606,40 +12800,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E33" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F33" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>Réception</x:v>
+        <x:v>Archives R9</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>Les noms du registre sont identiques pour tous.</x:v>
+        <x:v>Le registre R9 porte ARRIVÉE 03:09, LIGNE 09 et l’un des deux premiers indicatifs/pseudonymes présents, ou un témoin fictif explicitement étiqueté en solo et exclu du compteur réel. Cette identité peut varier entre passages, mais doit être commune aux perceptions.</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str">
-        <x:v>La dernière ligne porte son propre nom.</x:v>
+        <x:v>La même ligne du registre R9 porte deux identités différentes selon les observateurs.</x:v>
       </x:c>
       <x:c r="J33" s="11" t="str">
-        <x:v>La même ligne porte le nom du premier inspecteur.</x:v>
+        <x:v>Le registre conserve l’autre identité ordinaire prévue pour cette ligne.</x:v>
       </x:c>
       <x:c r="K33" s="11" t="str">
-        <x:v>Lire la ligne et l’heure d’arrivée correspondante.</x:v>
+        <x:v>Comparez l’arrivée 03:09, la ligne 09 et l’indicatif complet. En solo, l’entrée témoin fictive ne compte pas comme joueur connecté.</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>Ouverture volontaire du registre.</x:v>
+        <x:v>Valeurs assignées au passage ; lecture E facultative.</x:v>
       </x:c>
       <x:c r="M33" s="11" t="str">
-        <x:v>Deux identités différentes sur une ligne unique prouvent la fracture.</x:v>
+        <x:v>Deux indicatifs différents à ARRIVÉE 03:09 / LIGNE 09 constituent la contradiction.</x:v>
       </x:c>
       <x:c r="N33" s="11" t="str">
-        <x:v>Le jeu emploie seulement les pseudonymes saisis dans le salon.</x:v>
+        <x:v>Pseudonymes de session seulement, distingués par indicatif ; en solo une entrée témoin fictive ne compte pas comme personne présente.</x:v>
       </x:c>
       <x:c r="O33" s="11" t="str">
-        <x:v>Registre interactif, glyphes locaux.</x:v>
+        <x:v>Registre original, cartes de pseudonymes et lecture agrandie.</x:v>
       </x:c>
       <x:c r="P33" s="11" t="str">
         <x:v>paired_guestbook</x:v>
@@ -10648,10 +12842,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R33" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S33" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T33" s="19" t="str">
         <x:v>—</x:v>
@@ -10662,8 +12856,11 @@
       <x:c r="V33" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="40" customHeight="1">
+      <x:c r="W33" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="12" t="str">
         <x:v>PX-029</x:v>
       </x:c>
@@ -10674,40 +12871,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D34" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E34" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F34" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G34" s="12" t="str">
-        <x:v>Chariot</x:v>
+        <x:v>Hôtel · consigne C9</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str">
-        <x:v>Une seule valise porte une étiquette 09.</x:v>
+        <x:v>La consigne C9 contient deux valises A et B, étiquetées 09 et 18. Leur attribution peut varier entre passages mais concorde entre joueurs.</x:v>
       </x:c>
       <x:c r="I34" s="12" t="str">
-        <x:v>La valise de gauche est étiquetée 09.</x:v>
+        <x:v>L’étiquette 09 est portée par deux côtés différents de la consigne selon les observateurs.</x:v>
       </x:c>
       <x:c r="J34" s="12" t="str">
-        <x:v>La valise de droite est étiquetée 09.</x:v>
+        <x:v>Les étiquettes occupent leur position commune du passage.</x:v>
       </x:c>
       <x:c r="K34" s="12" t="str">
-        <x:v>Comparer position, poignée et texte de chaque valise.</x:v>
+        <x:v>Comparez le côté A rectangulaire et le côté B arrondi depuis la face de la consigne.</x:v>
       </x:c>
       <x:c r="L34" s="12" t="str">
-        <x:v>Inspection du chariot.</x:v>
+        <x:v>Inspection persistante de la nouvelle consigne C9.</x:v>
       </x:c>
       <x:c r="M34" s="12" t="str">
-        <x:v>Deux positions pour un repère unique constituent l’anomalie.</x:v>
+        <x:v>Le même identifiant unique est associé à deux positions différentes selon les témoins.</x:v>
       </x:c>
       <x:c r="N34" s="12" t="str">
-        <x:v>Formes différentes pour rester jouable sans perception des couleurs.</x:v>
+        <x:v>La différence reste lisible par forme, côté et texte. Le bagage du chariot original est un autre objet de référence.</x:v>
       </x:c>
       <x:c r="O34" s="12" t="str">
-        <x:v>Deux valises distinctes, étiquettes interverties.</x:v>
+        <x:v>Deux valises originales, formes contrastées, étiquettes 09/18 et attribution privée.</x:v>
       </x:c>
       <x:c r="P34" s="12" t="str">
         <x:v>paired_luggage</x:v>
@@ -10716,10 +12913,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R34" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S34" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T34" s="18" t="str">
         <x:v>—</x:v>
@@ -10730,8 +12927,11 @@
       <x:c r="V34" s="12" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" ht="40" customHeight="1">
+      <x:c r="W34" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="11" t="str">
         <x:v>PX-030</x:v>
       </x:c>
@@ -10742,40 +12942,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E35" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F35" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>Vestiaire</x:v>
+        <x:v>Consigne C9</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
-        <x:v>Un gant gauche repose sur le banc.</x:v>
+        <x:v>Le gant du plateau C9 peut être gauche ou droit selon le passage. Depuis le repère ICI, poignet vers vous, sa latéralité doit être commune à tous.</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str">
-        <x:v>Le pouce pointe à gauche.</x:v>
+        <x:v>Le pouce du même gant C9 se trouve de deux côtés différents selon les perceptions.</x:v>
       </x:c>
       <x:c r="J35" s="11" t="str">
-        <x:v>Le pouce pointe à droite.</x:v>
+        <x:v>Le même gant présente la latéralité ordinaire de ce passage.</x:v>
       </x:c>
       <x:c r="K35" s="11" t="str">
-        <x:v>Décrire l’orientation du pouce depuis le même côté du banc.</x:v>
+        <x:v>Placez-vous sur le même repère ICI, poignet du gant vers vous, puis comparez la position du pouce.</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>Approche du vestiaire.</x:v>
+        <x:v>Valeurs assignées au passage ; observation depuis ICI.</x:v>
       </x:c>
       <x:c r="M35" s="11" t="str">
-        <x:v>L’objet change de latéralité entre les vues.</x:v>
+        <x:v>Le pouce change de côté entre témoins orientés de la même façon.</x:v>
       </x:c>
       <x:c r="N35" s="11" t="str">
-        <x:v>Marquage sol pour éliminer l’ambiguïté du point de vue.</x:v>
+        <x:v>Gauche et droite sont deux variantes normales. Comparer la même orientation ; une variante isolée ne donne pas le verdict.</x:v>
       </x:c>
       <x:c r="O35" s="11" t="str">
-        <x:v>Gants gauche et droit détaillés.</x:v>
+        <x:v>Géométrie de paume, doigts et pouce ; repère ICI commun.</x:v>
       </x:c>
       <x:c r="P35" s="11" t="str">
         <x:v>paired_hand</x:v>
@@ -10784,10 +12984,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R35" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S35" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T35" s="19" t="str">
         <x:v>—</x:v>
@@ -10798,8 +12998,11 @@
       <x:c r="V35" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" ht="40" customHeight="1">
+      <x:c r="W35" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="12" t="str">
         <x:v>PX-031</x:v>
       </x:c>
@@ -10810,40 +13013,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D36" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E36" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F36" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G36" s="12" t="str">
-        <x:v>Tableau</x:v>
+        <x:v>Galerie G9</x:v>
       </x:c>
       <x:c r="H36" s="12" t="str">
-        <x:v>Une photo représente un même quai sous la pluie.</x:v>
+        <x:v>La photographie du quai G9 peut montrer pluie et parapluie, neige et flocons, ou soleil et rayons. Dans un passage, la même météo doit être visible par tous.</x:v>
       </x:c>
       <x:c r="I36" s="12" t="str">
-        <x:v>Le quai est ensoleillé.</x:v>
+        <x:v>La même photographie G9 montre deux météos différentes selon les perceptions.</x:v>
       </x:c>
       <x:c r="J36" s="12" t="str">
-        <x:v>Le quai est sous la neige.</x:v>
+        <x:v>La même photographie garde la météo ordinaire de ce passage.</x:v>
       </x:c>
       <x:c r="K36" s="12" t="str">
-        <x:v>Décrire les objets météo plutôt que la teinte générale.</x:v>
+        <x:v>Nommez les éléments visibles : parapluie, flocons ou disque solaire, puis comparez le même cadre.</x:v>
       </x:c>
       <x:c r="L36" s="12" t="str">
-        <x:v>Observation du cadre.</x:v>
+        <x:v>Valeurs assignées au passage ; lecture E facultative.</x:v>
       </x:c>
       <x:c r="M36" s="12" t="str">
-        <x:v>Deux saisons incompatibles sur une même photo.</x:v>
+        <x:v>Deux éléments météo différents dans le même cadre prouvent la contradiction.</x:v>
       </x:c>
       <x:c r="N36" s="12" t="str">
-        <x:v>Parapluie et neige lisibles même sans post-traitement.</x:v>
+        <x:v>Trois météos ordinaires ; la preuve repose sur leurs objets visibles, sans dépendre uniquement de la couleur.</x:v>
       </x:c>
       <x:c r="O36" s="12" t="str">
-        <x:v>Deux œuvres originales et masque de météo.</x:v>
+        <x:v>Image originale avec pluie/parapluie, flocons/neige ou disque solaire/rayons.</x:v>
       </x:c>
       <x:c r="P36" s="12" t="str">
         <x:v>paired_photo_weather</x:v>
@@ -10852,10 +13055,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R36" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S36" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T36" s="18" t="str">
         <x:v>—</x:v>
@@ -10866,8 +13069,11 @@
       <x:c r="V36" s="12" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="77" customHeight="1">
+      <x:c r="W36" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="11" t="str">
         <x:v>PX-032</x:v>
       </x:c>
@@ -10920,7 +13126,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R37" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S37" s="19" t="str">
         <x:v>Oui</x:v>
@@ -10933,6 +13139,9 @@
       </x:c>
       <x:c r="V37" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
+      </x:c>
+      <x:c r="W37" s="19" t="str">
+        <x:v>Oui</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="40" customHeight="1">
@@ -10988,7 +13197,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R38" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S38" s="18" t="str">
         <x:v>—</x:v>
@@ -11002,8 +13211,11 @@
       <x:c r="V38" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39" ht="40" customHeight="1">
+      <x:c r="W38" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="11" t="str">
         <x:v>PX-034</x:v>
       </x:c>
@@ -11014,40 +13226,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E39" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F39" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>Salon</x:v>
+        <x:v>Hôtel · bureau D2</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str">
-        <x:v>Les journaux portent la même date.</x:v>
+        <x:v>L’édition du journal peut être datée du 26 ou du 27 octobre 2026. Dans le même passage, tous doivent lire la même édition.</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str">
-        <x:v>Le journal est daté de demain.</x:v>
+        <x:v>Le Courrier de Saint-Clair porte deux dates différentes selon les perceptions.</x:v>
       </x:c>
       <x:c r="J39" s="11" t="str">
-        <x:v>Le journal est daté d’hier.</x:v>
+        <x:v>Il lit l’édition commune du passage.</x:v>
       </x:c>
       <x:c r="K39" s="11" t="str">
-        <x:v>Lire date et titre complet de la une.</x:v>
+        <x:v>Lisez la date complète sous le titre du journal ; les deux éditions sont plausibles prises isolément.</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
-        <x:v>Lecture volontaire.</x:v>
+        <x:v>Lecture volontaire persistante. L’agrandissement reste facultatif.</x:v>
       </x:c>
       <x:c r="M39" s="11" t="str">
-        <x:v>La différence de date au même emplacement est anormale.</x:v>
+        <x:v>Deux dates d’édition différentes au même emplacement confirment l’anomalie.</x:v>
       </x:c>
       <x:c r="N39" s="11" t="str">
-        <x:v>Une horloge de référence indique clairement la date attendue.</x:v>
+        <x:v>Ne pas utiliser hier/demain ni la date réelle de l’ordinateur. Un nouveau passage peut légitimement changer d’édition.</x:v>
       </x:c>
       <x:c r="O39" s="11" t="str">
-        <x:v>Une de journal fictionnel, deux versions.</x:v>
+        <x:v>Une de journal fictionnel, dates fixes lisibles et valeurs privées.</x:v>
       </x:c>
       <x:c r="P39" s="11" t="str">
         <x:v>paired_newspaper</x:v>
@@ -11056,10 +13268,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R39" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S39" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T39" s="19" t="str">
         <x:v>—</x:v>
@@ -11069,6 +13281,9 @@
       </x:c>
       <x:c r="V39" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
+      </x:c>
+      <x:c r="W39" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="40" customHeight="1">
@@ -11124,7 +13339,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R40" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S40" s="18" t="str">
         <x:v>—</x:v>
@@ -11138,8 +13353,11 @@
       <x:c r="V40" s="12" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41" ht="40" customHeight="1">
+      <x:c r="W40" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="11" t="str">
         <x:v>PX-036</x:v>
       </x:c>
@@ -11150,40 +13368,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E41" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F41" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>Bureau</x:v>
+        <x:v>Hôtel · bureau D2</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>Les formulaires possèdent un tampon cohérent.</x:v>
+        <x:v>Le dossier 09 peut porter VALIDÉ ou REFUSÉ ; les deux sont ordinaires entre passages, mais une même décision doit être visible par tous.</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str">
-        <x:v>Le dossier porte « VALIDÉ ».</x:v>
+        <x:v>Le même dossier est VALIDÉ pour certains inspecteurs et REFUSÉ pour les autres.</x:v>
       </x:c>
       <x:c r="J41" s="11" t="str">
-        <x:v>Le dossier porte « REFUSÉ ».</x:v>
+        <x:v>Il lit la décision commune du passage sur le dossier 09.</x:v>
       </x:c>
       <x:c r="K41" s="11" t="str">
-        <x:v>Épeler le tampon en citant le numéro du dossier.</x:v>
+        <x:v>Épelez la décision et le numéro du dossier. Ce document ne modifie jamais le protocole de vote.</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
-        <x:v>Interaction avec le classeur.</x:v>
+        <x:v>Lecture volontaire au bureau de contrôle.</x:v>
       </x:c>
       <x:c r="M41" s="11" t="str">
-        <x:v>Deux décisions opposées sur le même dossier sont anormales.</x:v>
+        <x:v>Deux décisions opposées et stables sur le même dossier constituent la preuve.</x:v>
       </x:c>
       <x:c r="N41" s="11" t="str">
-        <x:v>La fausse autorisation ne commande jamais la logique de jeu.</x:v>
+        <x:v>Le document ne commande ni les votes, ni les autorisations réseau, ni la progression.</x:v>
       </x:c>
       <x:c r="O41" s="11" t="str">
-        <x:v>Documents lisibles et tampons.</x:v>
+        <x:v>Document fictif original, tampons lisibles et variante privée.</x:v>
       </x:c>
       <x:c r="P41" s="11" t="str">
         <x:v>paired_stamp</x:v>
@@ -11192,10 +13410,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R41" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S41" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T41" s="19" t="str">
         <x:v>—</x:v>
@@ -11205,6 +13423,9 @@
       </x:c>
       <x:c r="V41" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
+      </x:c>
+      <x:c r="W41" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="40" customHeight="1">
@@ -11260,7 +13481,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R42" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S42" s="18" t="str">
         <x:v>—</x:v>
@@ -11273,6 +13494,9 @@
       </x:c>
       <x:c r="V42" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W42" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="40" customHeight="1">
@@ -11328,7 +13552,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R43" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S43" s="19" t="str">
         <x:v>—</x:v>
@@ -11341,6 +13565,9 @@
       </x:c>
       <x:c r="V43" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
+      </x:c>
+      <x:c r="W43" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="40" customHeight="1">
@@ -11396,7 +13623,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R44" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S44" s="18" t="str">
         <x:v>—</x:v>
@@ -11409,6 +13636,9 @@
       </x:c>
       <x:c r="V44" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W44" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="40" customHeight="1">
@@ -11464,7 +13694,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R45" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S45" s="19" t="str">
         <x:v>—</x:v>
@@ -11477,6 +13707,9 @@
       </x:c>
       <x:c r="V45" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W45" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="40" customHeight="1">
@@ -11532,7 +13765,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R46" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S46" s="18" t="str">
         <x:v>—</x:v>
@@ -11545,6 +13778,9 @@
       </x:c>
       <x:c r="V46" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W46" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="40" customHeight="1">
@@ -11600,7 +13836,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R47" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S47" s="19" t="str">
         <x:v>—</x:v>
@@ -11613,6 +13849,9 @@
       </x:c>
       <x:c r="V47" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W47" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="40" customHeight="1">
@@ -11668,7 +13907,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R48" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S48" s="18" t="str">
         <x:v>—</x:v>
@@ -11681,6 +13920,9 @@
       </x:c>
       <x:c r="V48" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W48" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="40" customHeight="1">
@@ -11736,7 +13978,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R49" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S49" s="19" t="str">
         <x:v>—</x:v>
@@ -11749,6 +13991,9 @@
       </x:c>
       <x:c r="V49" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W49" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="40" customHeight="1">
@@ -11804,7 +14049,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R50" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S50" s="18" t="str">
         <x:v>—</x:v>
@@ -11817,6 +14062,9 @@
       </x:c>
       <x:c r="V50" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W50" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="40" customHeight="1">
@@ -11872,7 +14120,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R51" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S51" s="19" t="str">
         <x:v>—</x:v>
@@ -11885,6 +14133,9 @@
       </x:c>
       <x:c r="V51" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W51" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="40" customHeight="1">
@@ -11940,7 +14191,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R52" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S52" s="18" t="str">
         <x:v>—</x:v>
@@ -11953,6 +14204,9 @@
       </x:c>
       <x:c r="V52" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W52" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="40" customHeight="1">
@@ -12008,7 +14262,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R53" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S53" s="19" t="str">
         <x:v>—</x:v>
@@ -12022,8 +14276,11 @@
       <x:c r="V53" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54" ht="40" customHeight="1">
+      <x:c r="W53" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
       <x:c r="A54" s="12" t="str">
         <x:v>PX-049</x:v>
       </x:c>
@@ -12034,40 +14291,40 @@
         <x:v>Physique</x:v>
       </x:c>
       <x:c r="D54" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E54" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F54" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G54" s="12" t="str">
-        <x:v>Bureau</x:v>
+        <x:v>Hôtel · table des objets témoins</x:v>
       </x:c>
       <x:c r="H54" s="12" t="str">
-        <x:v>Le sable tombe dans la chambre inférieure.</x:v>
+        <x:v>Les grains du sablier du poste 09 descendent dans la chambre inférieure.</x:v>
       </x:c>
       <x:c r="I54" s="12" t="str">
-        <x:v>Le sable remonte.</x:v>
+        <x:v>Les grains remontent vers la chambre supérieure.</x:v>
       </x:c>
       <x:c r="J54" s="12" t="str">
-        <x:v>Le sable tombe normalement.</x:v>
+        <x:v>Le sable continue de descendre.</x:v>
       </x:c>
       <x:c r="K54" s="12" t="str">
-        <x:v>Décrire le sens de circulation des grains.</x:v>
+        <x:v>Regardez le même grain sur une courte portion de sa trajectoire et comparez son sens.</x:v>
       </x:c>
       <x:c r="L54" s="12" t="str">
-        <x:v>Persistant après entrée.</x:v>
+        <x:v>Mouvement visible pendant l’inspection ; aucune collecte ni manipulation requise.</x:v>
       </x:c>
       <x:c r="M54" s="12" t="str">
         <x:v>Mouvement contraire à la gravité.</x:v>
       </x:c>
       <x:c r="N54" s="12" t="str">
-        <x:v>Un flux continu lisible remplace de minuscules grains isolés.</x:v>
+        <x:v>Conserver une vitesse lisible et la même direction à qualité réduite. Une image fixe ne suffit pas pour valider la preuve.</x:v>
       </x:c>
       <x:c r="O54" s="12" t="str">
-        <x:v>Sablier transparent et particules.</x:v>
+        <x:v>Sablier original translucide, flux animé continu et repère agrandi facultatif.</x:v>
       </x:c>
       <x:c r="P54" s="12" t="str">
         <x:v>sand_upward</x:v>
@@ -12076,10 +14333,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R54" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S54" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T54" s="18" t="str">
         <x:v>—</x:v>
@@ -12090,8 +14347,11 @@
       <x:c r="V54" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="55" ht="40" customHeight="1">
+      <x:c r="W54" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
       <x:c r="A55" s="11" t="str">
         <x:v>PX-050</x:v>
       </x:c>
@@ -12102,40 +14362,40 @@
         <x:v>Physique</x:v>
       </x:c>
       <x:c r="D55" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E55" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F55" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
-        <x:v>Tasse</x:v>
+        <x:v>Hôtel · table des objets témoins</x:v>
       </x:c>
       <x:c r="H55" s="11" t="str">
-        <x:v>La vapeur d’une tasse chaude monte doucement.</x:v>
+        <x:v>La vapeur de la tasse du poste 09 s’élève au-dessus du bord.</x:v>
       </x:c>
       <x:c r="I55" s="11" t="str">
-        <x:v>La vapeur descend sous la table.</x:v>
+        <x:v>La vapeur descend devant le meuble, jusqu’au-dessous de la tasse.</x:v>
       </x:c>
       <x:c r="J55" s="11" t="str">
-        <x:v>La vapeur monte.</x:v>
+        <x:v>La vapeur monte normalement.</x:v>
       </x:c>
       <x:c r="K55" s="11" t="str">
-        <x:v>Pointer la tasse puis suivre la courbe de vapeur.</x:v>
+        <x:v>Suivez la vapeur depuis le bord de la tasse et décrivez sa direction.</x:v>
       </x:c>
       <x:c r="L55" s="11" t="str">
-        <x:v>Approche de la table.</x:v>
+        <x:v>Mouvement persistant pendant l’inspection.</x:v>
       </x:c>
       <x:c r="M55" s="11" t="str">
         <x:v>La vapeur descendante confirme.</x:v>
       </x:c>
       <x:c r="N55" s="11" t="str">
-        <x:v>Version sans particules complexes disponible en qualité basse.</x:v>
+        <x:v>La qualité graphique doit conserver la direction. Le mouvement n’est pas un simple texte annonçant le diagnostic.</x:v>
       </x:c>
       <x:c r="O55" s="11" t="str">
-        <x:v>Tasse, vapeur volumétrique stylisée.</x:v>
+        <x:v>Tasse originale et animation de vapeur, simplifiable selon la qualité.</x:v>
       </x:c>
       <x:c r="P55" s="11" t="str">
         <x:v>steam_downward</x:v>
@@ -12144,10 +14404,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R55" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S55" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T55" s="19" t="str">
         <x:v>—</x:v>
@@ -12158,8 +14418,11 @@
       <x:c r="V55" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56" ht="77" customHeight="1">
+      <x:c r="W55" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
       <x:c r="A56" s="12" t="str">
         <x:v>PX-051</x:v>
       </x:c>
@@ -12212,7 +14475,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R56" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S56" s="18" t="str">
         <x:v>—</x:v>
@@ -12226,8 +14489,11 @@
       <x:c r="V56" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="57" ht="77" customHeight="1">
+      <x:c r="W56" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
       <x:c r="A57" s="11" t="str">
         <x:v>PX-052</x:v>
       </x:c>
@@ -12280,7 +14546,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R57" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S57" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12294,8 +14560,11 @@
       <x:c r="V57" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58" ht="40" customHeight="1">
+      <x:c r="W57" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
       <x:c r="A58" s="12" t="str">
         <x:v>PX-053</x:v>
       </x:c>
@@ -12306,16 +14575,16 @@
         <x:v>Organique</x:v>
       </x:c>
       <x:c r="D58" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E58" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F58" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G58" s="12" t="str">
-        <x:v>Porte</x:v>
+        <x:v>Seuil de la chambre 901</x:v>
       </x:c>
       <x:c r="H58" s="12" t="str">
         <x:v>Le seuil de la chambre reste libre.</x:v>
@@ -12324,22 +14593,22 @@
         <x:v>Des racines avancent sous la porte.</x:v>
       </x:c>
       <x:c r="J58" s="12" t="str">
-        <x:v>Aucune racine n’est visible.</x:v>
+        <x:v>Le seuil 901 reste libre de racines.</x:v>
       </x:c>
       <x:c r="K58" s="12" t="str">
         <x:v>Comparer le joint de seuil et le tapis voisin.</x:v>
       </x:c>
       <x:c r="L58" s="12" t="str">
-        <x:v>Croissance lente lors de l’inspection.</x:v>
+        <x:v>Racines présentes dès le passage, puis croissance lente depuis le seuil.</x:v>
       </x:c>
       <x:c r="M58" s="12" t="str">
-        <x:v>Les racines ajoutées constituent l’anomalie.</x:v>
+        <x:v>Des racines avancent sous la porte 901.</x:v>
       </x:c>
       <x:c r="N58" s="12" t="str">
-        <x:v>Les racines ne rendent jamais l’issue inaccessible.</x:v>
+        <x:v>Les racines restent latérales et ne rendent jamais l’issue inaccessible.</x:v>
       </x:c>
       <x:c r="O58" s="12" t="str">
-        <x:v>Courbes tubulaires et croissance locale.</x:v>
+        <x:v>Courbes tubulaires originales et croissance locale.</x:v>
       </x:c>
       <x:c r="P58" s="12" t="str">
         <x:v>root_under_door</x:v>
@@ -12348,10 +14617,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R58" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S58" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T58" s="18" t="str">
         <x:v>—</x:v>
@@ -12362,8 +14631,11 @@
       <x:c r="V58" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59" ht="40" customHeight="1">
+      <x:c r="W58" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
       <x:c r="A59" s="11" t="str">
         <x:v>PX-054</x:v>
       </x:c>
@@ -12374,16 +14646,16 @@
         <x:v>Physique</x:v>
       </x:c>
       <x:c r="D59" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E59" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F59" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
-        <x:v>Couloir</x:v>
+        <x:v>Panneau du couloir</x:v>
       </x:c>
       <x:c r="H59" s="11" t="str">
         <x:v>Aucune eau ne coule sur le mur.</x:v>
@@ -12392,22 +14664,22 @@
         <x:v>Des gouttes montent le long du panneau.</x:v>
       </x:c>
       <x:c r="J59" s="11" t="str">
-        <x:v>Le panneau est sec.</x:v>
+        <x:v>Le panneau reste sec.</x:v>
       </x:c>
       <x:c r="K59" s="11" t="str">
         <x:v>Observer un trajet complet de goutte.</x:v>
       </x:c>
       <x:c r="L59" s="11" t="str">
-        <x:v>Persistant à partir du début du tour.</x:v>
+        <x:v>Gouttes persistantes animées pendant le passage affecté.</x:v>
       </x:c>
       <x:c r="M59" s="11" t="str">
-        <x:v>Toute humidité ajoutée et ascendante confirme.</x:v>
+        <x:v>Le trajet complet d’une goutte va du bas vers le haut.</x:v>
       </x:c>
       <x:c r="N59" s="11" t="str">
-        <x:v>Pas de transparence dépendante d’un reflet avancé pour détecter.</x:v>
+        <x:v>Le mouvement et la présence d’eau suffisent ; pas de transparence avancée nécessaire.</x:v>
       </x:c>
       <x:c r="O59" s="11" t="str">
-        <x:v>Gouttes, roughness animée, traînée.</x:v>
+        <x:v>Gouttes originales et traces sur le panneau droit.</x:v>
       </x:c>
       <x:c r="P59" s="11" t="str">
         <x:v>water_up_wall</x:v>
@@ -12416,10 +14688,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R59" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S59" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T59" s="19" t="str">
         <x:v>—</x:v>
@@ -12430,8 +14702,11 @@
       <x:c r="V59" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="60" ht="40" customHeight="1">
+      <x:c r="W59" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
       <x:c r="A60" s="12" t="str">
         <x:v>PX-055</x:v>
       </x:c>
@@ -12442,16 +14717,16 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D60" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E60" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F60" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G60" s="12" t="str">
-        <x:v>Couloir</x:v>
+        <x:v>Couloir de Saint-Clair</x:v>
       </x:c>
       <x:c r="H60" s="12" t="str">
         <x:v>Le passage comporte quatre portes numérotées.</x:v>
@@ -12460,22 +14735,22 @@
         <x:v>Une cinquième porte apparaît entre deux panneaux.</x:v>
       </x:c>
       <x:c r="J60" s="12" t="str">
-        <x:v>Il en compte quatre.</x:v>
+        <x:v>Seules les quatre portes 901 à 904 sont présentes.</x:v>
       </x:c>
       <x:c r="K60" s="12" t="str">
         <x:v>Compter depuis l’entrée en alternant gauche puis droite.</x:v>
       </x:c>
       <x:c r="L60" s="12" t="str">
-        <x:v>À l’entrée du tour.</x:v>
+        <x:v>Pendant tout le passage affecté.</x:v>
       </x:c>
       <x:c r="M60" s="12" t="str">
-        <x:v>Une ouverture supplémentaire confirme.</x:v>
+        <x:v>Une cinquième porte 905 apparaît à droite vers la sortie.</x:v>
       </x:c>
       <x:c r="N60" s="12" t="str">
-        <x:v>La porte fantôme ne change pas le trajet physique commun.</x:v>
+        <x:v>Les quatre portes d’origine et le trajet commun restent en place ; aucune ouverture praticable supplémentaire.</x:v>
       </x:c>
       <x:c r="O60" s="12" t="str">
-        <x:v>Module de porte et panneau local.</x:v>
+        <x:v>Module original de porte 905 et panneau local.</x:v>
       </x:c>
       <x:c r="P60" s="12" t="str">
         <x:v>extra_door</x:v>
@@ -12484,10 +14759,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R60" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S60" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T60" s="18" t="str">
         <x:v>—</x:v>
@@ -12498,8 +14773,11 @@
       <x:c r="V60" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61" ht="77" customHeight="1">
+      <x:c r="W60" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
       <x:c r="A61" s="11" t="str">
         <x:v>PX-056</x:v>
       </x:c>
@@ -12552,7 +14830,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R61" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S61" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12565,6 +14843,9 @@
       </x:c>
       <x:c r="V61" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W61" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="40" customHeight="1">
@@ -12620,7 +14901,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R62" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S62" s="18" t="str">
         <x:v>—</x:v>
@@ -12633,6 +14914,9 @@
       </x:c>
       <x:c r="V62" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W62" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="40" customHeight="1">
@@ -12688,7 +14972,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R63" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S63" s="19" t="str">
         <x:v>—</x:v>
@@ -12702,8 +14986,11 @@
       <x:c r="V63" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64" ht="40" customHeight="1">
+      <x:c r="W63" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
       <x:c r="A64" s="12" t="str">
         <x:v>PX-059</x:v>
       </x:c>
@@ -12714,40 +15001,40 @@
         <x:v>Reflet</x:v>
       </x:c>
       <x:c r="D64" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E64" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F64" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G64" s="12" t="str">
-        <x:v>Miroir</x:v>
+        <x:v>Miroir de Saint-Clair</x:v>
       </x:c>
       <x:c r="H64" s="12" t="str">
-        <x:v>Le miroir ne montre aucune porte supplémentaire.</x:v>
+        <x:v>Le panneau situé en face du miroir ne porte aucune porte, dans la pièce ni dans son reflet.</x:v>
       </x:c>
       <x:c r="I64" s="12" t="str">
-        <x:v>Une porte existe dans le reflet derrière l’équipe.</x:v>
+        <x:v>Une porte supplémentaire apparaît uniquement dans le miroir de Saint-Clair.</x:v>
       </x:c>
       <x:c r="J64" s="12" t="str">
-        <x:v>Le miroir montre le panneau ordinaire.</x:v>
+        <x:v>Le miroir reflète le panneau sans porte supplémentaire.</x:v>
       </x:c>
       <x:c r="K64" s="12" t="str">
-        <x:v>Se retourner puis comparer le reflet.</x:v>
+        <x:v>Comparez le miroir puis le panneau réel en vous retournant. La porte du reflet n’existe pas dans la pièce.</x:v>
       </x:c>
       <x:c r="L64" s="12" t="str">
-        <x:v>Approche à moins de deux mètres.</x:v>
+        <x:v>Pendant tout le passage affecté ; visible seulement dans la passe du miroir de l’hôtel.</x:v>
       </x:c>
       <x:c r="M64" s="12" t="str">
-        <x:v>Porte absente de la pièce réelle mais présente dans le miroir.</x:v>
+        <x:v>Une porte est visible dans le miroir et absente du panneau réel.</x:v>
       </x:c>
       <x:c r="N64" s="12" t="str">
-        <x:v>Tester les angles extrêmes pour éviter de confondre clipping et anomalie.</x:v>
+        <x:v>La pièce réelle et le trajet commun ne changent pas ; angles extrêmes et clipping restent à vérifier sur GPU.</x:v>
       </x:c>
       <x:c r="O64" s="12" t="str">
-        <x:v>Scène de reflet dédiée.</x:v>
+        <x:v>Porte originale dessinée uniquement dans le reflet concerné.</x:v>
       </x:c>
       <x:c r="P64" s="12" t="str">
         <x:v>mirror_extra_door</x:v>
@@ -12756,10 +15043,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R64" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S64" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T64" s="18" t="str">
         <x:v>—</x:v>
@@ -12768,10 +15055,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="V64" s="12" t="str">
-        <x:v>Visuel / objet / espace</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="77" customHeight="1">
+        <x:v>Corps / reflet / mouvement</x:v>
+      </x:c>
+      <x:c r="W64" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
       <x:c r="A65" s="11" t="str">
         <x:v>PX-060</x:v>
       </x:c>
@@ -12824,7 +15114,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R65" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S65" s="19" t="str">
         <x:v>Oui</x:v>
@@ -12838,8 +15128,11 @@
       <x:c r="V65" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="66" ht="40" customHeight="1">
+      <x:c r="W65" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
       <x:c r="A66" s="12" t="str">
         <x:v>PX-061</x:v>
       </x:c>
@@ -12850,40 +15143,40 @@
         <x:v>Reflet</x:v>
       </x:c>
       <x:c r="D66" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E66" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F66" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G66" s="12" t="str">
-        <x:v>Miroir</x:v>
+        <x:v>Miroirs des quatre lieux</x:v>
       </x:c>
       <x:c r="H66" s="12" t="str">
-        <x:v>Les silhouettes de l’équipe sont représentées.</x:v>
+        <x:v>Le miroir montre votre corps et ceux des collègues présents. En solo, deux mannequins témoins numérotés permettent le même comptage.</x:v>
       </x:c>
       <x:c r="I66" s="12" t="str">
-        <x:v>Son miroir ne montre que lui.</x:v>
+        <x:v>Votre corps reste réfléchi, mais les collègues ou les mannequins témoins disparaissent uniquement du miroir.</x:v>
       </x:c>
       <x:c r="J66" s="12" t="str">
-        <x:v>Le miroir montre toute l’équipe.</x:v>
+        <x:v>Le miroir conserve le corps local et les collègues ou les deux mannequins témoins solo.</x:v>
       </x:c>
       <x:c r="K66" s="12" t="str">
-        <x:v>Compter les personnes devant et dans le miroir.</x:v>
+        <x:v>Comparez le nombre de silhouettes devant et dans le miroir ; les personnes et les socles restent dans la pièce.</x:v>
       </x:c>
       <x:c r="L66" s="12" t="str">
-        <x:v>Deux inspecteurs dans la zone de réflexion.</x:v>
+        <x:v>Pendant tout le passage affecté ; comparaison du groupe et de son reflet.</x:v>
       </x:c>
       <x:c r="M66" s="12" t="str">
-        <x:v>Le compte incohérent révèle l’anomalie.</x:v>
+        <x:v>Le corps local reste réfléchi alors que les autres silhouettes disparaissent du miroir.</x:v>
       </x:c>
       <x:c r="N66" s="12" t="str">
-        <x:v>Remplacer par mannequins témoins en entraînement solo.</x:v>
+        <x:v>Les corps physiques et socles restent visibles ; les témoins solo permettent de conclure sans ajouter de joueurs au roster.</x:v>
       </x:c>
       <x:c r="O66" s="12" t="str">
-        <x:v>Reflet par observateur, avatars simplifiés.</x:v>
+        <x:v>Masquage sélectif des reflets de pairs ; deux témoins numérotés en solo.</x:v>
       </x:c>
       <x:c r="P66" s="12" t="str">
         <x:v>reflection_no_team</x:v>
@@ -12892,19 +15185,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R66" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S66" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T66" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U66" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V66" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
+      </x:c>
+      <x:c r="W66" s="18" t="str">
+        <x:v>Oui</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="40" customHeight="1">
@@ -12960,7 +15256,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R67" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S67" s="19" t="str">
         <x:v>—</x:v>
@@ -12973,6 +15269,9 @@
       </x:c>
       <x:c r="V67" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W67" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="40" customHeight="1">
@@ -13028,7 +15327,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R68" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S68" s="18" t="str">
         <x:v>—</x:v>
@@ -13041,6 +15340,9 @@
       </x:c>
       <x:c r="V68" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W68" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="40" customHeight="1">
@@ -13096,7 +15398,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R69" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S69" s="19" t="str">
         <x:v>—</x:v>
@@ -13109,6 +15411,9 @@
       </x:c>
       <x:c r="V69" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W69" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="40" customHeight="1">
@@ -13164,7 +15469,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R70" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S70" s="18" t="str">
         <x:v>—</x:v>
@@ -13178,8 +15483,11 @@
       <x:c r="V70" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="71" ht="77" customHeight="1">
+      <x:c r="W70" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
       <x:c r="A71" s="11" t="str">
         <x:v>PX-066</x:v>
       </x:c>
@@ -13232,7 +15540,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R71" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S71" s="19" t="str">
         <x:v>Oui</x:v>
@@ -13245,6 +15553,9 @@
       </x:c>
       <x:c r="V71" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W71" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="40" customHeight="1">
@@ -13300,7 +15611,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R72" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S72" s="18" t="str">
         <x:v>—</x:v>
@@ -13314,8 +15625,11 @@
       <x:c r="V72" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="73" ht="40" customHeight="1">
+      <x:c r="W72" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
       <x:c r="A73" s="11" t="str">
         <x:v>PX-068</x:v>
       </x:c>
@@ -13326,16 +15640,16 @@
         <x:v>Organique</x:v>
       </x:c>
       <x:c r="D73" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E73" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F73" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
-        <x:v>Issue</x:v>
+        <x:v>Issue de Saint-Clair</x:v>
       </x:c>
       <x:c r="H73" s="11" t="str">
         <x:v>Le joint de la porte de sortie est fixe.</x:v>
@@ -13344,22 +15658,22 @@
         <x:v>Le joint s’écarte comme une respiration.</x:v>
       </x:c>
       <x:c r="J73" s="11" t="str">
-        <x:v>Le joint reste stable.</x:v>
+        <x:v>Le joint et le battant restent fixes.</x:v>
       </x:c>
       <x:c r="K73" s="11" t="str">
         <x:v>Observer le haut et le bas du battant pendant un cycle.</x:v>
       </x:c>
       <x:c r="L73" s="11" t="str">
-        <x:v>Approche du terminal.</x:v>
+        <x:v>Cycle lent pendant tout le passage affecté.</x:v>
       </x:c>
       <x:c r="M73" s="11" t="str">
-        <x:v>Le mouvement organique confirme.</x:v>
+        <x:v>Le joint s’écarte et se referme comme une respiration.</x:v>
       </x:c>
       <x:c r="N73" s="11" t="str">
-        <x:v>Le bouton de vote et l’évacuation restent accessibles.</x:v>
+        <x:v>Terminal de vote et évacuation demeurent accessibles.</x:v>
       </x:c>
       <x:c r="O73" s="11" t="str">
-        <x:v>Porte déformable, souffle sourd.</x:v>
+        <x:v>Battant et joint originaux animés ; aucun son requis pour conclure.</x:v>
       </x:c>
       <x:c r="P73" s="11" t="str">
         <x:v>exit_breath</x:v>
@@ -13368,10 +15682,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R73" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Contrôles de scène CPU : données, transformations, couches de reflet et accès. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S73" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T73" s="19" t="str">
         <x:v>—</x:v>
@@ -13382,8 +15696,11 @@
       <x:c r="V73" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="74" ht="40" customHeight="1">
+      <x:c r="W73" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
       <x:c r="A74" s="12" t="str">
         <x:v>PX-069</x:v>
       </x:c>
@@ -13394,40 +15711,40 @@
         <x:v>Mémoire</x:v>
       </x:c>
       <x:c r="D74" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E74" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F74" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G74" s="12" t="str">
-        <x:v>Réception</x:v>
+        <x:v>Galerie G9</x:v>
       </x:c>
       <x:c r="H74" s="12" t="str">
-        <x:v>La photo d’équipe montre des inconnus.</x:v>
+        <x:v>Le cadre ÉQUIPE DU SERVICE DE NUIT de G9 montre trois silhouettes signées A. MOREL / E. VIAL / N. ROCHER.</x:v>
       </x:c>
       <x:c r="I74" s="12" t="str">
-        <x:v>Il y découvre les pseudonymes de l’équipe actuelle.</x:v>
+        <x:v>Les signatures deviennent les indicatifs et pseudonymes actuels, et le nombre de silhouettes suit les membres présents.</x:v>
       </x:c>
       <x:c r="J74" s="12" t="str">
-        <x:v>Il voit les noms de la référence.</x:v>
+        <x:v>Le cadre garde les trois signatures fictives A. MOREL / E. VIAL / N. ROCHER.</x:v>
       </x:c>
       <x:c r="K74" s="12" t="str">
-        <x:v>Comparer la légende et le nombre de signatures.</x:v>
+        <x:v>Comparez le cadre ÉQUIPE de G9 et ses signatures avec la référence, sans confondre la photographie avec le vrai roster.</x:v>
       </x:c>
       <x:c r="L74" s="12" t="str">
-        <x:v>À partir d’un tour avancé.</x:v>
+        <x:v>Pendant tout le passage affecté ; le roster présent actualise la légende.</x:v>
       </x:c>
       <x:c r="M74" s="12" t="str">
-        <x:v>Une référence modifiée avec les noms actuels confirme.</x:v>
+        <x:v>Les signatures actuelles remplacent la référence fictive ; le nombre de silhouettes suit les présents.</x:v>
       </x:c>
       <x:c r="N74" s="12" t="str">
-        <x:v>Jamais de photos personnelles réelles des joueurs.</x:v>
+        <x:v>Aucune photo personnelle. Seuls les pseudonymes et indicatifs publics de la session sont utilisés ; le vrai roster reste exact.</x:v>
       </x:c>
       <x:c r="O74" s="12" t="str">
-        <x:v>Photo fictive, plaques nominatives.</x:v>
+        <x:v>Trois silhouettes de référence ; silhouettes et légende de session originales.</x:v>
       </x:c>
       <x:c r="P74" s="12" t="str">
         <x:v>wrong_team_photo</x:v>
@@ -13436,10 +15753,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R74" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S74" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T74" s="18" t="str">
         <x:v>—</x:v>
@@ -13450,8 +15767,11 @@
       <x:c r="V74" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="75" ht="40" customHeight="1">
+      <x:c r="W74" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
       <x:c r="A75" s="11" t="str">
         <x:v>PX-070</x:v>
       </x:c>
@@ -13462,40 +15782,40 @@
         <x:v>Mémoire</x:v>
       </x:c>
       <x:c r="D75" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E75" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F75" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
-        <x:v>Plan d’étage</x:v>
+        <x:v>Plan G9</x:v>
       </x:c>
       <x:c r="H75" s="11" t="str">
-        <x:v>Le plan contient toutes les portes de la référence.</x:v>
+        <x:v>Le plan G9 indique 901 à gauche et 902 à droite près de l’entrée, puis 903 à gauche et 904 à droite vers l’issue.</x:v>
       </x:c>
       <x:c r="I75" s="11" t="str">
-        <x:v>Une chambre manque sur le plan.</x:v>
+        <x:v>La chambre 903 et sa branche disparaissent du plan G9, tandis que la porte reste dans le couloir.</x:v>
       </x:c>
       <x:c r="J75" s="11" t="str">
-        <x:v>Le plan est complet.</x:v>
+        <x:v>Le plan présente ses quatre chambres et quatre branches.</x:v>
       </x:c>
       <x:c r="K75" s="11" t="str">
-        <x:v>Lire les chambres du plan et les comparer au couloir.</x:v>
+        <x:v>Lisez les quatre chambres sur le plan puis comparez la porte physique 903.</x:v>
       </x:c>
       <x:c r="L75" s="11" t="str">
-        <x:v>Lecture volontaire du plan.</x:v>
+        <x:v>Pendant tout le passage affecté ; lecture E facultative.</x:v>
       </x:c>
       <x:c r="M75" s="11" t="str">
-        <x:v>Une omission stable sur le même plan confirme.</x:v>
+        <x:v>La case 903 et sa branche manquent, alors que la porte 903 réelle demeure.</x:v>
       </x:c>
       <x:c r="N75" s="11" t="str">
-        <x:v>Permettre de zoomer le document et de fermer avec Échap.</x:v>
+        <x:v>Labels identiques aux quatre portes normales ; pas de modification de géométrie ni de collision du couloir.</x:v>
       </x:c>
       <x:c r="O75" s="11" t="str">
-        <x:v>Plan original lisible.</x:v>
+        <x:v>Plan original avec quatre chambres, branche 903 masquable et lecture agrandie.</x:v>
       </x:c>
       <x:c r="P75" s="11" t="str">
         <x:v>map_missing_room</x:v>
@@ -13504,10 +15824,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R75" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S75" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T75" s="19" t="str">
         <x:v>—</x:v>
@@ -13518,8 +15838,11 @@
       <x:c r="V75" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="76" ht="40" customHeight="1">
+      <x:c r="W75" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
       <x:c r="A76" s="12" t="str">
         <x:v>PX-071</x:v>
       </x:c>
@@ -13530,40 +15853,40 @@
         <x:v>Texte</x:v>
       </x:c>
       <x:c r="D76" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E76" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F76" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G76" s="12" t="str">
-        <x:v>Panneau</x:v>
+        <x:v>Archives R9</x:v>
       </x:c>
       <x:c r="H76" s="12" t="str">
-        <x:v>Le panneau diégétique demande de signaler les anomalies.</x:v>
+        <x:v>Le règlement R9 de Saint-Clair indique SIGNALEZ TOUTE ANOMALIE.</x:v>
       </x:c>
       <x:c r="I76" s="12" t="str">
-        <x:v>Il conseille soudain de ne rien signaler.</x:v>
+        <x:v>Le panneau R9 indique NE SIGNALEZ AUCUNE ANOMALIE. Les règles fiables de l’interface ne changent pas.</x:v>
       </x:c>
       <x:c r="J76" s="12" t="str">
-        <x:v>Le règlement de référence est intact.</x:v>
+        <x:v>Le panneau garde SIGNALEZ TOUTE ANOMALIE.</x:v>
       </x:c>
       <x:c r="K76" s="12" t="str">
-        <x:v>Lire la phrase et vérifier la règle permanente de l’interface.</x:v>
+        <x:v>Lisez la phrase du panneau et comparez-la avec la règle permanente : une anomalie observée suffit.</x:v>
       </x:c>
       <x:c r="L76" s="12" t="str">
-        <x:v>À l’entrée du tour.</x:v>
+        <x:v>Pendant tout le passage affecté.</x:v>
       </x:c>
       <x:c r="M76" s="12" t="str">
-        <x:v>Une consigne contradictoire dans le décor est une anomalie.</x:v>
+        <x:v>Le panneau du décor contredit la règle fiable de l’interface.</x:v>
       </x:c>
       <x:c r="N76" s="12" t="str">
-        <x:v>L’interface réelle maintient toujours la règle fiable.</x:v>
+        <x:v>La règle et les commandes de vote de l’interface demeurent fiables.</x:v>
       </x:c>
       <x:c r="O76" s="12" t="str">
-        <x:v>Panneau de règlement alternatif.</x:v>
+        <x:v>Panneau original avec phrase alternative et lecture agrandie.</x:v>
       </x:c>
       <x:c r="P76" s="12" t="str">
         <x:v>rules_swap</x:v>
@@ -13572,10 +15895,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R76" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S76" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T76" s="18" t="str">
         <x:v>—</x:v>
@@ -13586,8 +15909,11 @@
       <x:c r="V76" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="77" ht="40" customHeight="1">
+      <x:c r="W76" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
       <x:c r="A77" s="11" t="str">
         <x:v>PX-072</x:v>
       </x:c>
@@ -13598,40 +15924,40 @@
         <x:v>Relation</x:v>
       </x:c>
       <x:c r="D77" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E77" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F77" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
-        <x:v>Réception</x:v>
+        <x:v>Archives R9</x:v>
       </x:c>
       <x:c r="H77" s="11" t="str">
-        <x:v>L’afficheur annonce le nombre de joueurs présents.</x:v>
+        <x:v>L’afficheur R9 PRÉSENTS correspond au nombre de membres présents, soit un inspecteur en entraînement solo.</x:v>
       </x:c>
       <x:c r="I77" s="11" t="str">
-        <x:v>Il annonce un occupant de plus.</x:v>
+        <x:v>L’afficheur R9 ajoute un occupant au nombre réellement présent, sans changer le compteur de connexion.</x:v>
       </x:c>
       <x:c r="J77" s="11" t="str">
-        <x:v>Il annonce le nombre correct.</x:v>
+        <x:v>Le panneau indique le nombre exact de membres présents.</x:v>
       </x:c>
       <x:c r="K77" s="11" t="str">
-        <x:v>Compter les membres connectés et lire l’afficheur.</x:v>
+        <x:v>Comparez le chiffre du panneau avec les membres présents au même moment.</x:v>
       </x:c>
       <x:c r="L77" s="11" t="str">
-        <x:v>Après fermeture du salon.</x:v>
+        <x:v>Pendant tout le passage affecté ; recalcul à chaque changement du roster présent.</x:v>
       </x:c>
       <x:c r="M77" s="11" t="str">
-        <x:v>Un décompte diégétique trop élevé confirme.</x:v>
+        <x:v>PRÉSENTS est supérieur de un au nombre réellement présent au même instant.</x:v>
       </x:c>
       <x:c r="N77" s="11" t="str">
-        <x:v>Ne jamais modifier le vrai compteur de connexion.</x:v>
+        <x:v>Exclure les déconnectés et le témoin fictif solo ; ne jamais modifier le compteur de connexion.</x:v>
       </x:c>
       <x:c r="O77" s="11" t="str">
-        <x:v>Compteur lumineux et état serveur.</x:v>
+        <x:v>Afficheur original local et lecture agrandie, dérivés du roster public.</x:v>
       </x:c>
       <x:c r="P77" s="11" t="str">
         <x:v>guest_tally</x:v>
@@ -13640,10 +15966,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R77" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>13 tests d’inspection : données privées, meshes, lectures et roster. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S77" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T77" s="19" t="str">
         <x:v>—</x:v>
@@ -13654,8 +15980,11 @@
       <x:c r="V77" s="11" t="str">
         <x:v>Comparaison entre témoins</x:v>
       </x:c>
-    </x:row>
-    <x:row r="78" ht="40" customHeight="1">
+      <x:c r="W77" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
       <x:c r="A78" s="12" t="str">
         <x:v>PX-073</x:v>
       </x:c>
@@ -13666,40 +15995,40 @@
         <x:v>Duplication</x:v>
       </x:c>
       <x:c r="D78" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E78" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F78" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G78" s="12" t="str">
-        <x:v>Réception</x:v>
+        <x:v>Hôtel · râtelier de contrôle</x:v>
       </x:c>
       <x:c r="H78" s="12" t="str">
-        <x:v>Une seule clé 09 pend au râtelier.</x:v>
+        <x:v>Une seule clé portant 09 est suspendue au râtelier du poste 09.</x:v>
       </x:c>
       <x:c r="I78" s="12" t="str">
-        <x:v>Deux clés 09 sont présentes.</x:v>
+        <x:v>Une seconde clé 09 apparaît sur un autre crochet.</x:v>
       </x:c>
       <x:c r="J78" s="12" t="str">
-        <x:v>Il n’en voit qu’une.</x:v>
+        <x:v>Une seule clé 09 reste présente.</x:v>
       </x:c>
       <x:c r="K78" s="12" t="str">
-        <x:v>Compter et lire les étiquettes depuis gauche à droite.</x:v>
+        <x:v>Comptez les clés et lisez leur numéro plutôt que les crochets vides.</x:v>
       </x:c>
       <x:c r="L78" s="12" t="str">
-        <x:v>À l’entrée du tour.</x:v>
+        <x:v>Visible dès le début du passage ; lecture agrandie facultative.</x:v>
       </x:c>
       <x:c r="M78" s="12" t="str">
         <x:v>La duplication d’un identifiant unique confirme.</x:v>
       </x:c>
       <x:c r="N78" s="12" t="str">
-        <x:v>Aucun ramassage obligatoire et aucune perte de clé logique.</x:v>
+        <x:v>Aucun ramassage, inventaire ou accès à débloquer. La duplication visuelle ne retire aucune clé logique.</x:v>
       </x:c>
       <x:c r="O78" s="12" t="str">
-        <x:v>Clés haute définition et étiquettes.</x:v>
+        <x:v>Clés originales et étiquettes lisibles.</x:v>
       </x:c>
       <x:c r="P78" s="12" t="str">
         <x:v>same_key_twice</x:v>
@@ -13708,10 +16037,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R78" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S78" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T78" s="18" t="str">
         <x:v>—</x:v>
@@ -13721,6 +16050,9 @@
       </x:c>
       <x:c r="V78" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W78" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="40" customHeight="1">
@@ -13776,7 +16108,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R79" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S79" s="19" t="str">
         <x:v>—</x:v>
@@ -13789,6 +16121,9 @@
       </x:c>
       <x:c r="V79" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W79" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="40" customHeight="1">
@@ -13844,7 +16179,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R80" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S80" s="18" t="str">
         <x:v>—</x:v>
@@ -13858,8 +16193,11 @@
       <x:c r="V80" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="81" ht="40" customHeight="1">
+      <x:c r="W80" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="51" customHeight="1">
       <x:c r="A81" s="11" t="str">
         <x:v>PX-076</x:v>
       </x:c>
@@ -13870,40 +16208,40 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D81" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E81" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F81" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G81" s="11" t="str">
-        <x:v>Chalet futur</x:v>
+        <x:v>Chalet de service</x:v>
       </x:c>
       <x:c r="H81" s="11" t="str">
-        <x:v>La table laisse un passage égal des deux côtés.</x:v>
+        <x:v>La table a quatre pieds et un plateau de 2,10 m sur 1,40 m. Des espaces la séparent des murs ; la tasse et le carnet reposent dessus.</x:v>
       </x:c>
       <x:c r="I81" s="11" t="str">
-        <x:v>La table s’étend jusqu’au mur.</x:v>
+        <x:v>Le plateau rejoint le mur gauche tandis que son bord droit reste près du garde-corps.</x:v>
       </x:c>
       <x:c r="J81" s="11" t="str">
-        <x:v>Le mobilier conserve sa taille.</x:v>
+        <x:v>La table garde son plateau de 2,10 m sur 1,40 m.</x:v>
       </x:c>
       <x:c r="K81" s="11" t="str">
-        <x:v>Comparer nombre de pieds et distance au foyer.</x:v>
+        <x:v>Comparez le bord gauche du plateau et le mur depuis le même garde-corps ; le passage de droite reste commun.</x:v>
       </x:c>
       <x:c r="L81" s="11" t="str">
-        <x:v>Après retour dans la pièce principale.</x:v>
+        <x:v>Pendant tout le passage affecté ; comparer depuis le garde-corps.</x:v>
       </x:c>
       <x:c r="M81" s="11" t="str">
-        <x:v>Un meuble agrandi localement confirme.</x:v>
+        <x:v>Le bord gauche atteint le mur, contrairement au passage de référence.</x:v>
       </x:c>
       <x:c r="N81" s="11" t="str">
-        <x:v>Trajet commun conservé. Extension non présente dans le premier niveau.</x:v>
+        <x:v>Le trajet de droite et son volume de collision restent communs ; ni tasse ni carnet ne sont déplacés. Chalet disponible en mode autonome.</x:v>
       </x:c>
       <x:c r="O81" s="11" t="str">
-        <x:v>Module chalet, table paramétrique.</x:v>
+        <x:v>Table originale paramétrique, quatre pieds, tasse, carnet et garde-corps.</x:v>
       </x:c>
       <x:c r="P81" s="11" t="str">
         <x:v>cabine_table_size</x:v>
@@ -13912,7 +16250,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R81" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>9 tests chalet : géométrie, collisions, repères et états. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S81" s="19" t="str">
         <x:v>—</x:v>
@@ -13926,8 +16264,11 @@
       <x:c r="V81" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="82" ht="40" customHeight="1">
+      <x:c r="W81" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="51" customHeight="1">
       <x:c r="A82" s="12" t="str">
         <x:v>PX-077</x:v>
       </x:c>
@@ -13938,40 +16279,40 @@
         <x:v>Entité</x:v>
       </x:c>
       <x:c r="D82" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E82" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F82" s="16" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="G82" s="12" t="str">
-        <x:v>Chalet futur</x:v>
+        <x:v>Chalet de service</x:v>
       </x:c>
       <x:c r="H82" s="12" t="str">
-        <x:v>La cheminée est vide et éteinte.</x:v>
+        <x:v>La cheminée du mur droit est éteinte ; son conduit est vide, sans visage ni yeux.</x:v>
       </x:c>
       <x:c r="I82" s="12" t="str">
-        <x:v>Un visage apparaît au fond du conduit.</x:v>
+        <x:v>Un visage immobile et deux yeux apparaissent au fond du conduit froid.</x:v>
       </x:c>
       <x:c r="J82" s="12" t="str">
-        <x:v>Le conduit reste vide.</x:v>
+        <x:v>Le conduit reste froid et vide.</x:v>
       </x:c>
       <x:c r="K82" s="12" t="str">
-        <x:v>Observer depuis la limite du tapis et décrire les yeux.</x:v>
+        <x:v>Depuis le bord du tapis, comparez le fond du foyer. Il est inutile d’entrer dans la cheminée.</x:v>
       </x:c>
       <x:c r="L82" s="12" t="str">
-        <x:v>Approche du foyer.</x:v>
+        <x:v>Pendant tout le passage affecté ; observation du foyer.</x:v>
       </x:c>
       <x:c r="M82" s="12" t="str">
-        <x:v>La présence confirme sans entrer ni toucher.</x:v>
+        <x:v>Le visage immobile et ses deux yeux sont présents dans le conduit de l’observateur.</x:v>
       </x:c>
       <x:c r="N82" s="12" t="str">
-        <x:v>Aucune attaque obligatoire, alternative de peur réduite.</x:v>
+        <x:v>Observation depuis le tapis ; aucune attaque, aucun contact ni entrée dans la cheminée nécessaires.</x:v>
       </x:c>
       <x:c r="O82" s="12" t="str">
-        <x:v>Cheminée détaillée et visage original.</x:v>
+        <x:v>Cheminée originale, foyer creux et visage de géométrie originale.</x:v>
       </x:c>
       <x:c r="P82" s="12" t="str">
         <x:v>cabine_chimney_face</x:v>
@@ -13980,7 +16321,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R82" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>9 tests chalet : géométrie, collisions, repères et états. 25 contrôles de scène couvrent effets et reset. Rendu GPU et lisibilité sur écran non validés.</x:v>
       </x:c>
       <x:c r="S82" s="18" t="str">
         <x:v>—</x:v>
@@ -13994,8 +16335,11 @@
       <x:c r="V82" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="83" ht="77" customHeight="1">
+      <x:c r="W82" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
       <x:c r="A83" s="11" t="str">
         <x:v>PX-078</x:v>
       </x:c>
@@ -14048,7 +16392,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R83" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S83" s="19" t="str">
         <x:v>—</x:v>
@@ -14062,8 +16406,11 @@
       <x:c r="V83" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="84" ht="77" customHeight="1">
+      <x:c r="W83" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
       <x:c r="A84" s="12" t="str">
         <x:v>PX-079</x:v>
       </x:c>
@@ -14116,7 +16463,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R84" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S84" s="18" t="str">
         <x:v>—</x:v>
@@ -14129,6 +16476,9 @@
       </x:c>
       <x:c r="V84" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W84" s="18" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="40" customHeight="1">
@@ -14184,7 +16534,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R85" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Spécification originale ; effet absent du catalogue runtime v0.4.0.</x:v>
       </x:c>
       <x:c r="S85" s="19" t="str">
         <x:v>—</x:v>
@@ -14198,8 +16548,11 @@
       <x:c r="V85" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86" ht="77" customHeight="1">
+      <x:c r="W85" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64" customHeight="1">
       <x:c r="A86" s="12" t="str">
         <x:v>PX-081</x:v>
       </x:c>
@@ -14252,7 +16605,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R86" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S86" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14266,8 +16619,11 @@
       <x:c r="V86" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="87" ht="77" customHeight="1">
+      <x:c r="W86" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64" customHeight="1">
       <x:c r="A87" s="11" t="str">
         <x:v>PX-082</x:v>
       </x:c>
@@ -14320,7 +16676,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R87" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S87" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14334,8 +16690,11 @@
       <x:c r="V87" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88" ht="77" customHeight="1">
+      <x:c r="W87" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
       <x:c r="A88" s="12" t="str">
         <x:v>PX-083</x:v>
       </x:c>
@@ -14388,7 +16747,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R88" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S88" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14402,8 +16761,11 @@
       <x:c r="V88" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="89" ht="77" customHeight="1">
+      <x:c r="W88" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
       <x:c r="A89" s="11" t="str">
         <x:v>PX-084</x:v>
       </x:c>
@@ -14456,7 +16818,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R89" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S89" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14470,8 +16832,11 @@
       <x:c r="V89" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="90" ht="77" customHeight="1">
+      <x:c r="W89" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="64" customHeight="1">
       <x:c r="A90" s="12" t="str">
         <x:v>PX-085</x:v>
       </x:c>
@@ -14524,7 +16889,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R90" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S90" s="18" t="str">
         <x:v>Oui</x:v>
@@ -14538,8 +16903,11 @@
       <x:c r="V90" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="91" ht="77" customHeight="1">
+      <x:c r="W90" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="64" customHeight="1">
       <x:c r="A91" s="11" t="str">
         <x:v>PX-086</x:v>
       </x:c>
@@ -14559,31 +16927,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
-        <x:v>Relais du décor</x:v>
+        <x:v>Talkie de votre inspecteur</x:v>
       </x:c>
       <x:c r="H91" s="11" t="str">
-        <x:v>Le voyant du relais reste dans son état de référence.</x:v>
+        <x:v>Le talkie tenu par votre corps d’inspecteur garde un écran et une diode verts, même lorsque le microphone est éteint.</x:v>
       </x:c>
       <x:c r="I91" s="11" t="str">
-        <x:v>Le relais produit une lumière de signal inhabituelle dans une perception.</x:v>
+        <x:v>Le talkie physique de votre inspecteur se lève, son écran et sa diode deviennent rouges, sans activation réelle du microphone.</x:v>
       </x:c>
       <x:c r="J91" s="11" t="str">
-        <x:v>L’afficheur de l’appareil reste normal.</x:v>
+        <x:v>Le talkie corporel garde son écran et sa diode verts.</x:v>
       </x:c>
       <x:c r="K91" s="11" t="str">
-        <x:v>Comparez les voyants du même appareil sans confondre le voyant du micro personnel.</x:v>
+        <x:v>Comparez la couleur du talkie dans vos mains ou dans le miroir. Le témoin de microphone de l’interface reste une information technique fiable.</x:v>
       </x:c>
       <x:c r="L91" s="11" t="str">
         <x:v>Couche visuelle active pendant le passage.</x:v>
       </x:c>
       <x:c r="M91" s="11" t="str">
-        <x:v>Une indication diégétique incompatible avec la référence confirme.</x:v>
+        <x:v>Écran et diode rouges sur le modèle corporel ; état microphone réel inchangé.</x:v>
       </x:c>
       <x:c r="N91" s="11" t="str">
-        <x:v>L’état de connexion réel et l’autorisation micro sont affichés séparément et ne sont jamais falsifiés.</x:v>
+        <x:v>Effet visuel, exclu des douze profils radio. Aucun prompt micro ni falsification de l’état technique du navigateur.</x:v>
       </x:c>
       <x:c r="O91" s="11" t="str">
-        <x:v>Relais modélisé et voyant lumineux privé ; repère partagé.</x:v>
+        <x:v>Talkie 3D de l’inspecteur, écran et diode locaux, posture radio.</x:v>
       </x:c>
       <x:c r="P91" s="11" t="str">
         <x:v>radio_signal</x:v>
@@ -14592,7 +16960,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R91" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S91" s="19" t="str">
         <x:v>Oui</x:v>
@@ -14606,8 +16974,11 @@
       <x:c r="V91" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="92" ht="77" customHeight="1">
+      <x:c r="W91" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="64" customHeight="1">
       <x:c r="A92" s="12" t="str">
         <x:v>PX-087</x:v>
       </x:c>
@@ -14660,7 +17031,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R92" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S92" s="18" t="str">
         <x:v>—</x:v>
@@ -14674,8 +17045,11 @@
       <x:c r="V92" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="93" ht="77" customHeight="1">
+      <x:c r="W92" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="64" customHeight="1">
       <x:c r="A93" s="11" t="str">
         <x:v>PX-088</x:v>
       </x:c>
@@ -14728,7 +17102,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R93" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S93" s="19" t="str">
         <x:v>—</x:v>
@@ -14742,8 +17116,11 @@
       <x:c r="V93" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="94" ht="77" customHeight="1">
+      <x:c r="W93" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="64" customHeight="1">
       <x:c r="A94" s="12" t="str">
         <x:v>PX-089</x:v>
       </x:c>
@@ -14796,7 +17173,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R94" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S94" s="18" t="str">
         <x:v>—</x:v>
@@ -14810,8 +17187,11 @@
       <x:c r="V94" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="95" ht="77" customHeight="1">
+      <x:c r="W94" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="64" customHeight="1">
       <x:c r="A95" s="11" t="str">
         <x:v>PX-090</x:v>
       </x:c>
@@ -14864,7 +17244,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R95" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S95" s="19" t="str">
         <x:v>—</x:v>
@@ -14878,8 +17258,11 @@
       <x:c r="V95" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96" ht="77" customHeight="1">
+      <x:c r="W95" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="64" customHeight="1">
       <x:c r="A96" s="12" t="str">
         <x:v>PX-091</x:v>
       </x:c>
@@ -14932,7 +17315,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R96" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S96" s="18" t="str">
         <x:v>—</x:v>
@@ -14946,8 +17329,11 @@
       <x:c r="V96" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="97" ht="77" customHeight="1">
+      <x:c r="W96" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="64" customHeight="1">
       <x:c r="A97" s="11" t="str">
         <x:v>PX-092</x:v>
       </x:c>
@@ -15000,7 +17386,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R97" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S97" s="19" t="str">
         <x:v>—</x:v>
@@ -15014,8 +17400,11 @@
       <x:c r="V97" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="98" ht="77" customHeight="1">
+      <x:c r="W97" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="64" customHeight="1">
       <x:c r="A98" s="12" t="str">
         <x:v>PX-093</x:v>
       </x:c>
@@ -15068,7 +17457,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R98" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S98" s="18" t="str">
         <x:v>—</x:v>
@@ -15082,8 +17471,11 @@
       <x:c r="V98" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="99" ht="77" customHeight="1">
+      <x:c r="W98" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="64" customHeight="1">
       <x:c r="A99" s="11" t="str">
         <x:v>PX-094</x:v>
       </x:c>
@@ -15136,7 +17528,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R99" s="11" t="str">
-        <x:v>Preuves v0.2 conservées : ID intégré au catalogue et aux règles. 17 tests de règles couvrent les 54 cas ; 11 suites CPU couvrent 48 preuves visuelles et leur reset. Pixels, shaders, reflet final et FPS restent à tester sur GPU réel.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S99" s="19" t="str">
         <x:v>—</x:v>
@@ -15150,8 +17542,11 @@
       <x:c r="V99" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="100" ht="77" customHeight="1">
+      <x:c r="W99" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="64" customHeight="1">
       <x:c r="A100" s="12" t="str">
         <x:v>PX-095</x:v>
       </x:c>
@@ -15204,7 +17599,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R100" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S100" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15218,8 +17613,11 @@
       <x:c r="V100" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="101" ht="77" customHeight="1">
+      <x:c r="W100" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="64" customHeight="1">
       <x:c r="A101" s="11" t="str">
         <x:v>PX-096</x:v>
       </x:c>
@@ -15272,7 +17670,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R101" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S101" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15286,8 +17684,11 @@
       <x:c r="V101" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="102" ht="77" customHeight="1">
+      <x:c r="W101" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="64" customHeight="1">
       <x:c r="A102" s="12" t="str">
         <x:v>PX-097</x:v>
       </x:c>
@@ -15340,7 +17741,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R102" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S102" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15354,8 +17755,11 @@
       <x:c r="V102" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="103" ht="77" customHeight="1">
+      <x:c r="W102" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="64" customHeight="1">
       <x:c r="A103" s="11" t="str">
         <x:v>PX-098</x:v>
       </x:c>
@@ -15408,7 +17812,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R103" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S103" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15422,8 +17826,11 @@
       <x:c r="V103" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="104" ht="77" customHeight="1">
+      <x:c r="W103" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="64" customHeight="1">
       <x:c r="A104" s="12" t="str">
         <x:v>PX-099</x:v>
       </x:c>
@@ -15476,7 +17883,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R104" s="12" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S104" s="18" t="str">
         <x:v>Oui</x:v>
@@ -15490,8 +17897,11 @@
       <x:c r="V104" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="105" ht="77" customHeight="1">
+      <x:c r="W104" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="64" customHeight="1">
       <x:c r="A105" s="11" t="str">
         <x:v>PX-100</x:v>
       </x:c>
@@ -15544,7 +17954,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R105" s="11" t="str">
-        <x:v>Réception WebAudio et calibration déterministe intégrées. 19 tests radio réussis, dont relevés sans micro/réseau, PTT, consentement et annulation des demandes micro obsolètes. Écoute humaine, microphones physiques et TURN réel restent à éprouver.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S105" s="19" t="str">
         <x:v>Oui</x:v>
@@ -15558,8 +17968,11 @@
       <x:c r="V105" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="106" ht="51" customHeight="1">
+      <x:c r="W105" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="64" customHeight="1">
       <x:c r="A106" s="12" t="str">
         <x:v>PX-101</x:v>
       </x:c>
@@ -15570,10 +17983,10 @@
         <x:v>Radio audio</x:v>
       </x:c>
       <x:c r="D106" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E106" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F106" s="16" t="n">
         <x:v>2</x:v>
@@ -15582,28 +17995,28 @@
         <x:v>Talkie</x:v>
       </x:c>
       <x:c r="H106" s="12" t="str">
-        <x:v>Un clic d’ouverture et un clic de fermeture encadrent le test.</x:v>
+        <x:v>Un clic d’ouverture et un clic de fermeture encadrent l’identifiant RELAIS puis la séquence principale 1, 2, 3.</x:v>
       </x:c>
       <x:c r="I106" s="12" t="str">
-        <x:v>Le clic de fermeture manque malgré la fin confirmée du test.</x:v>
+        <x:v>Le clic final manque après la séquence principale.</x:v>
       </x:c>
       <x:c r="J106" s="12" t="str">
-        <x:v>Il entend les deux clics.</x:v>
+        <x:v>Il reçoit les deux clics habituels.</x:v>
       </x:c>
       <x:c r="K106" s="12" t="str">
-        <x:v>Décrire début et fin sur deux essais successifs.</x:v>
+        <x:v>Comparer ouverture, code, séquence principale et fermeture sur deux essais.</x:v>
       </x:c>
       <x:c r="L106" s="12" t="str">
-        <x:v>Étalonnage volontaire futur.</x:v>
+        <x:v>Bouton Étalonner, disponible indépendamment du microphone et des partenaires.</x:v>
       </x:c>
       <x:c r="M106" s="12" t="str">
         <x:v>L’absence reproductible d’un clic de référence constitue une anomalie légère.</x:v>
       </x:c>
       <x:c r="N106" s="12" t="str">
-        <x:v>L’icône réelle de transmission doit s’éteindre normalement pour ne pas suggérer un micro encore ouvert.</x:v>
+        <x:v>L’état de transmission réel s’éteint normalement. L’absence fictionnelle du clic n’indique jamais un microphone encore ouvert.</x:v>
       </x:c>
       <x:c r="O106" s="12" t="str">
-        <x:v>Squelch distinct début/fin, état factuel et transcription.</x:v>
+        <x:v>Clics synthétiques originaux et relevé écrit de début / fin.</x:v>
       </x:c>
       <x:c r="P106" s="12" t="str">
         <x:v>radio_no_squelch</x:v>
@@ -15612,22 +18025,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R106" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S106" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T106" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U106" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V106" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="107" ht="51" customHeight="1">
+      <x:c r="W106" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="64" customHeight="1">
       <x:c r="A107" s="11" t="str">
         <x:v>PX-102</x:v>
       </x:c>
@@ -15638,10 +18054,10 @@
         <x:v>Radio relationnelle</x:v>
       </x:c>
       <x:c r="D107" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E107" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F107" s="17" t="n">
         <x:v>3</x:v>
@@ -15650,52 +18066,55 @@
         <x:v>Talkie et panneau relais</x:v>
       </x:c>
       <x:c r="H107" s="11" t="str">
-        <x:v>Le test du talkie recopie les quatre chiffres du relais du passage.</x:v>
+        <x:v>Les quatre chiffres DTMF synthétiques du test et leur relevé correspondent au code du panneau RELAIS du même passage.</x:v>
       </x:c>
       <x:c r="I107" s="11" t="str">
-        <x:v>Le code parlé par le test diffère de son propre afficheur.</x:v>
+        <x:v>Le test encode un code à quatre chiffres qui ne correspond pas à son propre panneau RELAIS.</x:v>
       </x:c>
       <x:c r="J107" s="11" t="str">
-        <x:v>Son test correspond à son afficheur.</x:v>
+        <x:v>Son test et son panneau affichent les mêmes quatre chiffres.</x:v>
       </x:c>
       <x:c r="K107" s="11" t="str">
-        <x:v>Un inspecteur lit le panneau, l’autre répète la séquence synthétique reçue, puis échange les rôles.</x:v>
+        <x:v>Lire le panneau RELAIS puis le code du relevé de calibration ; comparer les quatre positions sans confondre avec les tons 1, 2, 3.</x:v>
       </x:c>
       <x:c r="L107" s="11" t="str">
-        <x:v>Étalonnage croisé futur.</x:v>
+        <x:v>Étalonnage volontaire du passage courant.</x:v>
       </x:c>
       <x:c r="M107" s="11" t="str">
-        <x:v>Une divergence entre l’appareil et son panneau de référence confirme.</x:v>
+        <x:v>La contradiction appareil / panneau confirme même si personne ne parle.</x:v>
       </x:c>
       <x:c r="N107" s="11" t="str">
-        <x:v>Aucune reconnaissance de voix ni utilisation de fichiers audio personnels.</x:v>
+        <x:v>Pas de voix parlée, de reconnaissance ou de clonage vocal. Les chiffres d’identification précèdent une section distincte de trois tons.</x:v>
       </x:c>
       <x:c r="O107" s="11" t="str">
-        <x:v>Synthèse de chiffres originaux, code de passage et texte accessible.</x:v>
+        <x:v>Doubles tonalités téléphoniques synthétiques originales et transcription des quatre chiffres.</x:v>
       </x:c>
       <x:c r="P107" s="11" t="str">
         <x:v>radio_countercode</x:v>
       </x:c>
       <x:c r="Q107" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R107" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S107" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T107" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U107" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V107" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="108" ht="51" customHeight="1">
+      <x:c r="W107" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="64" customHeight="1">
       <x:c r="A108" s="12" t="str">
         <x:v>PX-103</x:v>
       </x:c>
@@ -15706,10 +18125,10 @@
         <x:v>Radio audio</x:v>
       </x:c>
       <x:c r="D108" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E108" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F108" s="16" t="n">
         <x:v>2</x:v>
@@ -15718,28 +18137,28 @@
         <x:v>Casque / talkie</x:v>
       </x:c>
       <x:c r="H108" s="12" t="str">
-        <x:v>Le signal de test est centré et identique sur les deux canaux.</x:v>
+        <x:v>Le contrôle est centré ; le signal généré est réparti également à gauche et à droite.</x:v>
       </x:c>
       <x:c r="I108" s="12" t="str">
-        <x:v>Le test se déplace complètement d’un côté malgré le réglage centré.</x:v>
+        <x:v>Le signal de test est routé entièrement à gauche ; le relevé précise G 100 / D 0.</x:v>
       </x:c>
       <x:c r="J108" s="12" t="str">
-        <x:v>Le test reste centré.</x:v>
+        <x:v>Le test demeure centré.</x:v>
       </x:c>
       <x:c r="K108" s="12" t="str">
-        <x:v>Comparer le retour visuel gauche/droite du test après vérification du périphérique.</x:v>
+        <x:v>Comparer la répartition indiquée par les relevés du jeu, puis écouter si les appareils le permettent.</x:v>
       </x:c>
       <x:c r="L108" s="12" t="str">
-        <x:v>Étalonnage stéréo futur.</x:v>
+        <x:v>Étalonnage volontaire, casque non obligatoire.</x:v>
       </x:c>
       <x:c r="M108" s="12" t="str">
-        <x:v>Le signal local de test confirme un déplacement délibéré.</x:v>
+        <x:v>Le routage fictionnel unilatéral décrit par le relevé est la preuve.</x:v>
       </x:c>
       <x:c r="N108" s="12" t="str">
-        <x:v>Mode mono et transcription indispensables. Une panne d’écouteur réelle est un défaut matériel, pas une anomalie.</x:v>
+        <x:v>Le texte décrit le signal synthétisé, pas l’état mesuré du casque. Un écouteur réel défectueux ne devient pas une anomalie.</x:v>
       </x:c>
       <x:c r="O108" s="12" t="str">
-        <x:v>Panner stéréo, indicateurs gauche/droite.</x:v>
+        <x:v>Panoramique stéréo, valeurs de routage et relevé accessible.</x:v>
       </x:c>
       <x:c r="P108" s="12" t="str">
         <x:v>radio_left_only</x:v>
@@ -15748,22 +18167,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R108" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S108" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T108" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U108" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V108" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="109" ht="40" customHeight="1">
+      <x:c r="W108" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="64" customHeight="1">
       <x:c r="A109" s="11" t="str">
         <x:v>PX-104</x:v>
       </x:c>
@@ -15774,10 +18196,10 @@
         <x:v>Radio audio</x:v>
       </x:c>
       <x:c r="D109" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E109" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F109" s="17" t="n">
         <x:v>3</x:v>
@@ -15786,28 +18208,28 @@
         <x:v>Talkie dans un espace sec</x:v>
       </x:c>
       <x:c r="H109" s="11" t="str">
-        <x:v>Le test court produit une résonance faible identique entre joueurs.</x:v>
+        <x:v>La queue normale du contrôle reste courte, prévue à 0,12 seconde.</x:v>
       </x:c>
       <x:c r="I109" s="11" t="str">
-        <x:v>Sa réception semble provenir d’une immense salle réverbérante.</x:v>
+        <x:v>Le test résonne comme dans une grande pièce, avec une queue prévue à 2,4 secondes.</x:v>
       </x:c>
       <x:c r="J109" s="11" t="str">
-        <x:v>Le test conserve son acoustique habituelle.</x:v>
+        <x:v>La queue du test reste brève.</x:v>
       </x:c>
       <x:c r="K109" s="11" t="str">
-        <x:v>Comparer longueur de la queue du test, avec une graduation visuelle équivalente.</x:v>
+        <x:v>Laisser finir le signal et comparer la durée indiquée au relevé.</x:v>
       </x:c>
       <x:c r="L109" s="11" t="str">
-        <x:v>Étalonnage acoustique futur.</x:v>
+        <x:v>Étalonnage acoustique volontaire.</x:v>
       </x:c>
       <x:c r="M109" s="11" t="str">
         <x:v>Une réverbération synthétique anormalement longue confirme.</x:v>
       </x:c>
       <x:c r="N109" s="11" t="str">
-        <x:v>Le test doit neutraliser les différences de pièce et de micro réels.</x:v>
+        <x:v>La preuve est générée localement et ne dépend pas de l’acoustique réelle, du microphone ou de la latence réseau.</x:v>
       </x:c>
       <x:c r="O109" s="11" t="str">
-        <x:v>Réponse impulsionnelle originale, filtre et visualisation de durée.</x:v>
+        <x:v>Réverbération synthétique originale, enveloppe de durée et transcription.</x:v>
       </x:c>
       <x:c r="P109" s="11" t="str">
         <x:v>radio_wrong_room</x:v>
@@ -15816,22 +18238,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R109" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S109" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T109" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U109" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V109" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="110" ht="40" customHeight="1">
+      <x:c r="W109" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="64" customHeight="1">
       <x:c r="A110" s="12" t="str">
         <x:v>PX-105</x:v>
       </x:c>
@@ -15842,10 +18267,10 @@
         <x:v>Radio relationnelle</x:v>
       </x:c>
       <x:c r="D110" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E110" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F110" s="16" t="n">
         <x:v>2</x:v>
@@ -15854,28 +18279,28 @@
         <x:v>Talkie</x:v>
       </x:c>
       <x:c r="H110" s="12" t="str">
-        <x:v>Le test suit toujours 1, 2, 3.</x:v>
+        <x:v>Après l’identifiant RELAIS, la séquence principale est toujours 1, 2, 3.</x:v>
       </x:c>
       <x:c r="I110" s="12" t="str">
-        <x:v>Il reçoit 1, 3, 2, chaque tonalité restant claire.</x:v>
+        <x:v>La séquence principale devient 1, 3, 2.</x:v>
       </x:c>
       <x:c r="J110" s="12" t="str">
-        <x:v>Il reçoit 1, 2, 3.</x:v>
+        <x:v>La séquence principale reste 1, 2, 3.</x:v>
       </x:c>
       <x:c r="K110" s="12" t="str">
-        <x:v>Lire l’ordre complet sans se contenter de compter trois sons.</x:v>
+        <x:v>Lire l’ordre complet des trois tonalités principales, séparément des quatre chiffres d’identification.</x:v>
       </x:c>
       <x:c r="L110" s="12" t="str">
-        <x:v>Étalonnage de séquence futur.</x:v>
+        <x:v>Étalonnage de séquence volontaire.</x:v>
       </x:c>
       <x:c r="M110" s="12" t="str">
         <x:v>L’ordre contradictoire stable constitue la preuve.</x:v>
       </x:c>
       <x:c r="N110" s="12" t="str">
-        <x:v>Les trois sons doivent être nettement séparés, sans exiger une précision de réflexe.</x:v>
+        <x:v>Trois sons restent présents : compter seulement les sons ne suffit pas. Aucune précision de réflexe n’est requise.</x:v>
       </x:c>
       <x:c r="O110" s="12" t="str">
-        <x:v>Ordonnanceur déterministe et transcription des trois étapes.</x:v>
+        <x:v>Ordonnanceur déterministe et relevé de la séquence principale.</x:v>
       </x:c>
       <x:c r="P110" s="12" t="str">
         <x:v>radio_order_swap</x:v>
@@ -15884,22 +18309,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R110" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S110" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T110" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U110" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V110" s="12" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="111" ht="40" customHeight="1">
+      <x:c r="W110" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="64" customHeight="1">
       <x:c r="A111" s="11" t="str">
         <x:v>PX-106</x:v>
       </x:c>
@@ -15910,10 +18338,10 @@
         <x:v>Radio audio</x:v>
       </x:c>
       <x:c r="D111" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E111" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F111" s="17" t="n">
         <x:v>4</x:v>
@@ -15922,28 +18350,28 @@
         <x:v>Talkie posé</x:v>
       </x:c>
       <x:c r="H111" s="11" t="str">
-        <x:v>Le test se termine après trois impulsions et l’appareil redevient silencieux.</x:v>
+        <x:v>La séquence principale contient trois impulsions et se termine par un clic de fermeture puis le silence.</x:v>
       </x:c>
       <x:c r="I111" s="11" t="str">
-        <x:v>Une respiration synthétique accompagne une quatrième impulsion lente.</x:v>
+        <x:v>Une quatrième impulsion soufflée revient après la clôture.</x:v>
       </x:c>
       <x:c r="J111" s="11" t="str">
-        <x:v>L’appareil redevient silencieux après trois impulsions.</x:v>
+        <x:v>Il n’observe que les trois impulsions principales habituelles.</x:v>
       </x:c>
       <x:c r="K111" s="11" t="str">
-        <x:v>Compter les impulsions puis décrire la nature du son final.</x:v>
+        <x:v>Distinguer le code RELAIS initial, compter la séquence principale puis attendre après le clic final.</x:v>
       </x:c>
       <x:c r="L111" s="11" t="str">
-        <x:v>Après étalonnage futur.</x:v>
+        <x:v>Fin du contrôle volontaire.</x:v>
       </x:c>
       <x:c r="M111" s="11" t="str">
-        <x:v>La quatrième étape anormale, explicitement transcrite, confirme.</x:v>
+        <x:v>Une quatrième impulsion tardive, également décrite dans le relevé, confirme.</x:v>
       </x:c>
       <x:c r="N111" s="11" t="str">
-        <x:v>Aucune copie de souffle ou de voix réelle. Volume modéré et arrêt immédiat possible.</x:v>
+        <x:v>Aucun souffle ou voix de joueur n’est copié. Volume limité et arrêt immédiat doivent rester disponibles.</x:v>
       </x:c>
       <x:c r="O111" s="11" t="str">
-        <x:v>Souffle original synthétique, signal visuel de quatrième impulsion.</x:v>
+        <x:v>Souffle synthétique original, impulsion et transcription.</x:v>
       </x:c>
       <x:c r="P111" s="11" t="str">
         <x:v>radio_pulse_inside</x:v>
@@ -15952,22 +18380,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R111" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>32 tests radio réussis : PCM de production, calibration et API simulées. Douze profils ; écoute humaine, microphones et transport réel restent à éprouver.</x:v>
       </x:c>
       <x:c r="S111" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T111" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U111" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V111" s="11" t="str">
         <x:v>Audio + relevé écrit</x:v>
       </x:c>
-    </x:row>
-    <x:row r="112" ht="51" customHeight="1">
+      <x:c r="W111" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="64" customHeight="1">
       <x:c r="A112" s="12" t="str">
         <x:v>PX-107</x:v>
       </x:c>
@@ -15978,10 +18409,10 @@
         <x:v>Personnage</x:v>
       </x:c>
       <x:c r="D112" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E112" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F112" s="16" t="n">
         <x:v>2</x:v>
@@ -15990,28 +18421,28 @@
         <x:v>Inspecteur</x:v>
       </x:c>
       <x:c r="H112" s="12" t="str">
-        <x:v>Chaque inspecteur porte un badge lisible lié à son identité de salle.</x:v>
+        <x:v>Le premier collègue connecté porte un badge de slot lisible ; en solo le corps local sert de témoin.</x:v>
       </x:c>
       <x:c r="I112" s="12" t="str">
-        <x:v>Le badge physique d’un collègue est devenu vierge.</x:v>
+        <x:v>La plaque physique du badge devient vierge.</x:v>
       </x:c>
       <x:c r="J112" s="12" t="str">
-        <x:v>Le badge porte encore son nom ou symbole.</x:v>
+        <x:v>Le badge du même inspecteur conserve son code.</x:v>
       </x:c>
       <x:c r="K112" s="12" t="str">
-        <x:v>Nommer le collègue par l’interface fiable puis comparer le badge de son modèle.</x:v>
+        <x:v>Identifier le collègue par le roster fiable, puis comparer son badge physique au même moment.</x:v>
       </x:c>
       <x:c r="L112" s="12" t="str">
-        <x:v>Inspection de personnage future.</x:v>
+        <x:v>Inspection persistante ; premier collègue connecté par slot, sinon corps local / reflet.</x:v>
       </x:c>
       <x:c r="M112" s="12" t="str">
         <x:v>Une plaque de modèle vide alors que le badge normal est connu confirme.</x:v>
       </x:c>
       <x:c r="N112" s="12" t="str">
-        <x:v>Le roster d’identité ne change pas. Éviter la confusion avec un texte trop petit ou en cours de chargement.</x:v>
+        <x:v>Le roster et les poses réseau ne changent pas. Une plaque vierge doit se distinguer d’un texte trop petit ou masqué.</x:v>
       </x:c>
       <x:c r="O112" s="12" t="str">
-        <x:v>Badge dynamique local, texture et ancrage de torse.</x:v>
+        <x:v>Badge de torse, variante vierge et sélection stable de l’inspecteur.</x:v>
       </x:c>
       <x:c r="P112" s="12" t="str">
         <x:v>avatar_badge_missing</x:v>
@@ -16020,22 +18451,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R112" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S112" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T112" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U112" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V112" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="113" ht="51" customHeight="1">
+      <x:c r="W112" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="64" customHeight="1">
       <x:c r="A113" s="11" t="str">
         <x:v>PX-108</x:v>
       </x:c>
@@ -16046,10 +18480,10 @@
         <x:v>Personnage</x:v>
       </x:c>
       <x:c r="D113" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E113" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F113" s="17" t="n">
         <x:v>3</x:v>
@@ -16058,25 +18492,25 @@
         <x:v>Couloir partagé</x:v>
       </x:c>
       <x:c r="H113" s="11" t="str">
-        <x:v>La taille de chaque modèle reste fixe pendant la session.</x:v>
+        <x:v>Chaque inspecteur garde une taille fixe et des proportions cohérentes avec le cadre de porte.</x:v>
       </x:c>
       <x:c r="I113" s="11" t="str">
-        <x:v>Le collègue dépasse soudain un repère architectural connu.</x:v>
+        <x:v>Le corps du collègue paraît anormalement grand.</x:v>
       </x:c>
       <x:c r="J113" s="11" t="str">
-        <x:v>Le modèle garde sa taille normale.</x:v>
+        <x:v>Le même inspecteur conserve sa taille normale.</x:v>
       </x:c>
       <x:c r="K113" s="11" t="str">
-        <x:v>Se placer près d’une porte et comparer haut du casque et montant.</x:v>
+        <x:v>Le collègue s’immobilise près d’un repère architectural ; comparer la hauteur de son casque.</x:v>
       </x:c>
       <x:c r="L113" s="11" t="str">
-        <x:v>Début d’un tour futur.</x:v>
+        <x:v>Variation locale persistante de l’inspecteur désigné.</x:v>
       </x:c>
       <x:c r="M113" s="11" t="str">
         <x:v>Un changement d’échelle local confirmé par repère fixe est anormal.</x:v>
       </x:c>
       <x:c r="N113" s="11" t="str">
-        <x:v>Ne pas modifier la capsule physique commune. Un avatar personnalisé de grande taille ne constitue pas à lui seul une anomalie.</x:v>
+        <x:v>La pose réseau et les collisions partagées ne sont pas redimensionnées ; le roster reste exact.</x:v>
       </x:c>
       <x:c r="O113" s="11" t="str">
         <x:v>Rig redimensionnable, badge conservé, référence de taille.</x:v>
@@ -16088,22 +18522,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R113" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S113" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T113" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U113" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V113" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="114" ht="51" customHeight="1">
+      <x:c r="W113" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="64" customHeight="1">
       <x:c r="A114" s="12" t="str">
         <x:v>PX-109</x:v>
       </x:c>
@@ -16114,10 +18551,10 @@
         <x:v>Personnage</x:v>
       </x:c>
       <x:c r="D114" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E114" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F114" s="16" t="n">
         <x:v>3</x:v>
@@ -16126,28 +18563,28 @@
         <x:v>Corps et reflet</x:v>
       </x:c>
       <x:c r="H114" s="12" t="str">
-        <x:v>Le talkie est tenu de la main prévue et la main libre est cohérente.</x:v>
+        <x:v>Le talkie est tenu dans la main droite de l’inspecteur, même lorsque le microphone est coupé.</x:v>
       </x:c>
       <x:c r="I114" s="12" t="str">
-        <x:v>Le talkie est dans la main opposée sans mouvement de transfert.</x:v>
+        <x:v>Le talkie passe dans la main gauche d’un inspecteur dans une seule perception.</x:v>
       </x:c>
       <x:c r="J114" s="12" t="str">
-        <x:v>Le collègue conserve la prise normale.</x:v>
+        <x:v>Il reste dans la main droite.</x:v>
       </x:c>
       <x:c r="K114" s="12" t="str">
-        <x:v>Demander de lever puis baisser la main et comparer côté du badge et du talkie.</x:v>
+        <x:v>Comparez la main qui porte le talkie en nommant le côté du corps, pas le côté de l’écran.</x:v>
       </x:c>
       <x:c r="L114" s="12" t="str">
-        <x:v>Geste volontaire futur.</x:v>
+        <x:v>Inspection persistante sans pression PTT ni permission microphone.</x:v>
       </x:c>
       <x:c r="M114" s="12" t="str">
         <x:v>Une inversion persistante entre le corps attendu et sa perception confirme.</x:v>
       </x:c>
       <x:c r="N114" s="12" t="str">
-        <x:v>Documenter la main dominante choisie au salon afin qu’un gaucher normal ne devienne pas un faux positif.</x:v>
+        <x:v>La preuve ne dépend jamais d’une voix, d’un microphone, d’un geste réseau ou d’une préférence de main dominante non implémentée.</x:v>
       </x:c>
       <x:c r="O114" s="12" t="str">
-        <x:v>Rigs de mains, prise talkie gauche/droite et animation.</x:v>
+        <x:v>Attaches droite / gauche du talkie et pose abaissée lisible.</x:v>
       </x:c>
       <x:c r="P114" s="12" t="str">
         <x:v>avatar_hands_swap</x:v>
@@ -16156,22 +18593,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R114" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S114" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T114" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U114" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V114" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="115" ht="51" customHeight="1">
+      <x:c r="W114" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="64" customHeight="1">
       <x:c r="A115" s="11" t="str">
         <x:v>PX-110</x:v>
       </x:c>
@@ -16182,10 +18622,10 @@
         <x:v>Personnage</x:v>
       </x:c>
       <x:c r="D115" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E115" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F115" s="17" t="n">
         <x:v>4</x:v>
@@ -16194,25 +18634,25 @@
         <x:v>Visière d’inspecteur</x:v>
       </x:c>
       <x:c r="H115" s="11" t="str">
-        <x:v>Le regard et la tête suivent la pose réelle du collègue.</x:v>
+        <x:v>Les yeux et la tête du modèle restent cohérents avec sa pose.</x:v>
       </x:c>
       <x:c r="I115" s="11" t="str">
-        <x:v>Les yeux restent tournés vers lui alors que la tête se détourne.</x:v>
+        <x:v>Les yeux sous la visière suivent l’observateur indépendamment de la tête.</x:v>
       </x:c>
       <x:c r="J115" s="11" t="str">
-        <x:v>Le regard suit normalement la tête.</x:v>
+        <x:v>Le regard suit la tête.</x:v>
       </x:c>
       <x:c r="K115" s="11" t="str">
-        <x:v>Un collègue tourne lentement la tête. Les autres décrivent la direction des yeux.</x:v>
+        <x:v>Le collègue tourne lentement la tête ; comparer la direction des yeux et celle de la visière.</x:v>
       </x:c>
       <x:c r="L115" s="11" t="str">
-        <x:v>Rotation volontaire future.</x:v>
+        <x:v>Observation du modèle désigné ; preuve locale.</x:v>
       </x:c>
       <x:c r="M115" s="11" t="str">
         <x:v>Un regard autonome dans une seule perception confirme.</x:v>
       </x:c>
       <x:c r="N115" s="11" t="str">
-        <x:v>Pas d’accès à la webcam. Ne pas imposer une texture photoréaliste pour rendre l’indice lisible.</x:v>
+        <x:v>Aucun accès à une webcam. Le contraste et la taille des yeux doivent permettre la lecture sans texture photoréaliste.</x:v>
       </x:c>
       <x:c r="O115" s="11" t="str">
         <x:v>Yeux articulés, visière transparente et suivi local.</x:v>
@@ -16224,22 +18664,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R115" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S115" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T115" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U115" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V115" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="116" ht="40" customHeight="1">
+      <x:c r="W115" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="64" customHeight="1">
       <x:c r="A116" s="12" t="str">
         <x:v>PX-111</x:v>
       </x:c>
@@ -16250,10 +18693,10 @@
         <x:v>Personnage</x:v>
       </x:c>
       <x:c r="D116" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E116" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F116" s="16" t="n">
         <x:v>3</x:v>
@@ -16262,25 +18705,25 @@
         <x:v>Sol près d’un inspecteur</x:v>
       </x:c>
       <x:c r="H116" s="12" t="str">
-        <x:v>Les pieds touchent le sol pendant la marche.</x:v>
+        <x:v>Les pieds du modèle restent en contact avec le sol plan.</x:v>
       </x:c>
       <x:c r="I116" s="12" t="str">
-        <x:v>Le collègue marche quelques centimètres au-dessus du revêtement.</x:v>
+        <x:v>Le corps marche au-dessus du revêtement.</x:v>
       </x:c>
       <x:c r="J116" s="12" t="str">
-        <x:v>Ses pieds restent au contact du sol.</x:v>
+        <x:v>Les pieds touchent le sol.</x:v>
       </x:c>
       <x:c r="K116" s="12" t="str">
-        <x:v>Comparer chaussures, ombre et joints du revêtement pendant une marche lente.</x:v>
+        <x:v>Comparer la semelle et les joints du sol pendant une marche lente ou un arrêt.</x:v>
       </x:c>
       <x:c r="L116" s="12" t="str">
-        <x:v>Locomotion future en zone plane.</x:v>
+        <x:v>Décalage local du corps de l’inspecteur désigné.</x:v>
       </x:c>
       <x:c r="M116" s="12" t="str">
         <x:v>La hauteur locale anormale avec pose réseau stable confirme.</x:v>
       </x:c>
       <x:c r="N116" s="12" t="str">
-        <x:v>Une compensation réseau ou un dénivelé réel ne doit pas produire le même indice.</x:v>
+        <x:v>Le décalage ne modifie ni la caméra, ni la position autoritaire, ni la collision. Il doit se distinguer d’une interpolation réseau.</x:v>
       </x:c>
       <x:c r="O116" s="12" t="str">
         <x:v>Rig de pieds, décalage visuel local et ombre.</x:v>
@@ -16292,22 +18735,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R116" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S116" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T116" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U116" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V116" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="117" ht="40" customHeight="1">
+      <x:c r="W116" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="64" customHeight="1">
       <x:c r="A117" s="11" t="str">
         <x:v>PX-112</x:v>
       </x:c>
@@ -16318,10 +18764,10 @@
         <x:v>Reflet</x:v>
       </x:c>
       <x:c r="D117" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E117" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F117" s="17" t="n">
         <x:v>4</x:v>
@@ -16330,28 +18776,28 @@
         <x:v>Miroir près d’un siège</x:v>
       </x:c>
       <x:c r="H117" s="11" t="str">
-        <x:v>Le corps réfléchi reproduit la posture debout de l’inspecteur.</x:v>
+        <x:v>Le corps réfléchi est debout et suit la posture du corps réel.</x:v>
       </x:c>
       <x:c r="I117" s="11" t="str">
-        <x:v>Son reflet reste assis sur un siège vide tandis qu’il se tient debout.</x:v>
+        <x:v>Le corps réfléchi adopte une posture assise indépendante.</x:v>
       </x:c>
       <x:c r="J117" s="11" t="str">
-        <x:v>Le reflet reste debout.</x:v>
+        <x:v>Le reflet conserve la posture debout normale et le tabouret reste vide.</x:v>
       </x:c>
       <x:c r="K117" s="11" t="str">
-        <x:v>S’éloigner du siège et décrire la posture du reflet.</x:v>
+        <x:v>S’immobiliser debout au repère miroir, puis comparer jambes et bassin réels / réfléchis.</x:v>
       </x:c>
       <x:c r="L117" s="11" t="str">
-        <x:v>Passage futur après interaction avec le fauteuil.</x:v>
+        <x:v>Observation persistante du miroir ; aucune action préalable de s’asseoir requise.</x:v>
       </x:c>
       <x:c r="M117" s="11" t="str">
         <x:v>Une posture autonome clairement différente confirme.</x:v>
       </x:c>
       <x:c r="N117" s="11" t="str">
-        <x:v>Conserver le décor normal pour distinguer l’effet d’un reflet entièrement figé ou défaillant.</x:v>
+        <x:v>Le décor du miroir reste normal. La preuve porte sur la posture et la position du corps réfléchi, pas sur une surface entière figée.</x:v>
       </x:c>
       <x:c r="O117" s="11" t="str">
-        <x:v>Rig assis, siège reflété, masque du corps réfléchi.</x:v>
+        <x:v>Vrai tabouret, pose assise du corps réfléchi et surface planaire conservant le décor.</x:v>
       </x:c>
       <x:c r="P117" s="11" t="str">
         <x:v>reflection_seated</x:v>
@@ -16360,22 +18806,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R117" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S117" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T117" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U117" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V117" s="11" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="118" ht="51" customHeight="1">
+      <x:c r="W117" s="19" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="64" customHeight="1">
       <x:c r="A118" s="12" t="str">
         <x:v>PX-113</x:v>
       </x:c>
@@ -16386,10 +18835,10 @@
         <x:v>Reflet relationnel</x:v>
       </x:c>
       <x:c r="D118" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E118" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F118" s="16" t="n">
         <x:v>3</x:v>
@@ -16398,52 +18847,55 @@
         <x:v>Miroir</x:v>
       </x:c>
       <x:c r="H118" s="12" t="str">
-        <x:v>Le badge et le numéro de modèle sont cohérents entre corps et reflet.</x:v>
+        <x:v>Le numéro du badge réfléchi correspond au badge de la personne réelle.</x:v>
       </x:c>
       <x:c r="I118" s="12" t="str">
-        <x:v>Le badge réfléchi porte le numéro d’un autre inspecteur.</x:v>
+        <x:v>Le reflet porte un autre numéro de badge, alors que le badge réel reste inchangé.</x:v>
       </x:c>
       <x:c r="J118" s="12" t="str">
-        <x:v>Le badge réfléchi correspond au corps.</x:v>
+        <x:v>Le badge réfléchi conserve le code de son corps réel.</x:v>
       </x:c>
       <x:c r="K118" s="12" t="str">
-        <x:v>Lire d’abord le badge physique, puis le badge dans le miroir depuis le repère prévu.</x:v>
+        <x:v>Comparez le badge direct et son reflet ; un miroir inverse la direction, pas l’identité.</x:v>
       </x:c>
       <x:c r="L118" s="12" t="str">
-        <x:v>Observation rapprochée future.</x:v>
+        <x:v>Observation persistante du miroir.</x:v>
       </x:c>
       <x:c r="M118" s="12" t="str">
         <x:v>Une identité inversée seulement dans le reflet constitue la preuve.</x:v>
       </x:c>
       <x:c r="N118" s="12" t="str">
-        <x:v>Le texte ne doit pas être simplement retourné par la réflexion normale. L’interface d’identité reste fiable.</x:v>
+        <x:v>Le badge du corps réel et le roster demeurent inchangés. L’inversion optique normale du texte ne suffit pas à conclure.</x:v>
       </x:c>
       <x:c r="O118" s="12" t="str">
-        <x:v>Texte miroir corrigé pour la lecture, badges et caméra planaire.</x:v>
+        <x:v>Badge alternatif du corps réfléchi, code par slot et caméra planaire.</x:v>
       </x:c>
       <x:c r="P118" s="12" t="str">
         <x:v>reflection_badge_code</x:v>
       </x:c>
       <x:c r="Q118" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R118" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S118" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="T118" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U118" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V118" s="12" t="str">
         <x:v>Corps / reflet / mouvement</x:v>
       </x:c>
-    </x:row>
-    <x:row r="119" ht="51" customHeight="1">
+      <x:c r="W118" s="18" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="64" customHeight="1">
       <x:c r="A119" s="11" t="str">
         <x:v>PX-114</x:v>
       </x:c>
@@ -16454,40 +18906,40 @@
         <x:v>Métro</x:v>
       </x:c>
       <x:c r="D119" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E119" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F119" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G119" s="11" t="str">
-        <x:v>Tableau des horaires</x:v>
+        <x:v>Métro · tableau d’archives</x:v>
       </x:c>
       <x:c r="H119" s="11" t="str">
-        <x:v>Les destinations suivent un ordre stable et des temps décroissants cohérents.</x:v>
+        <x:v>Le tableau ARCHIVES conserve deux lignes fixes : 01:09 T09 → OBSERVATOIRE et 01:12 T12 ← BELVÉDÈRE. Il n’annonce aucun service actif.</x:v>
       </x:c>
       <x:c r="I119" s="11" t="str">
-        <x:v>Le même départ apparaît deux fois avec des directions opposées.</x:v>
+        <x:v>La seconde ligne d’archives répète 01:09 T09 au lieu de 01:12 T12, vers BELVÉDÈRE.</x:v>
       </x:c>
       <x:c r="J119" s="11" t="str">
-        <x:v>Le tableau conserve son ordre normal.</x:v>
+        <x:v>La seconde ligne demeure 01:12 T12 ← BELVÉDÈRE.</x:v>
       </x:c>
       <x:c r="K119" s="11" t="str">
-        <x:v>Lire numéro de rame, direction et minute sur les deux lignes.</x:v>
+        <x:v>Lisez l’heure, l’identifiant et la destination de chaque ligne ; aucune attente ni décompte réel n’est nécessaire.</x:v>
       </x:c>
       <x:c r="L119" s="11" t="str">
-        <x:v>Cycle d’affichage futur.</x:v>
+        <x:v>Inspection persistante du tableau d’archives du quai vide.</x:v>
       </x:c>
       <x:c r="M119" s="11" t="str">
         <x:v>Deux lignes incompatibles pour un même identifiant de train confirment.</x:v>
       </x:c>
       <x:c r="N119" s="11" t="str">
-        <x:v>La rotation normale des pages doit rester identique entre joueurs pour éviter un faux désaccord temporel.</x:v>
+        <x:v>Tableau statique d’archives, pas horaires en direct ni alternance de pages. SERVICE TERMINÉ reste normal.</x:v>
       </x:c>
       <x:c r="O119" s="11" t="str">
-        <x:v>Afficheur à plusieurs lignes et états déterministes.</x:v>
+        <x:v>Archives ferroviaires fictives à deux lignes, texte et flèches lisibles.</x:v>
       </x:c>
       <x:c r="P119" s="11" t="str">
         <x:v>metro_timetable_loop</x:v>
@@ -16496,13 +18948,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R119" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S119" s="19" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="T119" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U119" s="19" t="str">
         <x:v>—</x:v>
@@ -16510,8 +18962,11 @@
       <x:c r="V119" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="120" ht="40" customHeight="1">
+      <x:c r="W119" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="64" customHeight="1">
       <x:c r="A120" s="12" t="str">
         <x:v>PX-115</x:v>
       </x:c>
@@ -16522,37 +18977,37 @@
         <x:v>Métro relationnel</x:v>
       </x:c>
       <x:c r="D120" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E120" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F120" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G120" s="12" t="str">
-        <x:v>Plan de ligne</x:v>
+        <x:v>Métro · plan de ligne</x:v>
       </x:c>
       <x:c r="H120" s="12" t="str">
-        <x:v>Le plan comporte le même ensemble de stations pour tous.</x:v>
+        <x:v>Le plan de ligne indique BELVÉDÈRE → OBSERVATOIRE → TERMINUS 09.</x:v>
       </x:c>
       <x:c r="I120" s="12" t="str">
-        <x:v>Une station inconnue s’intercale entre deux arrêts.</x:v>
+        <x:v>La station NULLE PART s’ajoute entre BELVÉDÈRE et OBSERVATOIRE.</x:v>
       </x:c>
       <x:c r="J120" s="12" t="str">
-        <x:v>Le trajet reste celui de référence.</x:v>
+        <x:v>Le trajet conserve ses trois stations.</x:v>
       </x:c>
       <x:c r="K120" s="12" t="str">
-        <x:v>Lire trois stations consécutives autour du même embranchement.</x:v>
+        <x:v>Lisez chaque station du plan dans le même sens, en citant les deux voisines.</x:v>
       </x:c>
       <x:c r="L120" s="12" t="str">
-        <x:v>Inspection du plan futur.</x:v>
+        <x:v>Lecture persistante du plan original de la station.</x:v>
       </x:c>
       <x:c r="M120" s="12" t="str">
         <x:v>Une station ajoutée au même emplacement confirme.</x:v>
       </x:c>
       <x:c r="N120" s="12" t="str">
-        <x:v>Utiliser noms et formes, pas uniquement des couleurs de ligne.</x:v>
+        <x:v>Comparer des noms de station et leur ordre, pas seulement une couleur. Aucune station réelle n’est nécessaire.</x:v>
       </x:c>
       <x:c r="O120" s="12" t="str">
         <x:v>Carte originale, typographie lisible et variantes de trajet.</x:v>
@@ -16564,13 +19019,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R120" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S120" s="18" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="T120" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U120" s="18" t="str">
         <x:v>—</x:v>
@@ -16578,8 +19033,11 @@
       <x:c r="V120" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="121" ht="40" customHeight="1">
+      <x:c r="W120" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="64" customHeight="1">
       <x:c r="A121" s="11" t="str">
         <x:v>PX-116</x:v>
       </x:c>
@@ -16590,37 +19048,37 @@
         <x:v>Métro</x:v>
       </x:c>
       <x:c r="D121" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E121" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F121" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G121" s="11" t="str">
-        <x:v>Portique de quai</x:v>
+        <x:v>Métro · compteur du portique</x:v>
       </x:c>
       <x:c r="H121" s="11" t="str">
-        <x:v>Le compteur diégétique reste à sa valeur de référence lorsqu’aucun passage n’a lieu.</x:v>
+        <x:v>Le portique est SCELLÉ et son compteur reste à 0000. Aucun joueur ne peut traverser ce portique.</x:v>
       </x:c>
       <x:c r="I121" s="11" t="str">
-        <x:v>Il augmente lentement alors que personne ne passe.</x:v>
+        <x:v>Le compteur du portique scellé augmente tout seul, d’une unité toutes les 2,4 secondes.</x:v>
       </x:c>
       <x:c r="J121" s="11" t="str">
-        <x:v>Le compteur reste fixe.</x:v>
+        <x:v>Le compteur demeure 0000.</x:v>
       </x:c>
       <x:c r="K121" s="11" t="str">
-        <x:v>Se tenir tous hors du portique et comparer deux relevés espacés.</x:v>
+        <x:v>Restez devant le même portique et comparez deux lectures successives, sans attribuer la hausse aux déplacements de vos partenaires.</x:v>
       </x:c>
       <x:c r="L121" s="11" t="str">
-        <x:v>Immobilité commune future.</x:v>
+        <x:v>Évolution automatique pendant l’inspection ; aucun franchissement requis.</x:v>
       </x:c>
       <x:c r="M121" s="11" t="str">
         <x:v>Une augmentation sans passage réel confirme.</x:v>
       </x:c>
       <x:c r="N121" s="11" t="str">
-        <x:v>Le vrai nombre de joueurs connectés reste visible et ne change pas.</x:v>
+        <x:v>Le portique n’a pas de mécanique de passage physique. Le vrai roster et le nombre de membres connectés restent fiables.</x:v>
       </x:c>
       <x:c r="O121" s="11" t="str">
         <x:v>Compteur animé et zone de contrôle stable.</x:v>
@@ -16632,13 +19090,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R121" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S121" s="19" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="T121" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U121" s="19" t="str">
         <x:v>—</x:v>
@@ -16646,8 +19104,11 @@
       <x:c r="V121" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="122" ht="40" customHeight="1">
+      <x:c r="W121" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="64" customHeight="1">
       <x:c r="A122" s="12" t="str">
         <x:v>PX-117</x:v>
       </x:c>
@@ -16658,16 +19119,16 @@
         <x:v>Métro</x:v>
       </x:c>
       <x:c r="D122" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E122" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F122" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G122" s="12" t="str">
-        <x:v>Bouche du tunnel</x:v>
+        <x:v>Métro · bouche du tunnel</x:v>
       </x:c>
       <x:c r="H122" s="12" t="str">
         <x:v>Le tunnel est sombre et fermé au loin.</x:v>
@@ -16682,13 +19143,13 @@
         <x:v>Décrire la limite entre cadre du tunnel et ciel apparent.</x:v>
       </x:c>
       <x:c r="L122" s="12" t="str">
-        <x:v>Ouverture lumineuse lente future.</x:v>
+        <x:v>Inspection persistante depuis le quai sûr.</x:v>
       </x:c>
       <x:c r="M122" s="12" t="str">
         <x:v>L’extérieur diurne incompatible avec la référence confirme.</x:v>
       </x:c>
       <x:c r="N122" s="12" t="str">
-        <x:v>Aucun flash brutal. L’horizon ne devient pas une sortie physique piégeuse.</x:v>
+        <x:v>Pas de flash ni de voie devenant franchissable. Le fond lumineux n’est jamais une véritable sortie de niveau.</x:v>
       </x:c>
       <x:c r="O122" s="12" t="str">
         <x:v>Fond de tunnel original, horizon et éclairage local.</x:v>
@@ -16700,13 +19161,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R122" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S122" s="18" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="T122" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="U122" s="18" t="str">
         <x:v>—</x:v>
@@ -16714,8 +19175,11 @@
       <x:c r="V122" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="123" ht="40" customHeight="1">
+      <x:c r="W122" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="64" customHeight="1">
       <x:c r="A123" s="11" t="str">
         <x:v>PX-118</x:v>
       </x:c>
@@ -16726,40 +19190,40 @@
         <x:v>Clinique relationnelle</x:v>
       </x:c>
       <x:c r="D123" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E123" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F123" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G123" s="11" t="str">
-        <x:v>Têtes de lit</x:v>
+        <x:v>Clinique · lit du couloir / salle vitrée</x:v>
       </x:c>
       <x:c r="H123" s="11" t="str">
-        <x:v>Chaque lit vide possède un identifiant distinct.</x:v>
+        <x:v>Le lit du couloir porte 09 ; le lit visible dans la salle vitrée porte 10.</x:v>
       </x:c>
       <x:c r="I123" s="11" t="str">
-        <x:v>Deux lits portent le même identifiant.</x:v>
+        <x:v>La plaque du lit de la salle vitrée affiche 09, comme celle du couloir.</x:v>
       </x:c>
       <x:c r="J123" s="11" t="str">
-        <x:v>Les identifiants restent distincts.</x:v>
+        <x:v>Les plaques restent distinctes, 09 dans le couloir et 10 dans la salle vitrée.</x:v>
       </x:c>
       <x:c r="K123" s="11" t="str">
-        <x:v>Lire les plaques depuis l’entrée et les associer au côté de la pièce.</x:v>
+        <x:v>Lisez les plaques en précisant couloir ou salle vitrée.</x:v>
       </x:c>
       <x:c r="L123" s="11" t="str">
-        <x:v>Zone clinique étendue future.</x:v>
+        <x:v>Lecture persistante des deux espaces ; aucune ouverture ni manipulation requise.</x:v>
       </x:c>
       <x:c r="M123" s="11" t="str">
-        <x:v>La duplication d’un identifiant prévu unique confirme.</x:v>
+        <x:v>La duplication du code 09 sur deux lits de référence distincts confirme.</x:v>
       </x:c>
       <x:c r="N123" s="11" t="str">
-        <x:v>Aucun nom de patient réel. La comparaison ne demande aucune donnée de santé.</x:v>
+        <x:v>Ne pas confondre avec clinic_bed_count, qui ajoute un lit dans le couloir. Aucune donnée patient ni information de santé réelle.</x:v>
       </x:c>
       <x:c r="O123" s="11" t="str">
-        <x:v>Lits supplémentaires et plaques d’identification fictionnelles.</x:v>
+        <x:v>Plaques fictives 09 / 10 sur les deux lits des espaces séparés.</x:v>
       </x:c>
       <x:c r="P123" s="11" t="str">
         <x:v>clinic_tag_echo</x:v>
@@ -16768,7 +19232,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R123" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S123" s="19" t="str">
         <x:v>—</x:v>
@@ -16777,13 +19241,16 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="U123" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V123" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="124" ht="40" customHeight="1">
+      <x:c r="W123" s="19" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="64" customHeight="1">
       <x:c r="A124" s="12" t="str">
         <x:v>PX-119</x:v>
       </x:c>
@@ -16794,16 +19261,16 @@
         <x:v>Clinique</x:v>
       </x:c>
       <x:c r="D124" s="12" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E124" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F124" s="16" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G124" s="12" t="str">
-        <x:v>Mur derrière le lit</x:v>
+        <x:v>Clinique · mur derrière le lit</x:v>
       </x:c>
       <x:c r="H124" s="12" t="str">
         <x:v>L’ombre du lit vide ne comporte aucune silhouette humaine.</x:v>
@@ -16818,16 +19285,16 @@
         <x:v>Comparer surface du lit, silhouette sur le mur et position de la lampe.</x:v>
       </x:c>
       <x:c r="L124" s="12" t="str">
-        <x:v>Observation future depuis un repère fixe.</x:v>
+        <x:v>Inspection depuis le repère du lit vide.</x:v>
       </x:c>
       <x:c r="M124" s="12" t="str">
         <x:v>Un occupant absent du lit mais visible dans son ombre confirme.</x:v>
       </x:c>
       <x:c r="N124" s="12" t="str">
-        <x:v>Ne pas assimiler une ombre de joueur réel passant derrière la lampe à une anomalie.</x:v>
+        <x:v>La silhouette est distincte des ombres GPU dynamiques et de l’ombre d’un vrai joueur. Le matelas reste vide.</x:v>
       </x:c>
       <x:c r="O124" s="12" t="str">
-        <x:v>Projection contrôlée, lit vide et silhouette originale.</x:v>
+        <x:v>Projection plane originale d’une silhouette assise sur le mur près du lit, matelas vide.</x:v>
       </x:c>
       <x:c r="P124" s="12" t="str">
         <x:v>clinic_shadow_bed</x:v>
@@ -16836,7 +19303,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R124" s="12" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S124" s="18" t="str">
         <x:v>—</x:v>
@@ -16845,13 +19312,16 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="U124" s="18" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V124" s="12" t="str">
         <x:v>Visuel / objet / espace</x:v>
       </x:c>
-    </x:row>
-    <x:row r="125" ht="51" customHeight="1">
+      <x:c r="W124" s="18" t="str">
+        <x:v>—</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="64" customHeight="1">
       <x:c r="A125" s="11" t="str">
         <x:v>PX-120</x:v>
       </x:c>
@@ -16862,16 +19332,16 @@
         <x:v>Clinique</x:v>
       </x:c>
       <x:c r="D125" s="11" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Présent</x:v>
       </x:c>
       <x:c r="E125" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F125" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G125" s="11" t="str">
-        <x:v>Pied de perfusion vide</x:v>
+        <x:v>Clinique · perfusion de démonstration</x:v>
       </x:c>
       <x:c r="H125" s="11" t="str">
         <x:v>Le tube d’exposition présente un écoulement de démonstration régulier vers le bas.</x:v>
@@ -16886,13 +19356,13 @@
         <x:v>Observer ensemble trois gouttes puis décrire leur direction.</x:v>
       </x:c>
       <x:c r="L125" s="11" t="str">
-        <x:v>Dispositif de démonstration futur, sans patient.</x:v>
+        <x:v>Observer plusieurs gouttes du dispositif vide pendant l’inspection.</x:v>
       </x:c>
       <x:c r="M125" s="11" t="str">
         <x:v>Le mouvement inverse local est la preuve.</x:v>
       </x:c>
       <x:c r="N125" s="11" t="str">
-        <x:v>Montrer clairement le sens normal au passage de référence. Aucun geste de soin n’est simulé ou demandé.</x:v>
+        <x:v>Écoulement synthétique de démonstration sans patient ni geste de soin. Conserver le mouvement lisible à qualité réduite.</x:v>
       </x:c>
       <x:c r="O125" s="11" t="str">
         <x:v>Tube translucide, gouttes animées et pied médical.</x:v>
@@ -16904,7 +19374,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R125" s="11" t="str">
-        <x:v>Spécification originale ; effet absent du catalogue runtime v0.2.1.</x:v>
+        <x:v>Version 0.4.0 : 19 tests de règles et 25 contrôles CPU de scène ; données, transformations, effets et reset. Pixels, shaders, lisibilité, lumière et FPS restent à tester sur GPU.</x:v>
       </x:c>
       <x:c r="S125" s="19" t="str">
         <x:v>—</x:v>
@@ -16913,10 +19383,13 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="U125" s="19" t="str">
-        <x:v>—</x:v>
+        <x:v>Oui</x:v>
       </x:c>
       <x:c r="V125" s="11" t="str">
         <x:v>Visuel / objet / espace</x:v>
+      </x:c>
+      <x:c r="W125" s="19" t="str">
+        <x:v>—</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16940,7 +19413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c06891e25be4b15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra39f3ec528d641f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17259,7 +19732,7 @@
         <x:v>Déconnexion</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>Détecter les absents après 45 secondes ; suspendre le quorum et permettre la reprise.</x:v>
+        <x:v>Détecter l’absence à 45 secondes, annuler les votes antérieurs et demander un nouvel accord après la reprise.</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str">
         <x:v>Présence et jeton du membre</x:v>
@@ -17268,10 +19741,10 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
-        <x:v>Rapport v0.2 conservé : D1 local réel : quatre clients HTTP, neuf consensus concurrents, campagne trois lieux et références propres, signalisation privée et départ réussis. Ni microphones physiques ni trajet TURN réel testés par ce rapport.</x:v>
+        <x:v>19 tests de règles, 28 de résilience et vrai serveur HTTP portable réussis. Deux clients puis chalet à quatre clients, neuf diagnostics jusqu’à victoire, pings sans lecture privée. Linux / Node 24.22.1 ; aucune nouvelle campagne D1 hébergée ni partie humaine.</x:v>
       </x:c>
       <x:c r="G16" s="12" t="str">
-        <x:v>Un départ explicite retire le membre ; le transfert de responsable ne révèle pas les autres perceptions.</x:v>
+        <x:v>Les 28 tests de résilience vérifient retours, votes périmés, migration du responsable, projections privées et files radio. Essais Internet prolongés distincts.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="51" customHeight="1">
@@ -17320,7 +19793,7 @@
         <x:v>Les essais de microphones, casques, iOS/Android et réseaux réels restent nécessaires.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="40" customHeight="1">
+    <x:row r="19" ht="51" customHeight="1">
       <x:c r="A19" s="11" t="str">
         <x:v>C14</x:v>
       </x:c>
@@ -17337,7 +19810,7 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>Les six effets radio sont également révélés par l’étalonnage déterministe.</x:v>
+        <x:v>Les douze profils radio disposent de preuves d’étalonnage déterministes ; contre-code et ordre inversé portent seulement sur le contrôle synthétique.</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
         <x:v>Le partenaire continue de transmettre sa vraie voix ; aucune phrase personnelle n’est copiée ou rejouée à son insu.</x:v>
@@ -17504,7 +19977,7 @@
         <x:v>Les certificats et clés LAN sont optionnels et doivent être fournis par l’hébergeur.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="40" customHeight="1">
+    <x:row r="27" ht="51" customHeight="1">
       <x:c r="A27" s="11" t="str">
         <x:v>C22</x:v>
       </x:c>
@@ -17521,10 +19994,10 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>Identifiants calculés côté serveur ; le client ne reçoit pas le secret de signature.</x:v>
+        <x:v>59 tests vérifient URI, limites, secrets, HMAC, expiration et précontrôle statique ; aucun secret de signature n’est transmis au client.</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>Configuration et tests automatisés présents ; service TURN réel et trajet relay encore à éprouver.</x:v>
+        <x:v>tests/radio-config.test.mjs ; scripts/check-radio-config.mjs. Ne mesure ni DNS, ni certificat, ni disponibilité réelle du relais TURN.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="40" customHeight="1">
@@ -17596,20 +20069,135 @@
         <x:v>Le vrai roster et les noms de l’interface demeurent fiables.</x:v>
       </x:c>
     </x:row>
+    <x:row r="31" ht="51" customHeight="1">
+      <x:c r="A31" s="11" t="str">
+        <x:v>C26</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>Repères plausibles</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>Comparer BUREAU D2, CONSIGNE C9, dossier 09 et journal au même passage.</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>Valeurs communes variables par passage ; variante privée pour les témoins.</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>Les deux lectures sont plausibles isolément ; leur désaccord stable donne la preuve.</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str">
+        <x:v>Nommer l’appareil, le côté et le passage. Une différence entre deux passages peut être normale.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="40" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>C27</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Corps et interface</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Les altérations d’avatar changent seulement le modèle perçu.</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>Slot ciblé, corps local ou pair, couche de reflet.</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>Le roster, la pose autoritaire et le nombre de participants restent fiables.</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>Tester départ / retour de la cible et empêcher un effet d’avatar de s’étendre aux autres corps.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="51" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>C28</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Lecture agrandie</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>E conserve le ping et l’ajout au carnet sur toute cible ; l’agrandissement s’ouvre seulement si cet objet possède une lecture actuelle.</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>Valeur de l’objet dans la perception locale ; aucune valeur privée dans le ping.</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>Les quatorze postes d’inspection de l’hôtel reprennent la valeur privée réellement affichée, sans verdict ; seuls les IDs du repère sont partagés.</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str">
+        <x:v>L’inspection reste facultative ; le zoom ne remplace pas la preuve visuelle ou le dialogue.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="51" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>C29</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Roster et archives</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Registre, photo et afficheur utilisent les indicatifs et pseudonymes des membres présents.</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>ID stable, slot, pseudonyme public ; pas de donnée personnelle externe.</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Départ et retour actualisent le nombre et les signatures sans effacer l’effet privé.</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>En solo, Inspecteur reste le même membre lors du changement Alpha/Bêta ; le témoin fictif du registre ne compte pas comme connecté.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="51" customHeight="1">
+      <x:c r="A35" s="11" t="str">
+        <x:v>C30</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>Signalisation après reprise</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>Écarter les messages radio liés à une ancienne présence ou une ancienne identité radio.</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>Expéditeur, destinataire, epoch, date et présence courante.</x:v>
+      </x:c>
+      <x:c r="E35" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>Seul le destinataire actuel reçoit un message encore valide ; aucun résultat privé divulgué.</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str">
+        <x:v>tests/session-resilience.test.mjs : contrôles automatisés ; voix réellement connectée à vérifier sur appareils.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E30">
+  <x:conditionalFormatting sqref="E6:E35">
     <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E30">
+    <x:dataValidation type="list" sqref="E6:E35">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35883761b6a46d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda28ffe4025f49a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18307,7 +20895,7 @@
         <x:v>Recette casque</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>Tester voix normale et six effets à volume raisonnable.</x:v>
+        <x:v>Tester voix normale et les profils de réception disponibles à volume raisonnable.</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>Compréhension, absence de saturation dure et repos auditif.</x:v>
@@ -18322,7 +20910,7 @@
         <x:v>Deux puis quatre microphones physiques, plusieurs navigateurs.</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>19 tests radio et la négociation partielle de la v0.2 ne constituent pas un essai de microphones physiques ou d’écoute de flux vocal.</x:v>
+        <x:v>32 tests radio et la négociation partielle de la v0.2 ne constituent pas un essai de microphones physiques ou d’écoute de flux vocal.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="40" customHeight="1">
@@ -18348,7 +20936,7 @@
         <x:v>Aucune équipe bloquée si les partenaires sont sur deux canaux.</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>Ne pas annoncer cette extension comme disponible en v0.2.</x:v>
+        <x:v>Canaux de proximité et sous-groupes restent prévus, sans option jouable actuellement.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -18400,7 +20988,7 @@
         <x:v>Trois contradictions relationnelles ne peuvent être trouvées avec une seule lecture isolée.</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str">
-        <x:v>Le test 1 / 2 / 3 est un autre appareil de preuve ; nommer le repère évite de comparer deux écrans différents.</x:v>
+        <x:v>Le contrôle radio identifie aussi RELAIS avant ses trois tons principaux ; comparer chaque appareil nommé dans le même passage.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="40" customHeight="1">
@@ -18481,20 +21069,280 @@
         <x:v>Contrôleur testé séparément du client vocal ; ces tests ne sont pas un essai de permission sur microphone physique.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="40" customHeight="1">
+      <x:c r="A36" s="12" t="str">
+        <x:v>R31</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>Clic final absent</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="str">
+        <x:v>Clic initial, identification et séquence présents ; fermeture manquante.</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
+        <x:v>Comparer le relevé de clôture sur deux essais.</x:v>
+      </x:c>
+      <x:c r="E36" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>Répéter sans partenaire parlant ; l’indicateur micro réel doit suivre son état technique.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="40" customHeight="1">
+      <x:c r="A37" s="11" t="str">
+        <x:v>R32</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>Contre-code RELAIS</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>L’identifiant DTMF du contrôle diffère du panneau du même passage.</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>Lire les quatre chiffres panneau / contrôle.</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H37" s="11" t="str">
+        <x:v>Le code de panneau reste intact ; aucune voix humaine ou synthèse de parole requise.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="40" customHeight="1">
+      <x:c r="A38" s="12" t="str">
+        <x:v>R33</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>Signal latéral</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="str">
+        <x:v>Le contrôle est routé entièrement à gauche.</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
+        <x:v>Relevé G 100 / D 0 contre signal centré.</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="str">
+        <x:v>Le relevé décrit le routage prévu ; il ne diagnostique jamais un casque réel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="40" customHeight="1">
+      <x:c r="A39" s="11" t="str">
+        <x:v>R34</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>Acoustique impossible</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>La queue synthétique est prolongée après les tons.</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>Durée longue contre queue normale courte.</x:v>
+      </x:c>
+      <x:c r="E39" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H39" s="11" t="str">
+        <x:v>Aucune dépendance à la pièce physique, au microphone ou à la latence réseau.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="40" customHeight="1">
+      <x:c r="A40" s="12" t="str">
+        <x:v>R35</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>Ordre échangé</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>La séquence principale devient 1, 3, 2.</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>Lire l’ordre, pas seulement le nombre de tons.</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="str">
+        <x:v>Les chiffres RELAIS précèdent une section distincte ; les deux sections sont étiquetées.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="40" customHeight="1">
+      <x:c r="A41" s="11" t="str">
+        <x:v>R36</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>Quatrième souffle</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>Une impulsion synthétique soufflée suit les trois étapes et la clôture.</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>Attendre la fin complète puis compter les étapes principales.</x:v>
+      </x:c>
+      <x:c r="E41" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>Étalonner / relevé écrit</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="str">
+        <x:v>Résultat reproductible au même passage, même sans micro et sans connexion audio.</x:v>
+      </x:c>
+      <x:c r="H41" s="11" t="str">
+        <x:v>Pas de copie de voix ou de souffle de joueur ; arrêt de l’écoute disponible.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="40" customHeight="1">
+      <x:c r="A42" s="12" t="str">
+        <x:v>R37</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>Sections du contrôle</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="str">
+        <x:v>Clic initial → identifiant RELAIS DTMF → séquence principale 1, 2, 3 → clic final.</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
+        <x:v>Quatre chiffres d’identification séparés de trois étapes de contrôle.</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>Panneau RELAIS + bouton Étalonner</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>Chaque section est nommée dans le relevé ; les comptes de tons ne sont pas ambigus.</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="str">
+        <x:v>Le relevé décrit ce que le moteur produit, sans annoncer directement « anomalie ».</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="40" customHeight="1">
+      <x:c r="A43" s="11" t="str">
+        <x:v>R38</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>Équité sans matériel</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>Le contrôle détermine sa preuve à partir de la perception privée et du code du passage.</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>Aucun test ne requiert qu’un autre joueur parle.</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>Texte, audio local, voix si disponible</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str">
+        <x:v>Micro refusé, pair muet ou ICE indisponible ne changent pas la vérité du passage.</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="str">
+        <x:v>Le fonctionnement du transport vocal et le rendu du signal sont deux vérifications distinctes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="40" customHeight="1">
+      <x:c r="A44" s="12" t="str">
+        <x:v>R39</x:v>
+      </x:c>
+      <x:c r="B44" s="12" t="str">
+        <x:v>Configuration vérifiée</x:v>
+      </x:c>
+      <x:c r="C44" s="12" t="str">
+        <x:v>Valider et dédupliquer URI STUN/TURN ; signer des identifiants temporaires bornés.</x:v>
+      </x:c>
+      <x:c r="D44" s="12" t="str">
+        <x:v>Le précontrôle indique la cohérence de la configuration, pas la connectivité.</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>scripts/check-radio-config.mjs --json / --require-turn</x:v>
+      </x:c>
+      <x:c r="G44" s="12" t="str">
+        <x:v>59 tests automatisés : URI, secrets, expiration HMAC et diagnostics sans fuite.</x:v>
+      </x:c>
+      <x:c r="H44" s="12" t="str">
+        <x:v>Aucun serveur TURN déployé ni transport relay réel validé par ces tests.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="40" customHeight="1">
+      <x:c r="A45" s="11" t="str">
+        <x:v>R40</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>Reconnexion et files</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>Annuler les négociations périmées après interruption de présence ou changement d’epoch.</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>Seul un émetteur présent et une identité radio actuelle peuvent alimenter la boîte privée.</x:v>
+      </x:c>
+      <x:c r="E45" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>src/game/session.ts ; tests/session-resilience.test.mjs</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str">
+        <x:v>28 tests de résilience incluent les files radio, votes et projections privées.</x:v>
+      </x:c>
+      <x:c r="H45" s="11" t="str">
+        <x:v>Une suite automatisée ne prouve pas la réception de voix sur des appareils physiques.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E35">
+  <x:conditionalFormatting sqref="E6:E45">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E35">
+    <x:dataValidation type="list" sqref="E6:E45">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d358a9cbaef4e53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd4a5975d9e4dcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19065,7 +21913,7 @@
         <x:v>Source procédurale, contrats de pose et export GLB original fournis avec manifeste.</x:v>
       </x:c>
       <x:c r="D24" s="12" t="str">
-        <x:v>GLB et trois clips générés puis relus par GLTFLoader.</x:v>
+        <x:v>GLB v0.3.0 et trois clips de base générés puis relus par GLTFLoader.</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -19106,7 +21954,7 @@
         <x:v>Évaluer avec joueurs sensibles au mouvement et aux corps déformés.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="40" customHeight="1">
+    <x:row r="26" ht="51" customHeight="1">
       <x:c r="A26" s="12" t="str">
         <x:v>H21</x:v>
       </x:c>
@@ -19114,38 +21962,246 @@
         <x:v>Inspecteur exportable</x:v>
       </x:c>
       <x:c r="C26" s="12" t="str">
-        <x:v>inspecteur-parallaxe.glb : 52 444 triangles, 51 meshes, 12 nœuds articulés ; dimensions 0,6853 × 1,7287 × 0,508 m.</x:v>
+        <x:v>GLB v0.3.0 : 53 990 triangles, 58 maillages, 12 nœuds articulés ; dimensions 0,6853 × 1,7522 × 0,508 m.</x:v>
       </x:c>
       <x:c r="D26" s="12" t="str">
-        <x:v>Trois clips : Marche 0,766 s ; Radio 1,5 s ; Salut 2 s.</x:v>
+        <x:v>Trois clips exportés : Marche 0,766 s ; Radio 1,5 s ; Salut 2 s.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
-        <x:v>Export relu par GLTFLoader ; sommets finis et trois clips validés.</x:v>
+        <x:v>Réexport depuis avatar v0.3.0 puis relecture GLTFLoader ; sommets et trois clips validés.</x:v>
       </x:c>
       <x:c r="G26" s="12" t="str">
-        <x:v>4 826 384 octets. Pièces rigides sans skinning ; PBR de base. Lettrage du badge runtime non embarqué.</x:v>
+        <x:v>4 825 784 octets. Pièces rigides sans skinning, PBR de base. Lettrage Canvas, sprites de nom et effets de jeu exclus.</x:v>
       </x:c>
       <x:c r="H26" s="12" t="str">
-        <x:v>public/models/inspecteur-parallaxe.manifest.json ; rendu GPU et import outil final non validés.</x:v>
+        <x:v>Manifeste avec version et empreinte source. Les animations d’anomalies sont dans le code du jeu ; rendu GPU et import dans le logiciel final restent ouverts.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="51" customHeight="1">
+      <x:c r="A27" s="11" t="str">
+        <x:v>H22</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>Inspecteur désigné</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>Choisir le premier pair présent par slot, puis le suivant après son départ. Utiliser le corps local uniquement si aucun pair n’est présent.</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>Même corps nommé avant de comparer badge, taille, main, regard ou contact au sol.</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>La cible reste reconnaissable ; le roster ne crée aucun faux joueur.</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="str">
+        <x:v>Identité stable de la cible dans la vue locale ; ne pas sélectionner le modèle par son pseudonyme.</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str">
+        <x:v>Tester départ du collègue ciblé, retour et nettoyage à chaque référence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>H23</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>Badge physique</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Le badge du corps porte son code de slot.</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>La plaque devient vierge pour un témoin.</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>Plaque réellement vide avec contours du badge conservés.</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>Badge de torse et texte runtime ; interface d’identité fiable.</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>Capture proche et éloignée sur GPU, avec tous les éclairages.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="40" customHeight="1">
+      <x:c r="A29" s="11" t="str">
+        <x:v>H24</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>Main du talkie</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>Appareil abaissé dans la main droite normale.</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>Fixation dans la main gauche dans la perception affectée.</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>Preuve visible sans PTT et sans permission microphone.</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="str">
+        <x:v>Attaches du modèle ; aucune préférence de main dominante non réalisée.</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str">
+        <x:v>Comparer face, dos et miroir pour écarter une confusion gauche / droite.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="40" customHeight="1">
+      <x:c r="A30" s="12" t="str">
+        <x:v>H25</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>Échelle et contact</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>Taille constante et pieds au sol.</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>Échelle verticale 1,48 et largeur 1,18, ou décalage visuel du corps de 20 cm.</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>La collision et les coordonnées communes restent intactes.</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>Modifier le modèle seulement ; repères de porte et de sol.</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>Marche, arrêt, reconnexion et performance GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="A31" s="11" t="str">
+        <x:v>H26</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>Regard indépendant</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>Yeux alignés avec la pose de la tête.</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>Regard local orienté vers l’observateur malgré une tête détournée.</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>L’indice reste lisible sous la visière et ne dépend pas d’une webcam.</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str">
+        <x:v>Yeux procéduraux, tête réseau conservée.</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str">
+        <x:v>Captures de plusieurs angles et contraste sur GPU.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="40" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>H27</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Reflet assis</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Corps réel et reflet normalement debout.</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>Le reflet s’assoit sur le vrai tabouret vide, hanches et genoux à 90°, à position fixe près du miroir.</x:v>
+      </x:c>
+      <x:c r="E32" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>Jambes et bassin du reflet changent ; décor et corps réel restent cohérents.</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>Animation du corps réfléchi ; aucune interaction de siège requise.</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>Rendu comparatif, absence de récursion et reset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="40" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>H28</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Code du reflet</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>Badge du corps et badge réfléchi correspondent.</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>Le reflet porte le code du slot suivant.</x:v>
+      </x:c>
+      <x:c r="E33" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>Le vrai badge et le roster demeurent exacts.</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str">
+        <x:v>Texture / code du corps réfléchi uniquement.</x:v>
+      </x:c>
+      <x:c r="H33" s="11" t="str">
+        <x:v>Lisibilité miroir et absence de simple inversion optique prise comme preuve.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="40" customHeight="1">
+      <x:c r="A34" s="12" t="str">
+        <x:v>H29</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Le groupe absent</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="str">
+        <x:v>Le miroir montre le corps local et les collègues ; deux mannequins numérotés servent de témoins en solo.</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>Les collègues ou témoins disparaissent uniquement du miroir ; le corps local reste.</x:v>
+      </x:c>
+      <x:c r="E34" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Le compte réel et réfléchi diffère ; corps physiques et socles restent présents.</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>Masquage dans la passe de reflet ; compatible avec les quatre lieux.</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>Contrôle CPU des couches ; lisibilité, cadrage et performance GPU restent à vérifier.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E26">
+  <x:conditionalFormatting sqref="E6:E34">
     <x:cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E26">
+    <x:dataValidation type="list" sqref="E6:E34">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red0cdd15c5124224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4590cf0c7f51475d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19183,7 +22239,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>Campagne : trois lieux, trois preuves chacun</x:v>
+        <x:v>Trois lieux de campagne et un chalet autonome</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -19209,7 +22265,7 @@
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>Les pools partagent des anomalies communes : leurs tailles ne s’additionnent pas en contenu unique.</x:v>
+        <x:v>La campagne reste Saint-Clair → Terminus 09 → Aile blanche. Le Chalet de service se choisit en lieu unique. Les pools se chevauchent.</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -19253,7 +22309,7 @@
         <x:v>Recette restante</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="51" customHeight="1">
       <x:c r="A6" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -19267,14 +22323,14 @@
         <x:v>Campagne : 0 → 3. Une erreur remet le secteur à 0.</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Portes 901–904 fermées ; horloge 03:09 ; plantes vertes ; meubles au sol ; fenêtre vide ; tableau complet ; reflets synchrones.</x:v>
+        <x:v>Portes 901–904 ; horloge 03:09 ; bureau D2, consigne C9, archives R9 et galerie G9 concordants ; quatre chambres sur le plan ; silhouettes fictives de référence ; reflets synchrones.</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Objets de l’hôtel, altérations spatiales, bagage, miroir et effets communs.</x:v>
+        <x:v>Quatorze objets de contrôle, registre/gant/météo privés, photo d’équipe, plan, règlement, occupants, racines, eau, cinquième porte et issue animée.</x:v>
       </x:c>
       <x:c r="G6" s="26" t="n">
         <x:f>COUNTIFS('Anomalies'!$D$6:$D$125,"Présent",'Anomalies'!$S$6:$S$125,"Oui")</x:f>
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -19300,14 +22356,14 @@
         <x:v>Campagne : palier 3 conservé ; trois réussites pour atteindre 6.</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Quai vide ; QUAI 09 / SERVICE TERMINÉ ; signal vert ; deux rails droits ; corps et reflet synchrones.</x:v>
+        <x:v>Quai vide ; QUAI 09 / SERVICE TERMINÉ ; signal vert ; rails droits ; archives T09/T12 distinctes ; plan à trois stations ; portique SCELLÉ 0000 ; tunnel sombre.</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>Rame présente, destination impossible, signal altéré, rails orientés et ombre de train.</x:v>
+        <x:v>Rame, destination, signal, rails, ombre de train, archives, plan, compteur et ciel dans le tunnel.</x:v>
       </x:c>
       <x:c r="G7" s="29" t="n">
         <x:f>COUNTIFS('Anomalies'!$D$6:$D$125,"Présent",'Anomalies'!$T$6:$T$125,"Oui")</x:f>
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -19319,7 +22375,7 @@
         <x:v>Vérifier le panneau sans texte inversé, les voies hors accès et la visibilité des présences.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+    <x:row r="8" ht="51" customHeight="1">
       <x:c r="A8" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -19333,14 +22389,14 @@
         <x:v>Campagne : palier 6 conservé ; trois réussites pour atteindre 9 et sortir.</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>Un lit vide au sol ; FC 072 / RYTHME SINUSAL ; paravent sans présence ; fauteuil roulant immobile ; reflet normal.</x:v>
+        <x:v>Un lit 09 au couloir ; lit 10 dans la salle vitrée ; FC 072 / RYTHME SINUSAL ; paravent vide ; fauteuil immobile ; gouttes descendantes ; reflet normal.</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Lit levé ou supplémentaire, moniteur incohérent, paravent habité ou respirant, fauteuil mobile.</x:v>
+        <x:v>Mobilier clinique, plaques 09/10, ombre d’occupant sans corps et perfusion de démonstration inversée.</x:v>
       </x:c>
       <x:c r="G8" s="26" t="n">
         <x:f>COUNTIFS('Anomalies'!$D$6:$D$125,"Présent",'Anomalies'!$U$6:$U$125,"Oui")</x:f>
-        <x:v>31</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -19352,20 +22408,53 @@
         <x:v>Vérifier moniteur, tissu, silhouettes et contact au sol sur GPU ; conserver jeu sans audition.</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" ht="51" customHeight="1">
+      <x:c r="A9" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Chalet de service</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Le module d’inspection</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Autonome seulement : neuf validations consécutives. Une erreur remet la série à zéro.</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>Table à quatre pieds, plateau 2,10 m × 1,40 m, tasse et carnet ; cheminée froide et vide ; fenêtre vers un hangar fermé ; poutres et passages stables.</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Table agrandie et visage de cheminée ; preuves communes compatibles avec le lieu ; deux surfaces réfléchissantes.</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="n">
+        <x:f>COUNTIFS('Anomalies'!$D$6:$D$125,"Présent",'Anomalies'!$W$6:$W$125,"Oui")</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>Entrée, axe de marche et passage droit libre ; table derrière garde-corps, foyer observable depuis le tapis. Aucun étage ni transport automatisé de chalets.</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>Neuf tests CPU dédiés ; parcours, images, reflets, lumière et performance à éprouver sur GPU.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="H6:H8">
+  <x:conditionalFormatting sqref="H6:H9">
     <x:cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H6:H8">
+    <x:dataValidation type="list" sqref="H6:H9">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a7ae2a3476c4be6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc275d7f1d4549d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19418,7 +22507,7 @@
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="6" t="str">
-        <x:v>Trois architectures présentes en v0.2. Chaque extension future garde un statut explicite.</x:v>
+        <x:v>Architecture, repères et extensions. Les lieux supplémentaires restent explicitement prévus.</x:v>
       </x:c>
       <x:c r="B4" s="3"/>
       <x:c r="C4" s="3"/>
@@ -19610,7 +22699,7 @@
         <x:v>Conserver une zone de passage pour quatre avatars.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="51" customHeight="1">
       <x:c r="A12" s="12" t="str">
         <x:v>Z07</x:v>
       </x:c>
@@ -19627,7 +22716,7 @@
         <x:v>Corps local, équipiers, décor réfléchi.</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
-        <x:v>reflection_delay, reflection_absent, reflection_independent</x:v>
+        <x:v>reflection_delay, reflection_absent, reflection_independent, mirror_extra_door, reflection_no_team</x:v>
       </x:c>
       <x:c r="G12" s="13" t="str">
         <x:v>Implémenté — QA partielle</x:v>
@@ -19662,30 +22751,30 @@
         <x:v>La décision commune doit être accessible malgré les effets d’ambiance.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="51" customHeight="1">
       <x:c r="A14" s="12" t="str">
         <x:v>Z09</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>Chalet</x:v>
+        <x:v>Chalet de service</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>Usine de modules</x:v>
+        <x:v>Module dans un hangar</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>Chalets successifs transportés dans un hangar d’inspection.</x:v>
+        <x:v>Pièce originale en bois avec entrée, table, foyer, poutres et fenêtre sur le hangar fermé.</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>Foyer, table, étage, fenêtre.</x:v>
+        <x:v>Table 2,10 × 1,40 m, tasse, carnet, cheminée froide et vide.</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>cabine_table_size, cabine_chimney_face</x:v>
+        <x:v>cabine_table_size, cabine_chimney_face ; 35 effets compatibles au total.</x:v>
       </x:c>
       <x:c r="G14" s="13" t="str">
-        <x:v>Conçu — non implémenté</x:v>
+        <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str">
-        <x:v>Quatrième lieu proposé ; prévoir assets originaux et baseline spécifique.</x:v>
+        <x:v>Quatrième lieu autonome uniquement ; passage de droite commun, table protégée par garde-corps ; campagne des trois lieux conservée.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="40" customHeight="1">
@@ -19829,7 +22918,7 @@
         <x:v>Station de radio</x:v>
       </x:c>
       <x:c r="D20" s="12" t="str">
-        <x:v>Dispositif d’étalonnage et repères compatibles avec les trois architectures.</x:v>
+        <x:v>Dispositif d’étalonnage et repères compatibles avec les quatre architectures.</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
         <x:v>1 / 2 / 3 ; retour au silence.</x:v>
@@ -20000,20 +23089,202 @@
         <x:v>Aucun vote implicite par le franchissement d’une porte ; conserver le choix explicite du groupe.</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" ht="40" customHeight="1">
+      <x:c r="A27" s="11" t="str">
+        <x:v>Z22</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>Bureau D2</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>Bureau de contrôle près de l’entrée, distinct des vraies portes 901–904.</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>Chambre assignée 204/205, dossier 09 et journal 26/27 octobre.</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>PX-026,034,036 ; valeurs plausibles variables entre passages, communes entre témoins.</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str">
+        <x:v>Lecture agrandie facultative ; mêmes repères pour tous et aucun verdict automatique.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="40" customHeight="1">
+      <x:c r="A28" s="12" t="str">
+        <x:v>Z23</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="str">
+        <x:v>Consigne C9</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>Deux valises de formes distinctes ; chariot original à une seule valise conservé.</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>Étiquettes 09 et 18 ; la position du 09 est commune au passage.</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>PX-029 ; les étiquettes sont interverties pour une perception.</x:v>
+      </x:c>
+      <x:c r="G28" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>Vérifier formes, côtés, texte et accès au repère ; ne pas confondre consigne et chariot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="40" customHeight="1">
+      <x:c r="A29" s="11" t="str">
+        <x:v>Z24</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>Table témoin</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>Présenter sablier, tasse et râtelier à portée d’observation.</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>Sable descendant, vapeur montante et une seule clé 09.</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>PX-049,050,073 ; directions inversées ou seconde clé 09.</x:v>
+      </x:c>
+      <x:c r="G29" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str">
+        <x:v>Aucun ramassage ; comparer plusieurs instants et maintenir les mouvements à qualité réduite.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="40" customHeight="1">
+      <x:c r="A30" s="12" t="str">
+        <x:v>Z25</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>Aile blanche</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="str">
+        <x:v>Salle vitrée et couloir</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>Deux espaces distincts, chacun avec son lit de référence.</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>Plaque 09 dans le couloir ; plaque 10 dans la salle vitrée.</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>PX-118 ; duplicata 09 sur la seconde plaque. Le couloir conserve un seul lit normal.</x:v>
+      </x:c>
+      <x:c r="G30" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>Distinguer clinic_tag_echo de clinic_bed_count ; lire depuis la zone sûre.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="40" customHeight="1">
+      <x:c r="A31" s="11" t="str">
+        <x:v>Z26</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>Archives R9</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>Panneau mural droit : registre, règlement et afficheur de présence.</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>ARRIVÉE 03:09 / LIGNE 09 ; SIGNALEZ TOUTE ANOMALIE ; PRÉSENTS exact.</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>paired_guestbook, rules_swap, guest_tally</x:v>
+      </x:c>
+      <x:c r="G31" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str">
+        <x:v>Textes localisés et lecture E ; seuls les pseudonymes de session sont utilisés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="40" customHeight="1">
+      <x:c r="A32" s="12" t="str">
+        <x:v>Z27</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="str">
+        <x:v>Galerie G9</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>Panneau mural gauche : météo du quai, équipe de nuit et plan.</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>Météo commune du passage ; A. MOREL / E. VIAL / N. ROCHER ; chambres 901–904.</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>paired_photo_weather, wrong_team_photo, map_missing_room</x:v>
+      </x:c>
+      <x:c r="G32" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>Pluie, neige et soleil lisibles par leurs formes ; la chambre 903 correspond à la porte réelle à gauche vers l’issue.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="40" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>Z28</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Saint-Clair</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>Plateau de la consigne C9</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>Gant posé avec paume, doigts et pouce modélisés ; marque ICI au sol.</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>Poignet vers le témoin placé sur ICI ; latéralité commune dans un passage.</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>paired_hand</x:v>
+      </x:c>
+      <x:c r="G33" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="H33" s="11" t="str">
+        <x:v>Les deux latéralités sont ordinaires ; conserver un point de comparaison partagé et l’axe libre.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G6:G26">
+  <x:conditionalFormatting sqref="G6:G33">
     <x:cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G6:G26">
+    <x:dataValidation type="list" sqref="G6:G33">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2424c44b8c9c40f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cbe62c8253741d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20094,7 +23365,7 @@
         <x:v>Limite ou étape suivante</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="51" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>A01</x:v>
       </x:c>
@@ -20102,7 +23373,7 @@
         <x:v>Direction</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Trois atmosphères : hôtel laiton/bois, métro céramique/métal, clinique matière pâle/verre.</x:v>
+        <x:v>Quatre atmosphères : hôtel laiton/bois, métro céramique/métal, clinique pâle/verre, chalet de bois dans un hangar froid.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
         <x:v>Cohérence des repères ; silhouettes lisibles.</x:v>
@@ -20278,7 +23549,7 @@
         <x:v>La vue normale doit être montrée pendant la référence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="51" customHeight="1">
       <x:c r="A14" s="12" t="str">
         <x:v>A09</x:v>
       </x:c>
@@ -20295,7 +23566,7 @@
         <x:v>Implémenté — QA partielle</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>Le décor reste réfléchi quand seul le corps disparaît.</x:v>
+        <x:v>Huit surfaces planaires, deux par lieu ; les effets retirent uniquement les corps ou ajouts concernés, en conservant le décor.</x:v>
       </x:c>
       <x:c r="G14" s="12" t="str">
         <x:v>Reflection pass temps réel ; pas de promesse de ray tracing ni de validation de pixels GPU.</x:v>
@@ -20654,10 +23925,10 @@
         <x:v>Géométrie contrôlée</x:v>
       </x:c>
       <x:c r="C30" s="12" t="str">
-        <x:v>Hôtel : 196 580 triangles ; métro : 84 278 ; clinique : 107 032, effets cachés compris. Inspecteur articulé : 52 444 triangles. Six surfaces planaires, deux actives par lieu.</x:v>
+        <x:v>Géométrie stockée : 582 153 triangles et 1 244 maillages. Hôtel 252 932, métro 102 766, clinique 126 607, chalet 75 956. Inspecteur 53 990. Inclut objets/effets inactifs ; ce ne sont pas des triangles dessinés par image.</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>Preuves v0.2 conservées : 11 suites CPU réussies : données finies, normales, luminaires, 48 effets et raycasts, corps/reflets sans récursion, retard réel proche d’une seconde, traversée des trois lieux, relais, collision, qualité et nettoyage.</x:v>
+        <x:v>25 contrôles CPU de scène réussis : 84 effets visuels, reset, raycasts, accès, reflets, roster stable et quatre lieux. Huit surfaces planaires, deux par lieu. Neuf tests chalet séparés. Aucun pixel, shader ou FPS validé.</x:v>
       </x:c>
       <x:c r="E30" s="13" t="str">
         <x:v>Contrôle structurel partiel</x:v>
@@ -20666,7 +23937,7 @@
         <x:v>Contrôle de données et raycasts ; aucune mesure FPS implicite.</x:v>
       </x:c>
       <x:c r="G30" s="12" t="str">
-        <x:v>Le navigateur de contrôle ne fournit pas de renderer WebGL actif. Les shaders, reflets et images restent à éprouver sur GPU.</x:v>
+        <x:v>La route de prévisualisation terminal.local:4173 a refusé la connexion en 0.4.0. Aucun pixel, shader, éclairage perçu ni FPS n’est validé ; anciens essais GPU/ICE conservés comme historiques.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40" customHeight="1">
@@ -20876,20 +24147,43 @@
         <x:v>L’intensité est une intention de design, à confirmer en playtests de confort.</x:v>
       </x:c>
     </x:row>
+    <x:row r="40" ht="40" customHeight="1">
+      <x:c r="A40" s="12" t="str">
+        <x:v>A35</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>Chalet et dégagements</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="str">
+        <x:v>Architecture originale, plateau paramétrique, foyer creux, poutres, fenêtre sur hangar et garde-corps.</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>Volumes physiques communs entre perceptions.</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="str">
+        <x:v>Implémenté — QA partielle</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Neuf contrôles CPU dédiés : géométrie finie, accès, collisions, repères et reset.</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>Rendu et parcours sur appareils restent ouverts ; le comptage de triangles inclut les objets inactifs.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E6:E39">
+  <x:conditionalFormatting sqref="E6:E40">
     <x:cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="Bloqué"/>
     <x:cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="Validé"/>
     <x:cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Réussi"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="E6:E39">
+    <x:dataValidation type="list" sqref="E6:E40">
       <x:formula1>"Présent,Prévu,Implémenté — QA partielle,Validé,À vérifier,Conçu — non implémenté,Bloqué,Réussi,Partiel,À exécuter,À tester sur GPU,À tester sur appareils,Conception définie,Contrôle structurel partiel"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb908f5982fa1425a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1dea0bbf2434bc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>